--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Successful Signals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Successful Signals" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,7 +45,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,19 +53,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -571,55 +562,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>119</v>
+        <v>860</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>155</v>
+        <v>975</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>145</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>860</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -1639,7 +1630,7 @@
         <v>13.69</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>336</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>386</v>
@@ -1747,7 +1738,7 @@
         <v>12.12</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>316</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>372</v>
@@ -1759,142 +1750,142 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>30.41</v>
+        <v>11.61</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>11.49</v>
+        <v>11.61</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>16.39</v>
+        <v>30.41</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1903,214 +1894,214 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>30.34</v>
+        <v>22.5</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>14.73</v>
+        <v>30.34</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.11</v>
+        <v>11.24</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1955</v>
+        <v>93</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2220</v>
+        <v>116</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>12.67</v>
+        <v>14.73</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1690</v>
+        <v>2220</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1665</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>535</v>
+        <v>130</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>22.64</v>
+        <v>10.38</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>106</v>
+        <v>535</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>130</v>
+        <v>585</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>117</v>
+        <v>585</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>10.88</v>
+        <v>18.18</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>815</v>
+        <v>104</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>810</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2119,52 +2110,52 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>14.68</v>
+        <v>10.88</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>545</v>
+        <v>770</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>625</v>
+        <v>815</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>19.77</v>
+        <v>14.68</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>212</v>
+        <v>625</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2173,667 +2164,667 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>13.04</v>
+        <v>19.77</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>580</v>
+        <v>179</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>650</v>
+        <v>212</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>630</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>17.09</v>
+        <v>13.04</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9.49</v>
+        <v>9.57</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>316</v>
+        <v>580</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>346</v>
+        <v>630</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>11.4</v>
+        <v>11.72</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>388</v>
+        <v>128</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>422</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>11</v>
+        <v>22.73</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>28.09</v>
+        <v>11</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>22.69</v>
+        <v>28.09</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1085</v>
+        <v>177</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1325</v>
+        <v>228</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>15.2</v>
+        <v>22.69</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>8.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>364</v>
+        <v>1085</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>394</v>
+        <v>1325</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>372</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>18.46</v>
+        <v>15.2</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>141</v>
+        <v>372</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>14.29</v>
+        <v>24.57</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>112</v>
+        <v>2600</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>128</v>
+        <v>3600</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>121</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>10.11</v>
+        <v>14.29</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>7.98</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>945</v>
+        <v>112</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1035</v>
+        <v>128</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1015</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>23.46</v>
+        <v>13.38</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>161</v>
+        <v>4410</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>174</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>10.05</v>
+        <v>23.46</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>7.41</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>416</v>
+        <v>200</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>406</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>14</v>
+        <v>22.86</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>17.44</v>
+        <v>14</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>6.98</v>
+        <v>7</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>19.4</v>
+        <v>17.44</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>6.97</v>
+        <v>6.98</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>408</v>
+        <v>86</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>480</v>
+        <v>101</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>430</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>24.86</v>
+        <v>19.4</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>6.91</v>
+        <v>6.97</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2260</v>
+        <v>408</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2260</v>
+        <v>480</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1935</v>
+        <v>430</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>22.32</v>
+        <v>24.86</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6.87</v>
+        <v>6.91</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>490</v>
+        <v>2260</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>570</v>
+        <v>2260</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>498</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>15.53</v>
+        <v>22.32</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6.8</v>
+        <v>6.87</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>103</v>
+        <v>490</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>119</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>110</v>
+        <v>498</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>23.33</v>
+        <v>15.53</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="E88" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="F88" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="F88" s="3" t="n">
-        <v>148</v>
-      </c>
       <c r="G88" s="3" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89">
@@ -2866,196 +2857,196 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>17.46</v>
+        <v>23.33</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>148</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>16.67</v>
+        <v>11.47</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>5.83</v>
+        <v>6.18</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>605</v>
+        <v>3460</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>700</v>
+        <v>3790</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>635</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1095</v>
+        <v>605</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>1100</v>
+        <v>635</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>12.64</v>
+        <v>25</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>88</v>
+        <v>1095</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>98</v>
+        <v>1300</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>92</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>840</v>
+        <v>98</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>745</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>25</v>
+        <v>19.15</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.49</v>
+        <v>5.67</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>358</v>
+        <v>705</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>410</v>
+        <v>840</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>346</v>
+        <v>745</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3064,79 +3055,79 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>11.58</v>
+        <v>25</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.26</v>
+        <v>5.49</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>96</v>
+        <v>358</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>106</v>
+        <v>410</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>10.31</v>
+        <v>19.15</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>5.15</v>
+        <v>5.32</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>14.36</v>
+        <v>11.58</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5.13</v>
+        <v>5.26</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>390</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>410</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3145,133 +3136,133 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>11.5</v>
+        <v>10.31</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>4.87</v>
+        <v>5.15</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>2330</v>
+        <v>98</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>2520</v>
+        <v>107</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>2370</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>13.33</v>
+        <v>14.36</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4.71</v>
+        <v>5.13</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2750</v>
+        <v>390</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>2890</v>
+        <v>446</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>2670</v>
+        <v>410</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>11.63</v>
+        <v>11.5</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>87</v>
+        <v>2330</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>96</v>
+        <v>2520</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>90</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>10.6</v>
+        <v>13.33</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>152</v>
+        <v>2750</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>167</v>
+        <v>2890</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>158</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3280,133 +3271,133 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>252</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>15.09</v>
+        <v>19.77</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3.77</v>
+        <v>4.52</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>12.69</v>
+        <v>13.04</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>3.73</v>
+        <v>4.35</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>136</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>139</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>11.97</v>
+        <v>20.56</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>3.42</v>
+        <v>4.23</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>118</v>
+        <v>1980</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>131</v>
+        <v>2140</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>121</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>12.45</v>
+        <v>15</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>545</v>
+        <v>101</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>560</v>
+        <v>115</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>515</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3415,133 +3406,133 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>17.21</v>
+        <v>15.09</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>615</v>
+        <v>159</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>715</v>
+        <v>183</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>630</v>
+        <v>165</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>23.66</v>
+        <v>12.69</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>380</v>
+        <v>136</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>460</v>
+        <v>151</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>384</v>
+        <v>139</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>30.95</v>
+        <v>12.45</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>141</v>
+        <v>545</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>165</v>
+        <v>560</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>130</v>
+        <v>515</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>34.34</v>
+        <v>17.21</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3.03</v>
+        <v>3.28</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>133</v>
+        <v>615</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>133</v>
+        <v>715</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>102</v>
+        <v>630</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3550,106 +3541,106 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>11.63</v>
+        <v>23.66</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>174</v>
+        <v>380</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>192</v>
+        <v>460</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>177</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>11.89</v>
+        <v>11.83</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>288</v>
+        <v>95</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>320</v>
+        <v>104</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>294</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>12.15</v>
+        <v>30.95</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>16.7</v>
+        <v>34.34</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2.78</v>
+        <v>3.03</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>5200</v>
+        <v>133</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>5450</v>
+        <v>133</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>4800</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3658,133 +3649,133 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>14.62</v>
+        <v>11.63</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2550</v>
+        <v>174</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>2900</v>
+        <v>192</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>2600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>17.95</v>
+        <v>11.89</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>92</v>
+        <v>320</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>80</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>17.44</v>
+        <v>16.7</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>87</v>
+        <v>5200</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>101</v>
+        <v>5450</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>88</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>12.36</v>
+        <v>14.62</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>89</v>
+        <v>2550</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>91</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3793,52 +3784,52 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>11.75</v>
+        <v>10.16</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>3380</v>
+        <v>172</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>3900</v>
+        <v>206</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>3560</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>25</v>
+        <v>17.95</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3847,397 +3838,397 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>10.34</v>
+        <v>17.44</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>384</v>
+        <v>101</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>354</v>
+        <v>88</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>11.83</v>
+        <v>12.36</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>189</v>
+        <v>91</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>15.38</v>
+        <v>11.75</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.28</v>
+        <v>2.01</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>79</v>
+        <v>3380</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>90</v>
+        <v>3900</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>79</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>10.59</v>
+        <v>25</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>86</v>
+        <v>204</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>21.97</v>
+        <v>14.29</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1.16</v>
+        <v>1.97</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>865</v>
+        <v>2140</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1055</v>
+        <v>2320</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>875</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>13.64</v>
+        <v>11.54</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>88</v>
+        <v>2100</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>100</v>
+        <v>2320</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>89</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>10.68</v>
+        <v>10.34</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.97</v>
+        <v>1.72</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>210</v>
+        <v>348</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>208</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>22.58</v>
+        <v>11.83</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.54</v>
+        <v>1.61</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1910</v>
+        <v>187</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>2280</v>
+        <v>208</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>1870</v>
+        <v>189</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>10.76</v>
+        <v>19.87</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>3170</v>
+        <v>8125</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>3500</v>
+        <v>9350</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>3160</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>28.48</v>
+        <v>15.38</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>151</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>12.87</v>
+        <v>15.94</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>93</v>
+        <v>13800</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>114</v>
+        <v>16000</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>101</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>17.5</v>
+        <v>10.59</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>14.43</v>
+        <v>21.97</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>-0.52</v>
+        <v>1.16</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>2020</v>
+        <v>865</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>2220</v>
+        <v>1055</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>1930</v>
+        <v>875</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>18.04</v>
+        <v>13.64</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>-0.71</v>
+        <v>1.14</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>88</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>332.87</v>
+        <v>100</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>280</v>
+        <v>89</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>29.27</v>
+        <v>10.68</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>-1.22</v>
+        <v>0.97</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>81</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141">
@@ -4248,29 +4239,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>10.17</v>
+        <v>22.58</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>-1.27</v>
+        <v>0.54</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>2400</v>
+        <v>1910</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>2600</v>
+        <v>2280</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>2330</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4279,882 +4270,1179 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>16.02</v>
+        <v>10.76</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>-2.21</v>
+        <v>0</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>181</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>210</v>
+        <v>3500</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>177</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>10.49</v>
+        <v>17.5</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>-2.47</v>
+        <v>0</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>316</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>15.31</v>
+        <v>12.87</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>-2.55</v>
+        <v>0</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>226</v>
+        <v>114</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>191</v>
+        <v>101</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>10.1</v>
+        <v>28.48</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>-3.03</v>
+        <v>0</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>10300</v>
+        <v>152</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>10900</v>
+        <v>194</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>9600</v>
+        <v>151</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>10.65</v>
+        <v>14.43</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>-3.24</v>
+        <v>-0.52</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>458</v>
+        <v>2020</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>478</v>
+        <v>2220</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>418</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>11.11</v>
+        <v>18.04</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>-4.94</v>
+        <v>-0.71</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>83</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>90</v>
+        <v>332.87</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>77</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>23.53</v>
+        <v>29.27</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>-5.15</v>
+        <v>-1.22</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>840</v>
+        <v>106</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>645</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>13.58</v>
+        <v>10.17</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>-5.56</v>
+        <v>-1.27</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>162</v>
+        <v>2400</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>184</v>
+        <v>2600</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>153</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>10.5</v>
+        <v>16.02</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>-6.39</v>
+        <v>-2.21</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1175</v>
+        <v>181</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1210</v>
+        <v>210</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1025</v>
+        <v>177</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>16.8</v>
+        <v>10.49</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>-6.8</v>
+        <v>-2.47</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>2500</v>
+        <v>322</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>2920</v>
+        <v>358</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>10.67</v>
+        <v>11.19</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>-7.33</v>
+        <v>-2.52</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>152</v>
+        <v>420</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>166</v>
+        <v>454</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>139</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>15.79</v>
+        <v>15.31</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>-7.89</v>
+        <v>-2.55</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>835</v>
+        <v>169</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>880</v>
+        <v>226</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>700</v>
+        <v>191</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>20.41</v>
+        <v>10.1</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>-8.16</v>
+        <v>-3.03</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>100</v>
+        <v>10300</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>118</v>
+        <v>10900</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>90</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>12.73</v>
+        <v>10.65</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>-8.18</v>
+        <v>-3.24</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>248</v>
+        <v>478</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>202</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>24.62</v>
+        <v>19.31</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.14</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>1600</v>
+        <v>149</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1620</v>
+        <v>173</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>1190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>21.43</v>
+        <v>11.11</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>-8.57</v>
+        <v>-4.94</v>
       </c>
       <c r="E157" s="3" t="n">
         <v>83</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>18.95</v>
+        <v>10.19</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>-8.77</v>
+        <v>-5.1</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>8475</v>
+        <v>346</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>8475</v>
+        <v>346</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>6500</v>
+        <v>298</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>20.81</v>
+        <v>23.53</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>-9.09</v>
+        <v>-5.15</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>432</v>
+        <v>700</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>505</v>
+        <v>840</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>380</v>
+        <v>645</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>16.35</v>
+        <v>13.58</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>-12.5</v>
+        <v>-5.56</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>30.37</v>
+        <v>10.5</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>-14.07</v>
+        <v>-6.39</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>142</v>
+        <v>1175</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>176</v>
+        <v>1210</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>116</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>16.36</v>
+        <v>16.8</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-14.55</v>
+        <v>-6.8</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>175</v>
+        <v>2500</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>192</v>
+        <v>2920</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>141</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>15.1</v>
+        <v>10.67</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-14.58</v>
+        <v>-7.33</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>386</v>
+        <v>152</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>442</v>
+        <v>166</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>328</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>12.36</v>
+        <v>15.79</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-14.61</v>
+        <v>-7.89</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>860</v>
+        <v>835</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>18.87</v>
+        <v>20.41</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-14.62</v>
+        <v>-8.16</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>181</v>
+        <v>90</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>16.38</v>
+        <v>12.73</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-14.66</v>
+        <v>-8.18</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>470</v>
+        <v>240</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>540</v>
+        <v>248</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>396</v>
+        <v>202</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>19.27</v>
+        <v>24.62</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-14.68</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>222</v>
+        <v>1600</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>260</v>
+        <v>1620</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>17.21</v>
+        <v>21.43</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-14.75</v>
+        <v>-8.57</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>11.83</v>
+        <v>18.95</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-14.79</v>
+        <v>-8.77</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>318</v>
+        <v>8475</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>378</v>
+        <v>8475</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>288</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>20.37</v>
+        <v>20.81</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-14.81</v>
+        <v>-9.09</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>260</v>
+        <v>505</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>184</v>
+        <v>380</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>15.94</v>
+        <v>16.35</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-14.86</v>
+        <v>-12.5</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2760</v>
+        <v>91</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>3200</v>
+        <v>121</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2350</v>
+        <v>91</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>14.05</v>
+        <v>30.37</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.07</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>25</v>
+        <v>16.36</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.55</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>PEHA.JK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TALF.JK</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>-14.61</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>860</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>KJEN.JK</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>-14.62</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>-14.66</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>468.4084412545869</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>540</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>NZIA.JK</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C185" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D174" s="2" t="n">
+      <c r="D185" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E174" s="3" t="n">
+      <c r="E185" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F174" s="3" t="n">
+      <c r="F185" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G174" s="3" t="n">
+      <c r="G185" s="3" t="n">
         <v>120</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -1764,9 +1764,7 @@
       <c r="D49" s="2" t="n">
         <v>11.94</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>135</v>
-      </c>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="n">
         <v>156</v>
       </c>
@@ -3087,9 +3085,7 @@
       <c r="D98" s="2" t="n">
         <v>5.32</v>
       </c>
-      <c r="E98" s="3" t="n">
-        <v>103</v>
-      </c>
+      <c r="E98" s="3" t="inlineStr"/>
       <c r="F98" s="3" t="n">
         <v>112</v>
       </c>
@@ -3357,9 +3353,7 @@
       <c r="D108" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="E108" s="3" t="n">
-        <v>1980</v>
-      </c>
+      <c r="E108" s="3" t="inlineStr"/>
       <c r="F108" s="3" t="n">
         <v>2140</v>
       </c>
@@ -3384,9 +3378,7 @@
       <c r="D109" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E109" s="3" t="n">
-        <v>101</v>
-      </c>
+      <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="n">
         <v>115</v>
       </c>
@@ -3951,9 +3943,7 @@
       <c r="D130" s="2" t="n">
         <v>1.97</v>
       </c>
-      <c r="E130" s="3" t="n">
-        <v>2140</v>
-      </c>
+      <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3" t="n">
         <v>2320</v>
       </c>
@@ -3978,9 +3968,7 @@
       <c r="D131" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="E131" s="3" t="n">
-        <v>2100</v>
-      </c>
+      <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="n">
         <v>2320</v>
       </c>
@@ -4059,9 +4047,7 @@
       <c r="D134" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="E134" s="3" t="n">
-        <v>8125</v>
-      </c>
+      <c r="E134" s="3" t="inlineStr"/>
       <c r="F134" s="3" t="n">
         <v>9350</v>
       </c>
@@ -4113,9 +4099,7 @@
       <c r="D136" s="2" t="n">
         <v>1.27</v>
       </c>
-      <c r="E136" s="3" t="n">
-        <v>13800</v>
-      </c>
+      <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3" t="n">
         <v>16000</v>
       </c>
@@ -4545,9 +4529,7 @@
       <c r="D152" s="2" t="n">
         <v>-2.52</v>
       </c>
-      <c r="E152" s="3" t="n">
-        <v>420</v>
-      </c>
+      <c r="E152" s="3" t="inlineStr"/>
       <c r="F152" s="3" t="n">
         <v>454</v>
       </c>
@@ -4653,9 +4635,7 @@
       <c r="D156" s="2" t="n">
         <v>-4.14</v>
       </c>
-      <c r="E156" s="3" t="n">
-        <v>149</v>
-      </c>
+      <c r="E156" s="3" t="inlineStr"/>
       <c r="F156" s="3" t="n">
         <v>173</v>
       </c>
@@ -4707,9 +4687,7 @@
       <c r="D158" s="2" t="n">
         <v>-5.1</v>
       </c>
-      <c r="E158" s="3" t="n">
-        <v>346</v>
-      </c>
+      <c r="E158" s="3" t="inlineStr"/>
       <c r="F158" s="3" t="n">
         <v>346</v>
       </c>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1764,7 +1764,9 @@
       <c r="D49" s="2" t="n">
         <v>11.94</v>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="n">
+        <v>135</v>
+      </c>
       <c r="F49" s="3" t="n">
         <v>156</v>
       </c>
@@ -2261,493 +2263,493 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>11.4</v>
+        <v>25.18</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.33</v>
+        <v>9.35</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>422</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>11</v>
+        <v>22.73</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>28.09</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>22.69</v>
+        <v>28.09</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1085</v>
+        <v>177</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1325</v>
+        <v>228</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>15.2</v>
+        <v>22.69</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>8.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>364</v>
+        <v>1085</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>394</v>
+        <v>1325</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>372</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>18.46</v>
+        <v>15.2</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>141</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>14.29</v>
+        <v>24.57</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>112</v>
+        <v>2600</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>128</v>
+        <v>3600</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>121</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>10.11</v>
+        <v>14.29</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>7.98</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>945</v>
+        <v>112</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1035</v>
+        <v>128</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1015</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>23.46</v>
+        <v>16.35</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>10.05</v>
+        <v>13.38</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>372</v>
+        <v>4410</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>416</v>
+        <v>5000</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>406</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>14</v>
+        <v>10.05</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>17.44</v>
+        <v>22.86</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>19.4</v>
+        <v>14</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>480</v>
+        <v>114</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>430</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2756,52 +2758,52 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>24.86</v>
+        <v>17.44</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2260</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1935</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22.32</v>
+        <v>19.4</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6.87</v>
+        <v>6.97</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>498</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2810,187 +2812,187 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>15.53</v>
+        <v>24.86</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>103</v>
+        <v>2260</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>110</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>16</v>
+        <v>22.32</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>87</v>
+        <v>570</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>23.33</v>
+        <v>15.53</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="E90" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="F90" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>148</v>
-      </c>
       <c r="G90" s="3" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>17.46</v>
+        <v>16</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>11.47</v>
+        <v>23.33</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>6.18</v>
+        <v>6.67</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>3460</v>
+        <v>119</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3610</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>16.67</v>
+        <v>17.46</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>5.83</v>
+        <v>6.35</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>605</v>
+        <v>128</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>700</v>
+        <v>148</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>635</v>
+        <v>134</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2999,52 +3001,52 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.64</v>
+        <v>16.67</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>88</v>
+        <v>605</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>98</v>
+        <v>700</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>92</v>
+        <v>635</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>19.15</v>
+        <v>25</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.67</v>
+        <v>5.77</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>705</v>
+        <v>1095</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>840</v>
+        <v>1300</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>745</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3053,50 +3055,52 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>25</v>
+        <v>12.64</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.49</v>
+        <v>5.75</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>358</v>
+        <v>88</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>346</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>19.15</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E98" s="3" t="inlineStr"/>
+        <v>5.67</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>705</v>
+      </c>
       <c r="F98" s="3" t="n">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>99</v>
+        <v>745</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3105,79 +3109,79 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>11.58</v>
+        <v>25</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5.26</v>
+        <v>5.49</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>358</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>106</v>
+        <v>410</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>10.31</v>
+        <v>19.15</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>5.15</v>
+        <v>5.32</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>14.36</v>
+        <v>11.58</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>5.13</v>
+        <v>5.26</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>390</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>410</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3186,133 +3190,133 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>11.5</v>
+        <v>10.31</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>4.87</v>
+        <v>5.15</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2330</v>
+        <v>98</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>2520</v>
+        <v>107</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>2370</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>13.33</v>
+        <v>14.36</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>4.71</v>
+        <v>5.13</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2750</v>
+        <v>390</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>2890</v>
+        <v>446</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2670</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>11.63</v>
+        <v>11.5</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>87</v>
+        <v>2330</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>96</v>
+        <v>2520</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>90</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>10.6</v>
+        <v>13.33</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2750</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>167</v>
+        <v>2890</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>158</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3321,96 +3325,100 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>20.56</v>
+        <v>19.77</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E108" s="3" t="inlineStr"/>
+        <v>4.52</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>177</v>
+      </c>
       <c r="F108" s="3" t="n">
-        <v>2140</v>
+        <v>212</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1850</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>15</v>
+        <v>13.04</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E109" s="3" t="inlineStr"/>
+        <v>4.35</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>236.5864082336426</v>
+      </c>
       <c r="F109" s="3" t="n">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>104</v>
+        <v>240</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>15.09</v>
+        <v>20.56</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>159</v>
+        <v>1980</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>183</v>
+        <v>2140</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>165</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="111">
@@ -3421,29 +3429,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>12.69</v>
+        <v>15</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,25 +3460,25 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>11.97</v>
+        <v>15.09</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,25 +3487,25 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>12.45</v>
+        <v>12.69</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.41</v>
+        <v>3.73</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>545</v>
+        <v>136</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>560</v>
+        <v>151</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>515</v>
+        <v>139</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,376 +3514,376 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>17.21</v>
+        <v>11.97</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>615</v>
+        <v>118</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>715</v>
+        <v>131</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>630</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>23.66</v>
+        <v>12.45</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>380</v>
+        <v>545</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>384</v>
+        <v>515</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>11.83</v>
+        <v>17.21</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>95</v>
+        <v>615</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>104</v>
+        <v>715</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>96</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>30.95</v>
+        <v>11.83</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>11.63</v>
+        <v>30.95</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>12.15</v>
+        <v>34.34</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11.89</v>
+        <v>11.41</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>288</v>
+        <v>2080</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>320</v>
+        <v>2100</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>294</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>16.7</v>
+        <v>11.63</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>5200</v>
+        <v>174</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>5450</v>
+        <v>192</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>4800</v>
+        <v>177</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>14.62</v>
+        <v>11.57</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>2550</v>
+        <v>1210</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>2900</v>
+        <v>1350</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>2600</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>17.95</v>
+        <v>11.89</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>92</v>
+        <v>320</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>80</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>17.44</v>
+        <v>16.7</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>87</v>
+        <v>5200</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>101</v>
+        <v>5450</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>88</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>12.36</v>
+        <v>14.62</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>89</v>
+        <v>2550</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>91</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,102 +3892,106 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11.75</v>
+        <v>10.16</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>3380</v>
+        <v>172</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>3900</v>
+        <v>206</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>3560</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>25</v>
+        <v>17.95</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>14.29</v>
+        <v>17.44</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E130" s="3" t="inlineStr"/>
+        <v>2.33</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="F130" s="3" t="n">
-        <v>2320</v>
+        <v>101</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>2070</v>
+        <v>88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>11.54</v>
+        <v>12.36</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E131" s="3" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="F131" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>2120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3988,52 +4000,52 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>10.34</v>
+        <v>11.75</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>348</v>
+        <v>3380</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>384</v>
+        <v>3900</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>354</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>11.83</v>
+        <v>25</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4042,586 +4054,592 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>19.87</v>
+        <v>14.29</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E134" s="3" t="inlineStr"/>
+        <v>1.97</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>2140</v>
+      </c>
       <c r="F134" s="3" t="n">
-        <v>9350</v>
+        <v>2320</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>7900</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>15.38</v>
+        <v>11.54</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>79</v>
+        <v>2100</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>79</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>15.94</v>
+        <v>10.34</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E136" s="3" t="inlineStr"/>
+        <v>1.72</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>348</v>
+      </c>
       <c r="F136" s="3" t="n">
-        <v>16000</v>
+        <v>384</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>13975</v>
+        <v>354</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>10.59</v>
+        <v>11.83</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>94</v>
+        <v>208</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>13.64</v>
+        <v>15.38</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>10.68</v>
+        <v>15.94</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>210</v>
+        <v>13800</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>228</v>
+        <v>16000</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>208</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>22.58</v>
+        <v>10.59</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.54</v>
+        <v>1.18</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>1910</v>
+        <v>89</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>2280</v>
+        <v>94</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>1870</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>10.76</v>
+        <v>21.97</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>865</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>3500</v>
+        <v>1055</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>3160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>17.5</v>
+        <v>13.64</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>12.87</v>
+        <v>10.68</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>101</v>
+        <v>208</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>28.48</v>
+        <v>22.58</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>152</v>
+        <v>1910</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>194</v>
+        <v>2280</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>151</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>14.43</v>
+        <v>28.48</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>2020</v>
+        <v>152</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>2220</v>
+        <v>194</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1930</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>18.04</v>
+        <v>17.5</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>163</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>332.87</v>
+        <v>188</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>29.27</v>
+        <v>10.76</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>85</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>106</v>
+        <v>3500</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>81</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>10.17</v>
+        <v>12.87</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>2400</v>
+        <v>93</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>2600</v>
+        <v>114</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>2330</v>
+        <v>101</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>16.02</v>
+        <v>14.43</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.52</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>181</v>
+        <v>2020</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>210</v>
+        <v>2220</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>177</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>10.49</v>
+        <v>18.04</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>-2.47</v>
+        <v>-0.71</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>322</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>358</v>
+        <v>332.87</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>316</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>11.19</v>
+        <v>29.27</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="E152" s="3" t="inlineStr"/>
+        <v>-1.22</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="F152" s="3" t="n">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>398</v>
+        <v>81</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>15.31</v>
+        <v>10.17</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.27</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>169</v>
+        <v>2400</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>226</v>
+        <v>2600</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>191</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>10.1</v>
+        <v>16.02</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.21</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>10300</v>
+        <v>181</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>10900</v>
+        <v>210</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>9600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>10.65</v>
+        <v>10.49</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.47</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>458</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>478</v>
+        <v>358</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>418</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4630,345 +4648,349 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>19.31</v>
+        <v>11.19</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="E156" s="3" t="inlineStr"/>
+        <v>-2.52</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>420</v>
+      </c>
       <c r="F156" s="3" t="n">
-        <v>173</v>
+        <v>454</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>139</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>11.11</v>
+        <v>15.31</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>-4.94</v>
+        <v>-2.55</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>77</v>
+        <v>191</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>10.19</v>
+        <v>10.1</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="E158" s="3" t="inlineStr"/>
+        <v>-3.03</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>10300</v>
+      </c>
       <c r="F158" s="3" t="n">
-        <v>346</v>
+        <v>10900</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>298</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>23.53</v>
+        <v>10.65</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.24</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>700</v>
+        <v>458</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>840</v>
+        <v>478</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>645</v>
+        <v>418</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>13.58</v>
+        <v>19.31</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>10.5</v>
+        <v>11.11</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.94</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>1175</v>
+        <v>83</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1210</v>
+        <v>90</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>1025</v>
+        <v>77</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>16.8</v>
+        <v>10.19</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-6.8</v>
+        <v>-5.1</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2500</v>
+        <v>346</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2920</v>
+        <v>346</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2330</v>
+        <v>298</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>10.67</v>
+        <v>23.53</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.15</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>152</v>
+        <v>700</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>166</v>
+        <v>840</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>139</v>
+        <v>645</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>15.79</v>
+        <v>13.58</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.56</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>835</v>
+        <v>162</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>880</v>
+        <v>184</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>700</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>20.41</v>
+        <v>10.5</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-8.16</v>
+        <v>-6.39</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>100</v>
+        <v>1175</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>118</v>
+        <v>1210</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>90</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>12.73</v>
+        <v>16.8</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-8.18</v>
+        <v>-6.8</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>240</v>
+        <v>2500</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>248</v>
+        <v>2920</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>202</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>24.62</v>
+        <v>10.67</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-7.33</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>1600</v>
+        <v>152</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>1620</v>
+        <v>166</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>21.43</v>
+        <v>15.79</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-8.57</v>
+        <v>-7.89</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>83</v>
+        <v>835</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>85</v>
+        <v>880</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>64</v>
+        <v>700</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4977,450 +4999,558 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>18.95</v>
+        <v>20.41</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-8.77</v>
+        <v>-8.16</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>8475</v>
+        <v>100</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>8475</v>
+        <v>118</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>6500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>20.81</v>
+        <v>12.73</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.18</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>432</v>
+        <v>240</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>505</v>
+        <v>248</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>380</v>
+        <v>202</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>16.35</v>
+        <v>24.62</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>91</v>
+        <v>1600</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>91</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>30.37</v>
+        <v>21.43</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.57</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>16.36</v>
+        <v>18.95</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.77</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>175</v>
+        <v>8475</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>192</v>
+        <v>8475</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>141</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>15.1</v>
+        <v>20.81</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-14.58</v>
+        <v>-9.09</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>12.36</v>
+        <v>16.35</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-14.61</v>
+        <v>-12.5</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>860</v>
+        <v>91</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>1000</v>
+        <v>121</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>760</v>
+        <v>91</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>18.87</v>
+        <v>30.37</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-14.62</v>
+        <v>-14.07</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>218</v>
+        <v>142</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>16.38</v>
+        <v>16.36</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.55</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>175</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>396</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>19.27</v>
+        <v>15.1</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.58</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>222</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>260</v>
+        <v>442</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>186</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>17.21</v>
+        <v>12.36</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.61</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>132</v>
+        <v>860</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>143</v>
+        <v>1000</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>104</v>
+        <v>760</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>11.83</v>
+        <v>18.87</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.62</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>218</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>378</v>
+        <v>252</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>288</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>20.37</v>
+        <v>16.38</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.66</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>220</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>184</v>
+        <v>396</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>15.94</v>
+        <v>19.27</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.68</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2760</v>
+        <v>222</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>3200</v>
+        <v>260</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2350</v>
+        <v>186</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>25</v>
+        <v>17.21</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.75</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>14.05</v>
+        <v>11.83</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.79</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>115</v>
+        <v>316.9231611887614</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>138</v>
+        <v>378</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>103</v>
+        <v>288</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C189" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D185" s="2" t="n">
+      <c r="D189" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E185" s="3" t="n">
+      <c r="E189" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F185" s="3" t="n">
+      <c r="F189" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G185" s="3" t="n">
+      <c r="G189" s="3" t="n">
         <v>120</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1345,34 +1345,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1381,538 +1381,538 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>446</v>
+        <v>115</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>12.78</v>
+        <v>14.88</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>12.78</v>
+        <v>13.69</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>358</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>406</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>14.49</v>
+        <v>14.46</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>138</v>
+        <v>496</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>155</v>
+        <v>560</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>12.73</v>
+        <v>14.49</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>138</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>370</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>30.41</v>
+        <v>11.61</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11.49</v>
+        <v>11.61</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>16.39</v>
+        <v>30.41</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1921,127 +1921,127 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30.34</v>
+        <v>22.5</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>14.73</v>
+        <v>30.34</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.11</v>
+        <v>11.24</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1955</v>
+        <v>93</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2220</v>
+        <v>116</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>12.67</v>
+        <v>14.73</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1690</v>
+        <v>2220</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1665</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>535</v>
+        <v>130</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60">
@@ -2074,61 +2074,61 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>18.18</v>
+        <v>10.38</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>91</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>104</v>
+        <v>585</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>97</v>
+        <v>585</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>10.88</v>
+        <v>18.18</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>815</v>
+        <v>104</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>810</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2137,52 +2137,52 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>14.68</v>
+        <v>10.88</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>545</v>
+        <v>770</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>625</v>
+        <v>815</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>19.77</v>
+        <v>14.68</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>212</v>
+        <v>625</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2191,478 +2191,478 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>13.04</v>
+        <v>19.77</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>580</v>
+        <v>179</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>650</v>
+        <v>212</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>630</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>17.09</v>
+        <v>13.04</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9.49</v>
+        <v>9.57</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>316</v>
+        <v>580</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>346</v>
+        <v>630</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>25.18</v>
+        <v>11.72</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>11.4</v>
+        <v>25.18</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.33</v>
+        <v>9.35</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>422</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>11</v>
+        <v>22.73</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>28.09</v>
+        <v>11</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>22.69</v>
+        <v>28.09</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1085</v>
+        <v>177</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>1325</v>
+        <v>228</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>15.2</v>
+        <v>22.69</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>364</v>
+        <v>1085</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>394</v>
+        <v>1325</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>372</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>18.46</v>
+        <v>15.2</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>141</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>14.29</v>
+        <v>24.57</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>112</v>
+        <v>2600</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>128</v>
+        <v>3600</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>121</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>10.11</v>
+        <v>14.29</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.98</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>945</v>
+        <v>112</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1035</v>
+        <v>128</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1015</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>16.35</v>
+        <v>10.11</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>7.69</v>
+        <v>7.98</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>106</v>
+        <v>945</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>121</v>
+        <v>1035</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>112</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>13.38</v>
+        <v>16.35</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7.48</v>
+        <v>7.69</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>4410</v>
+        <v>106</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>5000</v>
+        <v>121</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>4740</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>23.46</v>
+        <v>13.38</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>161</v>
+        <v>4410</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>174</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="83">
@@ -2695,217 +2695,217 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>14</v>
+        <v>22.86</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>17.44</v>
+        <v>14</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6.98</v>
+        <v>7</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>101</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>19.4</v>
+        <v>17.44</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6.97</v>
+        <v>6.98</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>408</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>480</v>
+        <v>101</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>430</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>24.86</v>
+        <v>19.4</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.91</v>
+        <v>6.97</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2260</v>
+        <v>408</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2260</v>
+        <v>480</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>1935</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>22.32</v>
+        <v>24.86</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>6.87</v>
+        <v>6.91</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>490</v>
+        <v>2260</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>570</v>
+        <v>2260</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>498</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>15.53</v>
+        <v>22.32</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.8</v>
+        <v>6.87</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>103</v>
+        <v>490</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>119</v>
+        <v>570</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>110</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>16</v>
+        <v>15.53</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92">
@@ -2938,115 +2938,115 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>17.46</v>
+        <v>16</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>605</v>
+        <v>66</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3055,52 +3055,52 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>12.64</v>
+        <v>16.67</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>88</v>
+        <v>605</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>98</v>
+        <v>700</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>92</v>
+        <v>635</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>19.15</v>
+        <v>25</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>5.67</v>
+        <v>5.77</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>705</v>
+        <v>1095</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>840</v>
+        <v>1300</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>745</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3109,52 +3109,52 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>25</v>
+        <v>12.64</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5.49</v>
+        <v>5.75</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>358</v>
+        <v>88</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>346</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>19.15</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>5.32</v>
+        <v>5.67</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>103</v>
+        <v>705</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>99</v>
+        <v>745</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3163,79 +3163,79 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>11.58</v>
+        <v>25</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>5.26</v>
+        <v>5.49</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>358</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>106</v>
+        <v>410</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>10.31</v>
+        <v>19.15</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>5.15</v>
+        <v>5.32</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>14.36</v>
+        <v>11.58</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5.13</v>
+        <v>5.26</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>390</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>410</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3244,133 +3244,133 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>11.5</v>
+        <v>10.31</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>4.87</v>
+        <v>5.15</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2330</v>
+        <v>98</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>2520</v>
+        <v>107</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>2370</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>13.33</v>
+        <v>14.36</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>4.71</v>
+        <v>5.13</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>2750</v>
+        <v>390</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>2890</v>
+        <v>446</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2670</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>11.63</v>
+        <v>11.5</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>87</v>
+        <v>2330</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>96</v>
+        <v>2520</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>90</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>10.6</v>
+        <v>13.33</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>4.64</v>
+        <v>4.71</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2750</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>167</v>
+        <v>2890</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>158</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3379,430 +3379,430 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>23.66</v>
+        <v>12.45</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>545</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>384</v>
+        <v>515</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11.41</v>
+        <v>11.83</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>2080</v>
+        <v>95</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>2100</v>
+        <v>104</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>1940</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>11.63</v>
+        <v>30.95</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>11.57</v>
+        <v>34.34</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>1210</v>
+        <v>133</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1350</v>
+        <v>133</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>1245</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>12.15</v>
+        <v>11.41</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>109</v>
+        <v>2080</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>110</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3811,52 +3811,52 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>11.89</v>
+        <v>11.63</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>320</v>
+        <v>192</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>294</v>
+        <v>177</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3865,79 +3865,79 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>14.62</v>
+        <v>11.89</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>2550</v>
+        <v>288</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>2900</v>
+        <v>320</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>2600</v>
+        <v>294</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3946,79 +3946,79 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>3380</v>
+        <v>79</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4027,79 +4027,79 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>2140</v>
+        <v>89</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4108,52 +4108,52 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>11.83</v>
+        <v>14.29</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>187</v>
+        <v>2140</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>189</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4162,1395 +4162,1503 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>19.87</v>
+        <v>11.54</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>8125</v>
+        <v>2100</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>9350</v>
+        <v>2320</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>7900</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>15.38</v>
+        <v>10.34</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>90</v>
+        <v>384</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>79</v>
+        <v>354</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>15.94</v>
+        <v>11.83</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>13800</v>
+        <v>187</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>16000</v>
+        <v>208</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>13975</v>
+        <v>189</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>10.59</v>
+        <v>15.38</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>13.64</v>
+        <v>15.94</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>88</v>
+        <v>13800</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>100</v>
+        <v>16000</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>89</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>208</v>
+        <v>86</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>28.48</v>
+        <v>13.64</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>151</v>
+        <v>89</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>17.5</v>
+        <v>10.68</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>10.76</v>
+        <v>22.58</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>1910</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>3500</v>
+        <v>2280</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>3160</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>12.87</v>
+        <v>28.48</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>101</v>
+        <v>151</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>14.43</v>
+        <v>10.76</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>2020</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>2220</v>
+        <v>3500</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1930</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>18.04</v>
+        <v>17.5</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>163</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>332.87</v>
+        <v>188</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>29.27</v>
+        <v>12.87</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>10.17</v>
+        <v>14.43</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>-1.27</v>
+        <v>-0.52</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2400</v>
+        <v>2020</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2600</v>
+        <v>2220</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2330</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>16.02</v>
+        <v>18.04</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>181</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>210</v>
+        <v>332.87</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>10.49</v>
+        <v>29.27</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.22</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>85</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>316</v>
+        <v>81</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>11.19</v>
+        <v>10.17</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.27</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>420</v>
+        <v>2400</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>454</v>
+        <v>2600</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>398</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>15.31</v>
+        <v>16.02</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>-2.55</v>
+        <v>-2.21</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>10.1</v>
+        <v>10.49</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.47</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>10300</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>10900</v>
+        <v>358</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>9600</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>10.65</v>
+        <v>11.19</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.52</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>19.31</v>
+        <v>15.31</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.55</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>139</v>
+        <v>191</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>11.11</v>
+        <v>10.1</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>83</v>
+        <v>10300</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>90</v>
+        <v>10900</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>77</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>23.53</v>
+        <v>19.31</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>700</v>
+        <v>149</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>840</v>
+        <v>173</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>645</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>13.58</v>
+        <v>11.11</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.94</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>153</v>
+        <v>77</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.5</v>
+        <v>10.19</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-6.39</v>
+        <v>-5.1</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>1175</v>
+        <v>346</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>1210</v>
+        <v>346</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>1025</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>16.8</v>
+        <v>23.53</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-6.8</v>
+        <v>-5.15</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>2500</v>
+        <v>700</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2920</v>
+        <v>840</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>2330</v>
+        <v>645</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>10.67</v>
+        <v>13.58</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.56</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>15.79</v>
+        <v>10.5</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-7.89</v>
+        <v>-6.39</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>835</v>
+        <v>1175</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>880</v>
+        <v>1210</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>700</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>20.41</v>
+        <v>16.8</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-8.16</v>
+        <v>-6.8</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>118</v>
+        <v>2920</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>90</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>12.73</v>
+        <v>10.67</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-8.18</v>
+        <v>-7.33</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>240</v>
+        <v>152</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>202</v>
+        <v>139</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>24.62</v>
+        <v>15.79</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>1600</v>
+        <v>835</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>1620</v>
+        <v>880</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>1190</v>
+        <v>700</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>21.43</v>
+        <v>20.41</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-8.57</v>
+        <v>-8.16</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>18.95</v>
+        <v>12.73</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-8.77</v>
+        <v>-8.18</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>8475</v>
+        <v>240</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>8475</v>
+        <v>248</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>6500</v>
+        <v>202</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>20.81</v>
+        <v>24.62</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>432</v>
+        <v>1600</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>505</v>
+        <v>1620</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>380</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>16.35</v>
+        <v>21.43</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.57</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>30.37</v>
+        <v>18.95</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.77</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>176</v>
+        <v>8475</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>116</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>16.36</v>
+        <v>20.81</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-14.55</v>
+        <v>-9.09</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>175</v>
+        <v>432</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>141</v>
+        <v>380</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>15.1</v>
+        <v>16.35</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-14.58</v>
+        <v>-12.5</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>91</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>442</v>
+        <v>121</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>328</v>
+        <v>91</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>12.36</v>
+        <v>30.37</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-14.61</v>
+        <v>-14.07</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>860</v>
+        <v>142</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>1000</v>
+        <v>176</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>760</v>
+        <v>116</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>18.87</v>
+        <v>19.33</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-14.62</v>
+        <v>-14.29</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>252</v>
+        <v>142</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>181</v>
+        <v>102</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>16.38</v>
+        <v>16.36</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.55</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>175</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>396</v>
+        <v>141</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>19.27</v>
+        <v>15.1</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.58</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>222</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>260</v>
+        <v>442</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>186</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>17.21</v>
+        <v>12.36</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.61</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>132</v>
+        <v>860</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>143</v>
+        <v>1000</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>104</v>
+        <v>760</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>11.83</v>
+        <v>18.87</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.62</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>218</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>378</v>
+        <v>252</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>288</v>
+        <v>181</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>20.37</v>
+        <v>16.38</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.66</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>220</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>184</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>15.94</v>
+        <v>19.27</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.68</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>2760</v>
+        <v>222</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>3200</v>
+        <v>260</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>2350</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>14.05</v>
+        <v>17.21</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.75</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>25</v>
+        <v>11.83</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.79</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>165</v>
+        <v>316.9231611887614</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>210</v>
+        <v>378</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>143</v>
+        <v>288</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
+      <c r="C193" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D189" s="2" t="n">
+      <c r="D193" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E189" s="3" t="n">
+      <c r="E193" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F189" s="3" t="n">
+      <c r="F193" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G189" s="3" t="n">
+      <c r="G193" s="3" t="n">
         <v>120</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1345,61 +1345,61 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1408,457 +1408,457 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>12.78</v>
+        <v>14.88</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12.78</v>
+        <v>13.69</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>358</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>406</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>14.46</v>
+        <v>20.92</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>12.45</v>
+        <v>13.07</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>496</v>
+        <v>1525</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>570</v>
+        <v>1850</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>560</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>14.49</v>
+        <v>12.78</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>12.32</v>
+        <v>12.78</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>158</v>
+        <v>406</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>155</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>16.42</v>
+        <v>14.49</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11.94</v>
+        <v>12.32</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>19.05</v>
+        <v>12.73</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>11.9</v>
+        <v>12.12</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>86</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>94</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>11.61</v>
+        <v>16.42</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11.61</v>
+        <v>11.94</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1867,52 +1867,52 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>30.41</v>
+        <v>19.05</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11.49</v>
+        <v>11.9</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>165</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1921,916 +1921,916 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>22.48</v>
+        <v>14.73</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10.85</v>
+        <v>11.11</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>130</v>
+        <v>1955</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>158</v>
+        <v>2220</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>143</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>22.64</v>
+        <v>12.67</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>106</v>
+        <v>1515</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>130</v>
+        <v>1690</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>117</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>18.18</v>
+        <v>10.38</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>91</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>104</v>
+        <v>585</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>97</v>
+        <v>585</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>10.88</v>
+        <v>22.64</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>770</v>
+        <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>815</v>
+        <v>130</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>810</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>19.77</v>
+        <v>10.88</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>179</v>
+        <v>770</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>212</v>
+        <v>815</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>13.04</v>
+        <v>14.68</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>17.09</v>
+        <v>19.77</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>346</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>11.72</v>
+        <v>13.04</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>128</v>
+        <v>580</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>143</v>
+        <v>650</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>140</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>25.18</v>
+        <v>17.09</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.35</v>
+        <v>9.49</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>11.4</v>
+        <v>11.72</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>388</v>
+        <v>128</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>422</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>13.95</v>
+        <v>25.18</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>20500</v>
+        <v>141</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>24500</v>
+        <v>174</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>23500</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>22.73</v>
+        <v>11.4</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>216</v>
+        <v>430</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>192</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>11</v>
+        <v>13.95</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>104</v>
+        <v>20500</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>111</v>
+        <v>24500</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>109</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>28.09</v>
+        <v>22.73</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22.69</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1085</v>
+        <v>104</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1325</v>
+        <v>111</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>15.2</v>
+        <v>28.09</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8.77</v>
+        <v>8.99</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>364</v>
+        <v>177</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>372</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>24.57</v>
+        <v>15.2</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2600</v>
+        <v>364</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>3600</v>
+        <v>394</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>3130</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>10.11</v>
+        <v>24.57</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>7.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>945</v>
+        <v>2600</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1035</v>
+        <v>3600</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1015</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F81" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G81" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>23.46</v>
+        <v>13.38</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>161</v>
+        <v>4410</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>174</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>14</v>
+        <v>23.46</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>107</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>17.44</v>
+        <v>22.86</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>140</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>19.4</v>
+        <v>14</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>480</v>
+        <v>114</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>430</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2839,52 +2839,52 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>24.86</v>
+        <v>17.44</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2260</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1935</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>22.32</v>
+        <v>19.4</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.87</v>
+        <v>6.97</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>498</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2893,565 +2893,565 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>15.53</v>
+        <v>24.86</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>103</v>
+        <v>2260</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>110</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>23.33</v>
+        <v>22.32</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>128</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>16</v>
+        <v>15.53</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>17.46</v>
+        <v>23.33</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F94" s="3" t="n">
         <v>148</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F95" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G95" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>5.77</v>
+        <v>6.25</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1095</v>
+        <v>66</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1300</v>
+        <v>80</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>12.64</v>
+        <v>11.47</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5.75</v>
+        <v>6.18</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>88</v>
+        <v>3460</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>98</v>
+        <v>3790</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>92</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>4.65</v>
+        <v>5.13</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>87</v>
+        <v>390</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3460,619 +3460,619 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>23.66</v>
+        <v>11.97</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>118</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>460</v>
+        <v>131</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11.83</v>
+        <v>12.45</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>95</v>
+        <v>545</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>104</v>
+        <v>560</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>96</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>34.34</v>
+        <v>11.83</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>11.41</v>
+        <v>23.66</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>2080</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>2100</v>
+        <v>460</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>1940</v>
+        <v>384</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>11.63</v>
+        <v>30.95</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>11.57</v>
+        <v>34.34</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>1210</v>
+        <v>133</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>1350</v>
+        <v>133</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>1245</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>11.89</v>
+        <v>14.71</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>320</v>
+        <v>78</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>294</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>12.15</v>
+        <v>11.41</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>109</v>
+        <v>2080</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>110</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>16.7</v>
+        <v>11.63</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>5200</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>5450</v>
+        <v>192</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>4800</v>
+        <v>177</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>14.62</v>
+        <v>11.57</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>2550</v>
+        <v>1210</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>2900</v>
+        <v>1350</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>2600</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>17.95</v>
+        <v>11.89</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>92</v>
+        <v>320</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>80</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>17.44</v>
+        <v>16.7</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>87</v>
+        <v>5200</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>101</v>
+        <v>5450</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>88</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>12.36</v>
+        <v>14.62</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>89</v>
+        <v>2550</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>91</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4081,106 +4081,106 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>11.75</v>
+        <v>10.16</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>172</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>3900</v>
+        <v>206</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>3560</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>25</v>
+        <v>17.95</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>14.29</v>
+        <v>17.44</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>2140</v>
+        <v>87</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>2320</v>
+        <v>101</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>2070</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>11.54</v>
+        <v>12.36</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>2100</v>
+        <v>89</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>2120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4189,79 +4189,79 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>10.34</v>
+        <v>11.75</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>348</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>384</v>
+        <v>3900</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>354</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>11.83</v>
+        <v>25</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>79</v>
+        <v>2140</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>79</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4270,160 +4270,160 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>19.87</v>
+        <v>11.54</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>8125</v>
+        <v>2100</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>9350</v>
+        <v>2320</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>7900</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>15.94</v>
+        <v>10.34</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>13800</v>
+        <v>348</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>16000</v>
+        <v>384</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>13975</v>
+        <v>354</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>10.59</v>
+        <v>11.41</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>89</v>
+        <v>1490</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>94</v>
+        <v>1660</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>86</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>21.97</v>
+        <v>11.83</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>865</v>
+        <v>187</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1055</v>
+        <v>208</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>875</v>
+        <v>189</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>13.64</v>
+        <v>18.31</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>88</v>
+        <v>710</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>100</v>
+        <v>840</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>89</v>
+        <v>720</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>10.68</v>
+        <v>19.87</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.97</v>
+        <v>1.28</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>210</v>
+        <v>8125</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>228</v>
+        <v>9350</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>208</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4432,241 +4432,241 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>22.58</v>
+        <v>15.38</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>1910</v>
+        <v>79</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>2280</v>
+        <v>90</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>1870</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>28.48</v>
+        <v>15.94</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>152</v>
+        <v>13800</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>194</v>
+        <v>16000</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>151</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>10.76</v>
+        <v>10.59</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>89</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>3500</v>
+        <v>94</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>3160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>17.5</v>
+        <v>21.97</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>163</v>
+        <v>865</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>188</v>
+        <v>1055</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>12.87</v>
+        <v>13.64</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>14.43</v>
+        <v>10.68</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>-0.52</v>
+        <v>0.97</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2020</v>
+        <v>210</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2220</v>
+        <v>228</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1930</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>18.04</v>
+        <v>22.58</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>-0.71</v>
+        <v>0.54</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>1910</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>332.87</v>
+        <v>2280</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>280</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>29.27</v>
+        <v>12.87</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>10.17</v>
+        <v>17.5</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>2400</v>
+        <v>163</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2600</v>
+        <v>188</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2330</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4675,214 +4675,214 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>16.02</v>
+        <v>28.48</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>-2.21</v>
+        <v>0</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>10.49</v>
+        <v>10.76</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>-2.47</v>
+        <v>0</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>358</v>
+        <v>3500</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>316</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>11.19</v>
+        <v>14.43</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>-2.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>420</v>
+        <v>2020</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>454</v>
+        <v>2220</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>398</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>15.31</v>
+        <v>18.04</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>-2.55</v>
+        <v>-0.71</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>169</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>226</v>
+        <v>332.87</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>191</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>10.1</v>
+        <v>29.27</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.22</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>10300</v>
+        <v>85</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>10900</v>
+        <v>106</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>9600</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>10.65</v>
+        <v>10.17</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-3.24</v>
+        <v>-1.27</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>458</v>
+        <v>2400</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>478</v>
+        <v>2600</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>418</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>19.31</v>
+        <v>16.02</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.21</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>139</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>11.11</v>
+        <v>10.49</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-4.94</v>
+        <v>-2.47</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>83</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>90</v>
+        <v>358</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>77</v>
+        <v>316</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4891,268 +4891,268 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.19</v>
+        <v>11.19</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-5.1</v>
+        <v>-2.52</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>346</v>
+        <v>420</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>298</v>
+        <v>398</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>23.53</v>
+        <v>15.31</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-5.15</v>
+        <v>-2.55</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>700</v>
+        <v>169</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>840</v>
+        <v>226</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>645</v>
+        <v>191</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>13.58</v>
+        <v>10.1</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-5.56</v>
+        <v>-3.03</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>162</v>
+        <v>10300</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>184</v>
+        <v>10900</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>153</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>10.5</v>
+        <v>10.65</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-6.39</v>
+        <v>-3.24</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1175</v>
+        <v>458</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1210</v>
+        <v>478</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>1025</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>16.8</v>
+        <v>19.31</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.14</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2500</v>
+        <v>149</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2920</v>
+        <v>173</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2330</v>
+        <v>139</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>10.67</v>
+        <v>11.11</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-7.33</v>
+        <v>-4.94</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>15.79</v>
+        <v>10.19</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.1</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>835</v>
+        <v>346</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>880</v>
+        <v>346</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>700</v>
+        <v>298</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>20.41</v>
+        <v>23.53</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.15</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>118</v>
+        <v>840</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>90</v>
+        <v>645</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>12.73</v>
+        <v>13.58</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.56</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>24.62</v>
+        <v>10.5</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.39</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>1600</v>
+        <v>1175</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>1620</v>
+        <v>1210</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>1190</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5161,504 +5161,666 @@
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>21.43</v>
+        <v>16.8</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.8</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>83</v>
+        <v>2500</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>85</v>
+        <v>2920</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>64</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>18.95</v>
+        <v>10.67</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-8.77</v>
+        <v>-7.33</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>8475</v>
+        <v>152</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>8475</v>
+        <v>166</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>6500</v>
+        <v>139</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>20.81</v>
+        <v>15.79</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-9.09</v>
+        <v>-7.89</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>432</v>
+        <v>835</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>505</v>
+        <v>880</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>380</v>
+        <v>700</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>16.35</v>
+        <v>20.41</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.16</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>30.37</v>
+        <v>12.73</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.18</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>116</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>19.33</v>
+        <v>24.62</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>127</v>
+        <v>1600</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>142</v>
+        <v>1620</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>102</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>16.36</v>
+        <v>21.43</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.57</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>141</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>15.1</v>
+        <v>18.95</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.77</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>8475</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>442</v>
+        <v>8475</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>328</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>12.36</v>
+        <v>20.81</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-14.61</v>
+        <v>-9.09</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>860</v>
+        <v>432</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1000</v>
+        <v>505</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>760</v>
+        <v>380</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>18.87</v>
+        <v>16.35</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.5</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>16.38</v>
+        <v>30.37</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.07</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>142</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>17.21</v>
+        <v>16.36</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.55</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>11.83</v>
+        <v>15.1</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.58</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>378</v>
+        <v>442</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>288</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>20.37</v>
+        <v>12.36</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.61</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>220</v>
+        <v>860</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>184</v>
+        <v>760</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>15.94</v>
+        <v>18.87</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.62</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>2760</v>
+        <v>218</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>3200</v>
+        <v>252</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>2350</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>14.05</v>
+        <v>16.38</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.66</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>115</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>138</v>
+        <v>540</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>103</v>
+        <v>396</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>25</v>
+        <v>19.27</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
+      <c r="C199" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D193" s="2" t="n">
+      <c r="D199" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E193" s="3" t="n">
+      <c r="E199" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F193" s="3" t="n">
+      <c r="F199" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G193" s="3" t="n">
+      <c r="G199" s="3" t="n">
         <v>120</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -994,439 +994,439 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>20.2</v>
+        <v>24.86</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1535</v>
+        <v>1685</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1845</v>
+        <v>2160</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1845</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>6550</v>
+        <v>1535</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12125</v>
+        <v>6550</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5950</v>
+        <v>12125</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6300</v>
+        <v>5950</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>24.7</v>
+        <v>19.68</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.52</v>
+        <v>19.68</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1565</v>
+        <v>6300</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1565</v>
+        <v>7450</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1500</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>33.79</v>
+        <v>24.7</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>18.62</v>
+        <v>19.52</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>149</v>
+        <v>1565</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>194</v>
+        <v>1565</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>172</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>21.31</v>
+        <v>34.19</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17.21</v>
+        <v>17.95</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>635</v>
+        <v>126</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>740</v>
+        <v>157</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>715</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1435,565 +1435,565 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>20.92</v>
+        <v>14.88</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>1525</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1850</v>
+        <v>386</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1730</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>12.78</v>
+        <v>20.92</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>358</v>
+        <v>1525</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>406</v>
+        <v>1850</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>406</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>14.49</v>
+        <v>14.46</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>138</v>
+        <v>496</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>155</v>
+        <v>560</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>12.73</v>
+        <v>14.49</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>138</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>370</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30.41</v>
+        <v>11.61</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.49</v>
+        <v>11.61</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>16.39</v>
+        <v>30.41</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2002,214 +2002,214 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>30.34</v>
+        <v>22.5</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>14.73</v>
+        <v>30.34</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.11</v>
+        <v>11.24</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1955</v>
+        <v>93</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2220</v>
+        <v>116</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>12.67</v>
+        <v>14.73</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1690</v>
+        <v>2220</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1665</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>22.64</v>
+        <v>10.38</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>106</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>130</v>
+        <v>585</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>117</v>
+        <v>585</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>10.88</v>
+        <v>18.18</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>815</v>
+        <v>104</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>810</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2218,52 +2218,52 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>14.68</v>
+        <v>10.88</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>545</v>
+        <v>770</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>625</v>
+        <v>815</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>19.77</v>
+        <v>14.68</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>212</v>
+        <v>625</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2272,1267 +2272,1267 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>13.04</v>
+        <v>19.77</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>580</v>
+        <v>179</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>650</v>
+        <v>212</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>630</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>17.09</v>
+        <v>13.04</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.49</v>
+        <v>9.57</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>316</v>
+        <v>580</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>346</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>25.18</v>
+        <v>11.72</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>11.4</v>
+        <v>25.18</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9.33</v>
+        <v>9.35</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>422</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>11</v>
+        <v>22.73</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>28.09</v>
+        <v>11</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>22.69</v>
+        <v>28.09</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1085</v>
+        <v>177</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1325</v>
+        <v>228</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>15.2</v>
+        <v>22.69</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>8.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>364</v>
+        <v>1085</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>394</v>
+        <v>1325</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>372</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>18.46</v>
+        <v>15.2</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>141</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>14.29</v>
+        <v>10.19</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>10.11</v>
+        <v>24.57</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>945</v>
+        <v>2600</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1035</v>
+        <v>3600</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1015</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F83" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G83" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>23.46</v>
+        <v>13.38</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>161</v>
+        <v>4410</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>174</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>14</v>
+        <v>10.05</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>17.44</v>
+        <v>11.76</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>6.98</v>
+        <v>7.35</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>68</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>19.4</v>
+        <v>22.86</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.97</v>
+        <v>7.14</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>15.53</v>
+        <v>19.4</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>6.8</v>
+        <v>6.97</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>110</v>
+        <v>430</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>23.33</v>
+        <v>24.86</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>148</v>
+        <v>2260</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>128</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>16</v>
+        <v>22.32</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>87</v>
+        <v>570</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>10.94</v>
+        <v>23.33</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F98" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G98" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>5.77</v>
+        <v>6.25</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>1095</v>
+        <v>66</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>1300</v>
+        <v>80</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>1100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>12.64</v>
+        <v>11.47</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>5.75</v>
+        <v>6.18</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>88</v>
+        <v>3460</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>98</v>
+        <v>3790</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>92</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4.65</v>
+        <v>5.13</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>87</v>
+        <v>390</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3541,457 +3541,457 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>23.66</v>
+        <v>12.45</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>545</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>384</v>
+        <v>515</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>34.34</v>
+        <v>11.83</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>14.71</v>
+        <v>23.66</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>70</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>70</v>
+        <v>384</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>12.15</v>
+        <v>11.41</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>109</v>
+        <v>2080</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>110</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4000,52 +4000,52 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>11.89</v>
+        <v>11.63</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>288</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>320</v>
+        <v>192</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>294</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4054,79 +4054,79 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>14.62</v>
+        <v>11.89</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>2550</v>
+        <v>288</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>2900</v>
+        <v>320</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>2600</v>
+        <v>294</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4135,79 +4135,79 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>79</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4216,79 +4216,79 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>2140</v>
+        <v>89</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4297,403 +4297,403 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>11.41</v>
+        <v>14.29</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>1490</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>1660</v>
+        <v>2320</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>1515</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>187</v>
+        <v>2100</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>189</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>18.31</v>
+        <v>10.34</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>710</v>
+        <v>348</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>840</v>
+        <v>384</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>720</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>19.87</v>
+        <v>11.41</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>8125</v>
+        <v>1490</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>9350</v>
+        <v>1660</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>7900</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>15.38</v>
+        <v>11.83</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>79</v>
+        <v>189</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>15.94</v>
+        <v>18.31</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>13800</v>
+        <v>710</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>16000</v>
+        <v>840</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>13975</v>
+        <v>720</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>10.59</v>
+        <v>15.38</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>13.64</v>
+        <v>15.94</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>88</v>
+        <v>13800</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>100</v>
+        <v>16000</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>89</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>208</v>
+        <v>86</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>12.87</v>
+        <v>13.64</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>17.5</v>
+        <v>10.68</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>28.48</v>
+        <v>22.58</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>152</v>
+        <v>1910</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>194</v>
+        <v>2280</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>151</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4702,997 +4702,997 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>10.76</v>
+        <v>28.48</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>152</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>3500</v>
+        <v>194</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>3160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>14.43</v>
+        <v>10.76</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2020</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2220</v>
+        <v>3500</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1930</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>18.04</v>
+        <v>17.5</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>163</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>332.87</v>
+        <v>188</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>29.27</v>
+        <v>12.87</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>10.17</v>
+        <v>14.43</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-1.27</v>
+        <v>-0.52</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2400</v>
+        <v>2020</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2600</v>
+        <v>2220</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2330</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>16.02</v>
+        <v>18.04</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>181</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>210</v>
+        <v>332.87</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>10.49</v>
+        <v>29.27</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.22</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>85</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>316</v>
+        <v>81</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>11.19</v>
+        <v>10.17</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.27</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>420</v>
+        <v>2400</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>454</v>
+        <v>2600</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>398</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>15.31</v>
+        <v>14.29</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>10.1</v>
+        <v>11.24</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.78</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>10300</v>
+        <v>169</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>10900</v>
+        <v>188</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>9600</v>
+        <v>166</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>10.65</v>
+        <v>16.02</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.21</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>458</v>
+        <v>181</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>478</v>
+        <v>210</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>418</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>19.31</v>
+        <v>10.49</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.47</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>149</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>173</v>
+        <v>358</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>139</v>
+        <v>316</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>11.11</v>
+        <v>11.19</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-4.94</v>
+        <v>-2.52</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>90</v>
+        <v>454</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>77</v>
+        <v>398</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>10.19</v>
+        <v>15.31</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-5.1</v>
+        <v>-2.55</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>346</v>
+        <v>169</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>346</v>
+        <v>226</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>23.53</v>
+        <v>17.36</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-5.15</v>
+        <v>-2.78</v>
       </c>
       <c r="E172" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="G172" s="3" t="n">
         <v>700</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>840</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>645</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>13.58</v>
+        <v>10.1</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-5.56</v>
+        <v>-3.03</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>162</v>
+        <v>10300</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>184</v>
+        <v>10900</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>153</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>10.5</v>
+        <v>10.65</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-6.39</v>
+        <v>-3.24</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>1175</v>
+        <v>458</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>1210</v>
+        <v>478</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>1025</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>16.8</v>
+        <v>19.31</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.14</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2500</v>
+        <v>149</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2920</v>
+        <v>173</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2330</v>
+        <v>139</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>10.67</v>
+        <v>13.82</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-7.33</v>
+        <v>-4.88</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>152</v>
+        <v>675</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>166</v>
+        <v>700</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>139</v>
+        <v>585</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>15.79</v>
+        <v>11.11</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-7.89</v>
+        <v>-4.94</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>835</v>
+        <v>83</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>880</v>
+        <v>90</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>700</v>
+        <v>77</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>20.41</v>
+        <v>10.19</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.1</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>118</v>
+        <v>346</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>90</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>12.73</v>
+        <v>23.53</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.15</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>248</v>
+        <v>840</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>202</v>
+        <v>645</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>24.62</v>
+        <v>13.58</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-5.56</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>1600</v>
+        <v>162</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>1620</v>
+        <v>184</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>1190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>21.43</v>
+        <v>10.5</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.39</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>83</v>
+        <v>1175</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>85</v>
+        <v>1210</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>64</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>18.95</v>
+        <v>16.8</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-8.77</v>
+        <v>-6.8</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>8475</v>
+        <v>2500</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>8475</v>
+        <v>2920</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>6500</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>20.81</v>
+        <v>10.67</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-9.09</v>
+        <v>-7.33</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>432</v>
+        <v>152</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>505</v>
+        <v>166</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>380</v>
+        <v>139</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>16.35</v>
+        <v>15.79</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-12.5</v>
+        <v>-7.89</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>91</v>
+        <v>835</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>121</v>
+        <v>880</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>30.37</v>
+        <v>20.41</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.16</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>19.33</v>
+        <v>12.73</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.18</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>102</v>
+        <v>202</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>16.36</v>
+        <v>24.62</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>175</v>
+        <v>1600</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>192</v>
+        <v>1620</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>141</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>15.1</v>
+        <v>21.43</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.57</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>83</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>328</v>
+        <v>64</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>12.36</v>
+        <v>18.95</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-14.61</v>
+        <v>-8.77</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>860</v>
+        <v>8475</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>1000</v>
+        <v>8475</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>760</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>18.87</v>
+        <v>20.81</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-14.62</v>
+        <v>-9.09</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>218</v>
+        <v>432</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>252</v>
+        <v>505</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>181</v>
+        <v>380</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>16.38</v>
+        <v>16.35</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-14.66</v>
+        <v>-12.5</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>91</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>540</v>
+        <v>121</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>396</v>
+        <v>91</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>19.27</v>
+        <v>30.37</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.07</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>260</v>
+        <v>176</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>17.21</v>
+        <v>19.33</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.29</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>11.83</v>
+        <v>16.36</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.55</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>175</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>378</v>
+        <v>192</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>288</v>
+        <v>141</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5701,126 +5701,342 @@
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>20.37</v>
+        <v>15.1</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.58</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>220</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>260</v>
+        <v>442</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>184</v>
+        <v>328</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>15.94</v>
+        <v>12.36</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.61</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>2760</v>
+        <v>860</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>2350</v>
+        <v>760</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>25</v>
+        <v>18.87</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.62</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>14.05</v>
+        <v>16.38</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.66</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>115</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>138</v>
+        <v>540</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>103</v>
+        <v>396</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>NZIA.JK</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>YUPI.JK</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="C207" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D199" s="2" t="n">
+      <c r="D207" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E199" s="3" t="n">
+      <c r="E207" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F199" s="3" t="n">
+      <c r="F207" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G199" s="3" t="n">
+      <c r="G207" s="3" t="n">
         <v>120</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -562,55 +562,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>860</v>
+        <v>119</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>119</v>
+        <v>860</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>155</v>
+        <v>975</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>145</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
@@ -1183,277 +1183,277 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>33.79</v>
+        <v>24.57</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>18.62</v>
+        <v>19.43</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>149</v>
+        <v>430</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>172</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>21.31</v>
+        <v>34.19</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>17.21</v>
+        <v>17.95</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>635</v>
+        <v>126</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>740</v>
+        <v>157</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>715</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1462,484 +1462,484 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>20.92</v>
+        <v>14.88</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1525</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1850</v>
+        <v>386</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1730</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>12.78</v>
+        <v>17.27</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>12.78</v>
+        <v>13.64</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>358</v>
+        <v>550</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>406</v>
+        <v>645</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>406</v>
+        <v>625</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>14.46</v>
+        <v>20.92</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>12.45</v>
+        <v>13.07</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>496</v>
+        <v>1525</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>570</v>
+        <v>1850</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>560</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>14.49</v>
+        <v>12.78</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12.32</v>
+        <v>12.78</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>158</v>
+        <v>406</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>155</v>
+        <v>406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>16.42</v>
+        <v>14.49</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11.94</v>
+        <v>12.32</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>19.05</v>
+        <v>12.73</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11.9</v>
+        <v>12.12</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>86</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>94</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>11.61</v>
+        <v>16.42</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.61</v>
+        <v>11.94</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1948,52 +1948,52 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>30.41</v>
+        <v>19.05</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.49</v>
+        <v>11.9</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>165</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2002,268 +2002,268 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>22.48</v>
+        <v>14.73</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10.85</v>
+        <v>11.11</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>130</v>
+        <v>1955</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>158</v>
+        <v>2220</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>143</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>10.38</v>
+        <v>12.67</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>1515</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>585</v>
+        <v>1690</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>585</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>22.64</v>
+        <v>16.44</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>18.18</v>
+        <v>22.48</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10.23</v>
+        <v>10.85</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>97</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>10.88</v>
+        <v>22.64</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>770</v>
+        <v>106</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>815</v>
+        <v>130</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>810</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>14.68</v>
+        <v>10.38</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10.09</v>
+        <v>10.38</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>545</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>625</v>
+        <v>585</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2272,1348 +2272,1348 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>19.77</v>
+        <v>18.18</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9.6</v>
+        <v>10.23</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>194</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>13.04</v>
+        <v>10.88</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>9.57</v>
+        <v>10.2</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>580</v>
+        <v>770</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>650</v>
+        <v>815</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>630</v>
+        <v>810</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>17.09</v>
+        <v>14.68</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.49</v>
+        <v>10.09</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>316</v>
+        <v>545</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>370</v>
+        <v>625</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>346</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>11.72</v>
+        <v>19.77</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>25.18</v>
+        <v>13.04</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9.35</v>
+        <v>9.57</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>141</v>
+        <v>580</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>174</v>
+        <v>650</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>152</v>
+        <v>630</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>11.4</v>
+        <v>17.09</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9.33</v>
+        <v>9.49</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>422</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>13.95</v>
+        <v>11.72</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>20500</v>
+        <v>128</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>24500</v>
+        <v>143</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>23500</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22.73</v>
+        <v>25.18</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.09</v>
+        <v>9.35</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>104</v>
+        <v>388</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>111</v>
+        <v>430</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>109</v>
+        <v>422</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>28.09</v>
+        <v>13.95</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>8.99</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>177</v>
+        <v>20500</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>228</v>
+        <v>24500</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>194</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1085</v>
+        <v>176</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1325</v>
+        <v>216</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>372</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>18.46</v>
+        <v>28.09</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>141</v>
+        <v>194</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>10.19</v>
+        <v>22.69</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>8.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>109</v>
+        <v>1085</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>119</v>
+        <v>1325</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>24.57</v>
+        <v>15.2</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2600</v>
+        <v>364</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>3600</v>
+        <v>394</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3130</v>
+        <v>372</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>945</v>
+        <v>109</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1035</v>
+        <v>119</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1015</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>16.35</v>
+        <v>24.57</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>7.69</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>106</v>
+        <v>2600</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>121</v>
+        <v>3600</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>112</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>13.38</v>
+        <v>14.29</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>7.48</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>4410</v>
+        <v>112</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>5000</v>
+        <v>128</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>4740</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>23.46</v>
+        <v>10.11</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.41</v>
+        <v>7.98</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>161</v>
+        <v>945</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>200</v>
+        <v>1035</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>174</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>14</v>
+        <v>23.46</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>107</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>17.44</v>
+        <v>11.76</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>6.98</v>
+        <v>7.35</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>68</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>19.4</v>
+        <v>22.86</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>6.97</v>
+        <v>7.14</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>15.53</v>
+        <v>19.4</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>6.8</v>
+        <v>6.97</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>110</v>
+        <v>430</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>23.33</v>
+        <v>24.86</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>148</v>
+        <v>2260</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>128</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>16</v>
+        <v>22.32</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>87</v>
+        <v>570</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>10.94</v>
+        <v>23.33</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F101" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G101" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>5.77</v>
+        <v>6.25</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>1095</v>
+        <v>66</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>1300</v>
+        <v>80</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>1100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>12.64</v>
+        <v>11.47</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>5.75</v>
+        <v>6.18</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>88</v>
+        <v>3460</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>98</v>
+        <v>3790</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>92</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4.65</v>
+        <v>5.13</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>87</v>
+        <v>390</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3622,511 +3622,511 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>23.66</v>
+        <v>12.45</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>545</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>384</v>
+        <v>515</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>14.71</v>
+        <v>11.83</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>11.89</v>
+        <v>11.41</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>288</v>
+        <v>2080</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>320</v>
+        <v>2100</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>294</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>12.15</v>
+        <v>11.63</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>109</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>110</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4135,79 +4135,79 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>14.62</v>
+        <v>11.89</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>2550</v>
+        <v>288</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>2900</v>
+        <v>320</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>2600</v>
+        <v>294</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>10.16</v>
+        <v>12.15</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4216,79 +4216,79 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>79</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4297,79 +4297,79 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>89</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4378,376 +4378,376 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>11.41</v>
+        <v>14.29</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>1490</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>1660</v>
+        <v>2320</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>1515</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>187</v>
+        <v>2100</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>189</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>18.31</v>
+        <v>10.34</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>710</v>
+        <v>348</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>840</v>
+        <v>384</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>720</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>15.38</v>
+        <v>11.41</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>79</v>
+        <v>1490</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>90</v>
+        <v>1660</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>79</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>19.87</v>
+        <v>11.83</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>8125</v>
+        <v>187</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>9350</v>
+        <v>208</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>7900</v>
+        <v>189</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>15.94</v>
+        <v>18.31</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>13800</v>
+        <v>710</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>16000</v>
+        <v>840</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>13975</v>
+        <v>720</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>10.59</v>
+        <v>19.87</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>89</v>
+        <v>8125</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>94</v>
+        <v>9350</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>86</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>21.97</v>
+        <v>15.38</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>865</v>
+        <v>79</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>1055</v>
+        <v>90</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>875</v>
+        <v>79</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>13.64</v>
+        <v>15.94</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>88</v>
+        <v>13800</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>100</v>
+        <v>16000</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>89</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>208</v>
+        <v>86</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>28.48</v>
+        <v>13.64</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>151</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>10.76</v>
+        <v>10.68</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>210</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>3500</v>
+        <v>228</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>3160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4756,430 +4756,430 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>17.5</v>
+        <v>22.58</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>163</v>
+        <v>1910</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>188</v>
+        <v>2280</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>160</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>12.87</v>
+        <v>10.76</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>93</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>114</v>
+        <v>3500</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>101</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>14.43</v>
+        <v>12.78</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2020</v>
+        <v>2640</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2220</v>
+        <v>3000</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1930</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>18.04</v>
+        <v>28.48</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>152</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>332.87</v>
+        <v>194</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>280</v>
+        <v>151</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>29.27</v>
+        <v>12.87</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.17</v>
+        <v>17.5</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2400</v>
+        <v>163</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2600</v>
+        <v>188</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2330</v>
+        <v>160</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.52</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>70</v>
+        <v>2020</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>80</v>
+        <v>2220</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>69</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>11.24</v>
+        <v>18.04</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.71</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>169</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>188</v>
+        <v>332.87</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>16.02</v>
+        <v>29.27</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-2.21</v>
+        <v>-1.22</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>10.49</v>
+        <v>10.17</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.27</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>2400</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>358</v>
+        <v>2600</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>316</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>11.19</v>
+        <v>14.29</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.43</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>398</v>
+        <v>69</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>15.31</v>
+        <v>11.24</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.78</v>
       </c>
       <c r="E171" s="3" t="n">
         <v>169</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>191</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>17.36</v>
+        <v>16.02</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-2.78</v>
+        <v>-2.21</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>720</v>
+        <v>181</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>845</v>
+        <v>210</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>700</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>10.1</v>
+        <v>10.49</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.47</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>10300</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>10900</v>
+        <v>358</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>9600</v>
+        <v>316</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>10.65</v>
+        <v>11.19</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.52</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>19.31</v>
+        <v>15.31</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.55</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>139</v>
+        <v>191</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5188,349 +5188,349 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>13.82</v>
+        <v>17.36</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.78</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="F176" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="G176" s="3" t="n">
         <v>700</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>585</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>11.11</v>
+        <v>10.1</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>83</v>
+        <v>10300</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>90</v>
+        <v>10900</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>77</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>23.53</v>
+        <v>19.31</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>700</v>
+        <v>149</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>840</v>
+        <v>173</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>645</v>
+        <v>139</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>13.58</v>
+        <v>13.82</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.88</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>162</v>
+        <v>675</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>184</v>
+        <v>700</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>153</v>
+        <v>585</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>10.5</v>
+        <v>11.11</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.94</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>1175</v>
+        <v>83</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>1210</v>
+        <v>90</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1025</v>
+        <v>77</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>16.8</v>
+        <v>10.19</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-6.8</v>
+        <v>-5.1</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2500</v>
+        <v>346</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>2920</v>
+        <v>346</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2330</v>
+        <v>298</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>10.67</v>
+        <v>23.53</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.15</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>152</v>
+        <v>700</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>166</v>
+        <v>840</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>139</v>
+        <v>645</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>15.79</v>
+        <v>13.58</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.56</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>835</v>
+        <v>162</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>880</v>
+        <v>184</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>700</v>
+        <v>153</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>20.41</v>
+        <v>10.5</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-8.16</v>
+        <v>-6.39</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>100</v>
+        <v>1175</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>118</v>
+        <v>1210</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>90</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>12.73</v>
+        <v>16.8</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-8.18</v>
+        <v>-6.8</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>240</v>
+        <v>2500</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>248</v>
+        <v>2920</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>202</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>24.62</v>
+        <v>10.67</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-7.33</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>1600</v>
+        <v>152</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>1620</v>
+        <v>166</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>1190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>21.43</v>
+        <v>15.79</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-8.57</v>
+        <v>-7.89</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>83</v>
+        <v>835</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>85</v>
+        <v>880</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>64</v>
+        <v>700</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5539,343 +5539,343 @@
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>18.95</v>
+        <v>20.41</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-8.77</v>
+        <v>-8.16</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>8475</v>
+        <v>100</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>8475</v>
+        <v>118</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>6500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>20.81</v>
+        <v>12.73</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.18</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>432</v>
+        <v>240</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>505</v>
+        <v>248</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>380</v>
+        <v>202</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>16.35</v>
+        <v>24.62</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>91</v>
+        <v>1600</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>91</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>30.37</v>
+        <v>21.43</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.57</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>19.33</v>
+        <v>18.95</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.77</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>127</v>
+        <v>8475</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>102</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>16.36</v>
+        <v>20.81</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-14.55</v>
+        <v>-9.09</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>175</v>
+        <v>432</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>141</v>
+        <v>380</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>15.1</v>
+        <v>16.35</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-14.58</v>
+        <v>-12.5</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>91</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>442</v>
+        <v>121</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>328</v>
+        <v>91</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>12.36</v>
+        <v>30.37</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-14.61</v>
+        <v>-14.07</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>860</v>
+        <v>142</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1000</v>
+        <v>176</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>760</v>
+        <v>116</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>18.87</v>
+        <v>19.33</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-14.62</v>
+        <v>-14.29</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>252</v>
+        <v>142</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>181</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>16.38</v>
+        <v>16.36</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.55</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>175</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>396</v>
+        <v>141</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>19.27</v>
+        <v>15.1</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.58</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>222</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>260</v>
+        <v>442</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>186</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>24.77</v>
+        <v>12.36</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.61</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>1810</v>
+        <v>860</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>2040</v>
+        <v>1000</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1395</v>
+        <v>760</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>17.21</v>
+        <v>18.87</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.62</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>104</v>
+        <v>181</v>
       </c>
     </row>
     <row r="202">
@@ -5886,158 +5886,293 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>11.83</v>
+        <v>16.38</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.66</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>378</v>
+        <v>540</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>288</v>
+        <v>396</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>20.37</v>
+        <v>19.27</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.68</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F203" s="3" t="n">
         <v>260</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>15.94</v>
+        <v>24.77</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.68</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>2760</v>
+        <v>1810</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>3200</v>
+        <v>2040</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>2350</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>25</v>
+        <v>17.21</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.75</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>14.05</v>
+        <v>11.83</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.79</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>115</v>
+        <v>316.9231611887614</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>138</v>
+        <v>378</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>103</v>
+        <v>288</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>LCKM.JK</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
+      <c r="C211" s="2" t="n">
         <v>18.44</v>
       </c>
-      <c r="D207" s="2" t="n">
+      <c r="D211" s="2" t="n">
         <v>-14.89</v>
       </c>
-      <c r="E207" s="3" t="n">
+      <c r="E211" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F207" s="3" t="n">
+      <c r="F211" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="G207" s="3" t="n">
+      <c r="G211" s="3" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BHAT.JK</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>2560</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>1770</v>
       </c>
     </row>
   </sheetData>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -562,223 +562,223 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>33.62</v>
+        <v>31.16</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>25</v>
+        <v>27.54</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>145</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>860</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1170</v>
+        <v>860</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1255</v>
+        <v>975</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1255</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>4120</v>
+        <v>1170</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>525</v>
+        <v>3070</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1625</v>
+        <v>525</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24.6</v>
+        <v>24.69</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.6</v>
+        <v>24.69</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>750</v>
+        <v>1625</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>785</v>
+        <v>2020</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>785</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -787,25 +787,25 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>685</v>
+        <v>785</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>685</v>
+        <v>785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -814,673 +814,673 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>24.41</v>
+        <v>24.55</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24.41</v>
+        <v>24.55</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>440</v>
+        <v>550</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>525</v>
+        <v>685</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>525</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>26.02</v>
+        <v>24.41</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24.39</v>
+        <v>24.41</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>125</v>
+        <v>440</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>155</v>
+        <v>525</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>153</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>25</v>
+        <v>26.02</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.09</v>
+        <v>24.39</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1185</v>
+        <v>125</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1375</v>
+        <v>155</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1365</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>24.76</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>22.8</v>
+        <v>24.09</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3830</v>
+        <v>1185</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3830</v>
+        <v>1375</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3770</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>21.95</v>
+        <v>24.76</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>21.95</v>
+        <v>22.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2870</v>
+        <v>3830</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3500</v>
+        <v>3830</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3500</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>24.75</v>
+        <v>21.95</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>21.78</v>
+        <v>21.95</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2490</v>
+        <v>2870</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2520</v>
+        <v>3500</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2460</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>24.68</v>
+        <v>24.75</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.04</v>
+        <v>21.78</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1930</v>
+        <v>2490</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2400</v>
+        <v>2520</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2330</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>24.86</v>
+        <v>24.68</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>20.23</v>
+        <v>21.04</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1685</v>
+        <v>1930</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2160</v>
+        <v>2400</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2080</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20.2</v>
+        <v>24.86</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1535</v>
+        <v>1685</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1845</v>
+        <v>2160</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1845</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6550</v>
+        <v>1535</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>12125</v>
+        <v>6550</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5950</v>
+        <v>12125</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6300</v>
+        <v>5950</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>24.7</v>
+        <v>19.68</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>19.52</v>
+        <v>19.68</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1565</v>
+        <v>6300</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1565</v>
+        <v>7450</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1500</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24.57</v>
+        <v>24.7</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>19.43</v>
+        <v>19.52</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>430</v>
+        <v>1565</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>436</v>
+        <v>1565</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>418</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>33.79</v>
+        <v>24.57</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>18.62</v>
+        <v>19.43</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>149</v>
+        <v>430</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>172</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>21.31</v>
+        <v>34.19</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.21</v>
+        <v>17.95</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>635</v>
+        <v>126</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>740</v>
+        <v>157</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>715</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1489,592 +1489,592 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>20.92</v>
+        <v>17.27</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.07</v>
+        <v>13.64</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1525</v>
+        <v>550</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1850</v>
+        <v>645</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1730</v>
+        <v>625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>12.78</v>
+        <v>20.92</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>358</v>
+        <v>1525</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>406</v>
+        <v>1850</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>406</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>14.49</v>
+        <v>14.46</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>138</v>
+        <v>496</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>155</v>
+        <v>560</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>12.73</v>
+        <v>14.49</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>138</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>370</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>30.41</v>
+        <v>11.61</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11.49</v>
+        <v>11.61</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>16.39</v>
+        <v>30.41</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2083,241 +2083,241 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>30.34</v>
+        <v>22.5</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>14.73</v>
+        <v>30.34</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11.11</v>
+        <v>11.24</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1955</v>
+        <v>93</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2220</v>
+        <v>116</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>12.67</v>
+        <v>14.73</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1690</v>
+        <v>2220</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1665</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>16.44</v>
+        <v>12.67</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>74</v>
+        <v>1515</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>85</v>
+        <v>1690</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>81</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>22.48</v>
+        <v>16.44</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10.85</v>
+        <v>10.96</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>22.64</v>
+        <v>22.48</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>10.38</v>
+        <v>22.64</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>106</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>585</v>
+        <v>130</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>585</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>18.18</v>
+        <v>10.38</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>91</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>104</v>
+        <v>585</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>97</v>
+        <v>585</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>10.88</v>
+        <v>18.18</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>815</v>
+        <v>104</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>810</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2326,52 +2326,52 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>14.68</v>
+        <v>10.88</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>545</v>
+        <v>770</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>625</v>
+        <v>815</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>19.77</v>
+        <v>14.68</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>212</v>
+        <v>625</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2380,673 +2380,673 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>13.04</v>
+        <v>19.77</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>580</v>
+        <v>179</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>650</v>
+        <v>212</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>630</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>17.09</v>
+        <v>13.04</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9.49</v>
+        <v>9.57</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>316</v>
+        <v>580</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>346</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>25.18</v>
+        <v>11.72</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>11.4</v>
+        <v>25.18</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9.33</v>
+        <v>9.35</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>422</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>104</v>
+        <v>2820</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>111</v>
+        <v>3290</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>109</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>28.09</v>
+        <v>22.73</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>22.69</v>
+        <v>11</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1085</v>
+        <v>104</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1325</v>
+        <v>111</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>15.2</v>
+        <v>28.09</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>8.77</v>
+        <v>8.99</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>364</v>
+        <v>177</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>372</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>10.19</v>
+        <v>15.2</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>117</v>
+        <v>372</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>14.29</v>
+        <v>10.19</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>10.11</v>
+        <v>24.57</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>945</v>
+        <v>2600</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1035</v>
+        <v>3600</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1015</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F88" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G88" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>23.46</v>
+        <v>13.38</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>161</v>
+        <v>4410</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>174</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>11.76</v>
+        <v>10.05</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>7.35</v>
+        <v>7.41</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>68</v>
+        <v>372</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>76</v>
+        <v>416</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>73</v>
+        <v>406</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>14</v>
+        <v>11.76</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>7</v>
+        <v>7.35</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>17.44</v>
+        <v>22.86</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>140</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>19.4</v>
+        <v>14</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>480</v>
+        <v>114</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>430</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3055,52 +3055,52 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>24.86</v>
+        <v>17.44</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>2260</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1935</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>22.32</v>
+        <v>19.4</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.87</v>
+        <v>6.97</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>490</v>
+        <v>408</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>498</v>
+        <v>430</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3109,592 +3109,592 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>15.53</v>
+        <v>24.86</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>103</v>
+        <v>2260</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>110</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>23.33</v>
+        <v>22.32</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>128</v>
+        <v>498</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>16</v>
+        <v>15.53</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>17.46</v>
+        <v>23.33</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>148</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>10.94</v>
+        <v>16</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>25</v>
+        <v>17.46</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>68</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>11.47</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>3460</v>
+        <v>66</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>3790</v>
+        <v>80</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>3610</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4.65</v>
+        <v>5.13</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>87</v>
+        <v>390</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3703,538 +3703,538 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>23.66</v>
+        <v>11.97</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>118</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>460</v>
+        <v>131</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>11.83</v>
+        <v>12.45</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>95</v>
+        <v>545</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>104</v>
+        <v>560</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>96</v>
+        <v>515</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>14.71</v>
+        <v>11.83</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>11.89</v>
+        <v>11.41</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>288</v>
+        <v>2080</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>320</v>
+        <v>2100</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>294</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>12.15</v>
+        <v>11.63</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>109</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>110</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>14.62</v>
+        <v>12.15</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>2550</v>
+        <v>109</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>2900</v>
+        <v>120</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>2600</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4243,52 +4243,52 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>10.16</v>
+        <v>11.89</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4297,79 +4297,79 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>79</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4378,79 +4378,79 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>89</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4459,835 +4459,835 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>11.41</v>
+        <v>14.29</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1490</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1660</v>
+        <v>2320</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1515</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>187</v>
+        <v>2100</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>189</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>18.31</v>
+        <v>10.34</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>710</v>
+        <v>348</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>840</v>
+        <v>384</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>720</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>19.87</v>
+        <v>11.41</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>8125</v>
+        <v>1490</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>9350</v>
+        <v>1660</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>7900</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>15.38</v>
+        <v>11.83</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>79</v>
+        <v>189</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>15.94</v>
+        <v>18.31</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>13800</v>
+        <v>710</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>16000</v>
+        <v>840</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>13975</v>
+        <v>720</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>10.59</v>
+        <v>15.38</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>13.64</v>
+        <v>15.94</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>88</v>
+        <v>13800</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>100</v>
+        <v>16000</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>89</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>208</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>10.76</v>
+        <v>13.64</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>88</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>3160</v>
+        <v>89</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>12.78</v>
+        <v>10.68</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2640</v>
+        <v>210</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>3000</v>
+        <v>228</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2660</v>
+        <v>208</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>28.48</v>
+        <v>20</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>152</v>
+        <v>406</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>12.87</v>
+        <v>22.58</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>93</v>
+        <v>1910</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>114</v>
+        <v>2280</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>101</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>17.5</v>
+        <v>10.76</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>163</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>188</v>
+        <v>3500</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>160</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>14.43</v>
+        <v>12.87</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>2020</v>
+        <v>93</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2220</v>
+        <v>114</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1930</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>18.04</v>
+        <v>17.5</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>163</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>332.87</v>
+        <v>188</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>29.27</v>
+        <v>28.48</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>10.17</v>
+        <v>12.78</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2400</v>
+        <v>2640</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2330</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.52</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>70</v>
+        <v>2020</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>80</v>
+        <v>2220</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>69</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>11.24</v>
+        <v>18.04</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.71</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>169</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>188</v>
+        <v>332.87</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>16.02</v>
+        <v>29.27</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-2.21</v>
+        <v>-1.22</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>10.49</v>
+        <v>10.17</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.27</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>2400</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>358</v>
+        <v>2600</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>316</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>11.19</v>
+        <v>14.29</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.43</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>398</v>
+        <v>69</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>15.31</v>
+        <v>11.24</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.78</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>169</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>191</v>
+        <v>166</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>17.36</v>
+        <v>16.02</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-2.78</v>
+        <v>-2.21</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>720</v>
+        <v>181</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>845</v>
+        <v>210</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>700</v>
+        <v>177</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>10.1</v>
+        <v>10.49</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.47</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>10300</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>10900</v>
+        <v>358</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>9600</v>
+        <v>316</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>10.65</v>
+        <v>11.19</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.52</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>19.31</v>
+        <v>15.31</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.55</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>139</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5296,241 +5296,241 @@
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>13.82</v>
+        <v>17.36</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.78</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="F180" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="G180" s="3" t="n">
         <v>700</v>
-      </c>
-      <c r="G180" s="3" t="n">
-        <v>585</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>11.11</v>
+        <v>10.1</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>83</v>
+        <v>10300</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>90</v>
+        <v>10900</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>77</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>23.53</v>
+        <v>18.05</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>700</v>
+        <v>2700</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>840</v>
+        <v>3140</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>645</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>13.58</v>
+        <v>19.31</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>10.5</v>
+        <v>13.82</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.88</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>1175</v>
+        <v>675</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>1210</v>
+        <v>700</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>1025</v>
+        <v>585</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>16.8</v>
+        <v>11.11</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.94</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>2500</v>
+        <v>83</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>2920</v>
+        <v>90</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>2330</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>10.67</v>
+        <v>10.19</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.1</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>139</v>
+        <v>298</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>15.79</v>
+        <v>23.53</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.15</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>835</v>
+        <v>700</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>700</v>
+        <v>645</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5539,133 +5539,133 @@
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>20.41</v>
+        <v>13.58</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.56</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>90</v>
+        <v>153</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>12.73</v>
+        <v>10.5</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-8.18</v>
+        <v>-6.39</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>240</v>
+        <v>1175</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>248</v>
+        <v>1210</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>202</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>24.62</v>
+        <v>16.8</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.8</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>1620</v>
+        <v>2920</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>1190</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>21.43</v>
+        <v>10.67</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-8.57</v>
+        <v>-7.33</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>64</v>
+        <v>139</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>18.95</v>
+        <v>15.79</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-8.77</v>
+        <v>-7.89</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>8475</v>
+        <v>835</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>8475</v>
+        <v>880</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>6500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5674,504 +5674,666 @@
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>20.81</v>
+        <v>20.41</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.16</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>432</v>
+        <v>100</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>505</v>
+        <v>118</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>16.35</v>
+        <v>12.73</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.18</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>91</v>
+        <v>240</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>91</v>
+        <v>202</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>30.37</v>
+        <v>24.62</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>142</v>
+        <v>1600</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>176</v>
+        <v>1620</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>116</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>19.33</v>
+        <v>21.43</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.57</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>16.36</v>
+        <v>18.95</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.77</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>175</v>
+        <v>8475</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>192</v>
+        <v>8475</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>141</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>15.1</v>
+        <v>24.44</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>91</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>442</v>
+        <v>112</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>328</v>
+        <v>82</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>12.36</v>
+        <v>20.81</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-14.61</v>
+        <v>-9.09</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>860</v>
+        <v>432</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>1000</v>
+        <v>505</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>760</v>
+        <v>380</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>18.87</v>
+        <v>16.35</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.5</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>16.38</v>
+        <v>30.37</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.07</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>142</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>24.77</v>
+        <v>16.36</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.55</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>1810</v>
+        <v>175</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>2040</v>
+        <v>192</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>1395</v>
+        <v>141</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>17.21</v>
+        <v>15.1</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.58</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>132</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>104</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>11.83</v>
+        <v>12.36</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.61</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>860</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>378</v>
+        <v>1000</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>288</v>
+        <v>760</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>20.37</v>
+        <v>18.87</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.62</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>15.94</v>
+        <v>16.38</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.66</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>2760</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>3200</v>
+        <v>540</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>2350</v>
+        <v>396</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>25</v>
+        <v>19.27</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>14.05</v>
+        <v>24.77</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>115</v>
+        <v>1810</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>138</v>
+        <v>2040</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>103</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>18.44</v>
+        <v>17.21</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.75</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
+      <c r="C218" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D212" s="2" t="n">
+      <c r="D218" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E212" s="3" t="n">
+      <c r="E218" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F212" s="3" t="n">
+      <c r="F218" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G212" s="3" t="n">
+      <c r="G218" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,55 +589,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>119</v>
+        <v>860</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>155</v>
+        <v>975</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>145</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>860</v>
+        <v>119</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -1588,493 +1588,493 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>31.46</v>
+        <v>20.78</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>95</v>
+        <v>2550</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>117</v>
+        <v>3080</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>102</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>20.92</v>
+        <v>17.27</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>13.07</v>
+        <v>13.64</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1525</v>
+        <v>550</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1850</v>
+        <v>645</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1730</v>
+        <v>625</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>12.78</v>
+        <v>20.92</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>358</v>
+        <v>1525</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>406</v>
+        <v>1850</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>406</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>14.49</v>
+        <v>14.46</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>138</v>
+        <v>496</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>155</v>
+        <v>560</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>12.73</v>
+        <v>14.49</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>138</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>370</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>131</v>
+        <v>390</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2083,1699 +2083,1699 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>16.44</v>
+        <v>14.73</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>74</v>
+        <v>1955</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>85</v>
+        <v>2220</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>81</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>22.64</v>
+        <v>16.44</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>18.18</v>
+        <v>10.38</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>91</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>104</v>
+        <v>585</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>97</v>
+        <v>585</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>10.88</v>
+        <v>22.64</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>770</v>
+        <v>106</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>815</v>
+        <v>130</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>810</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>19.77</v>
+        <v>10.88</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>179</v>
+        <v>770</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>212</v>
+        <v>815</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>13.04</v>
+        <v>14.68</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>17.09</v>
+        <v>19.77</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>346</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>11.72</v>
+        <v>13.04</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>128</v>
+        <v>580</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>143</v>
+        <v>650</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>140</v>
+        <v>630</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>25.18</v>
+        <v>17.09</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9.35</v>
+        <v>9.49</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>11.4</v>
+        <v>11.72</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>388</v>
+        <v>128</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>422</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>13.95</v>
+        <v>25.18</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>20500</v>
+        <v>141</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>24500</v>
+        <v>174</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>23500</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>16.67</v>
+        <v>11.4</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2820</v>
+        <v>388</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>3290</v>
+        <v>430</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>3080</v>
+        <v>422</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>104</v>
+        <v>2820</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>111</v>
+        <v>3290</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>109</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>28.09</v>
+        <v>22.73</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>22.69</v>
+        <v>11</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1085</v>
+        <v>104</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1325</v>
+        <v>111</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>15.2</v>
+        <v>28.09</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8.77</v>
+        <v>8.99</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>364</v>
+        <v>177</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>372</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>10.19</v>
+        <v>15.2</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>117</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>24.57</v>
+        <v>16.1</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2600</v>
+        <v>120</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3600</v>
+        <v>137</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>945</v>
+        <v>109</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1035</v>
+        <v>119</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1015</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>16.35</v>
+        <v>24.57</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7.69</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>106</v>
+        <v>2600</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>121</v>
+        <v>3600</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>112</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>13.38</v>
+        <v>14.29</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>7.48</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>4410</v>
+        <v>112</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>5000</v>
+        <v>128</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>4740</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>10.05</v>
+        <v>10.11</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>7.41</v>
+        <v>7.98</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>372</v>
+        <v>945</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>416</v>
+        <v>1035</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>406</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>23.46</v>
+        <v>16.35</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>14</v>
+        <v>23.46</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>107</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>17.44</v>
+        <v>11.76</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.98</v>
+        <v>7.35</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>68</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>19.4</v>
+        <v>22.86</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.97</v>
+        <v>7.14</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>15.53</v>
+        <v>19.4</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>6.8</v>
+        <v>6.97</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>110</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>23.33</v>
+        <v>24.86</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>148</v>
+        <v>2260</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>128</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>16</v>
+        <v>22.32</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>87</v>
+        <v>570</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>10.94</v>
+        <v>16</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>11.92</v>
+        <v>10.94</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>605</v>
+        <v>66</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>4.65</v>
+        <v>5.13</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>87</v>
+        <v>390</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3784,457 +3784,457 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>20.56</v>
+        <v>24.91</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>1980</v>
+        <v>1425</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>1850</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>23.66</v>
+        <v>11.97</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>118</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>460</v>
+        <v>131</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>11.83</v>
+        <v>12.45</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>95</v>
+        <v>545</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>104</v>
+        <v>560</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>96</v>
+        <v>515</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>14.71</v>
+        <v>11.83</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>12.15</v>
+        <v>11.41</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>109</v>
+        <v>2080</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>110</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4243,79 +4243,79 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>11.89</v>
+        <v>11.63</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>288</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>320</v>
+        <v>192</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>294</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>14.62</v>
+        <v>12.15</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>2550</v>
+        <v>109</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>2900</v>
+        <v>120</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>2600</v>
+        <v>110</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4324,52 +4324,52 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>10.16</v>
+        <v>11.89</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4378,79 +4378,79 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>79</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4459,79 +4459,79 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>89</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4540,403 +4540,403 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>11.41</v>
+        <v>14.29</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1490</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>1660</v>
+        <v>2320</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1515</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>187</v>
+        <v>2100</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>189</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>18.31</v>
+        <v>10.34</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>710</v>
+        <v>348</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>840</v>
+        <v>384</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>720</v>
+        <v>354</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>15.38</v>
+        <v>11.41</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>79</v>
+        <v>1490</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>90</v>
+        <v>1660</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>79</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>19.87</v>
+        <v>11.83</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>8125</v>
+        <v>187</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>9350</v>
+        <v>208</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>7900</v>
+        <v>189</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>15.94</v>
+        <v>18.31</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>13800</v>
+        <v>710</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>16000</v>
+        <v>840</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>13975</v>
+        <v>720</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>10.59</v>
+        <v>15.38</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>13.64</v>
+        <v>15.94</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>88</v>
+        <v>13800</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>100</v>
+        <v>16000</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>89</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>208</v>
+        <v>86</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>20</v>
+        <v>21.97</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>406</v>
+        <v>865</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>432</v>
+        <v>1055</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>362</v>
+        <v>875</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>22.58</v>
+        <v>13.64</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>1910</v>
+        <v>88</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2280</v>
+        <v>100</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>1870</v>
+        <v>89</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.76</v>
+        <v>10.68</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>210</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>3500</v>
+        <v>228</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>3160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>12.87</v>
+        <v>20</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>114</v>
+        <v>432</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>101</v>
+        <v>362</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4945,241 +4945,241 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>17.5</v>
+        <v>22.58</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>163</v>
+        <v>1910</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>188</v>
+        <v>2280</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>160</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>28.48</v>
+        <v>12.87</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>151</v>
+        <v>101</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>12.78</v>
+        <v>10.76</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2640</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2660</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>14.43</v>
+        <v>12.78</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2020</v>
+        <v>2640</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>2220</v>
+        <v>3000</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>1930</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>18.04</v>
+        <v>17.5</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>163</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>332.87</v>
+        <v>188</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>29.27</v>
+        <v>28.48</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>10.17</v>
+        <v>14.43</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-1.27</v>
+        <v>-0.52</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>2400</v>
+        <v>2020</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2600</v>
+        <v>2220</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2330</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>14.29</v>
+        <v>18.04</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.71</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>70</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>80</v>
+        <v>332.87</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>69</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>11.24</v>
+        <v>29.27</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-1.78</v>
+        <v>-1.22</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>166</v>
+        <v>81</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5188,295 +5188,295 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>16.02</v>
+        <v>10.17</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-2.21</v>
+        <v>-1.27</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>181</v>
+        <v>2400</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>210</v>
+        <v>2600</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>177</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>10.49</v>
+        <v>14.29</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.43</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>70</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>316</v>
+        <v>69</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>11.19</v>
+        <v>11.24</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.78</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>420</v>
+        <v>169</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>454</v>
+        <v>188</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>398</v>
+        <v>166</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>15.31</v>
+        <v>16.02</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-2.55</v>
+        <v>-2.21</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>17.36</v>
+        <v>10.49</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-2.78</v>
+        <v>-2.47</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>720</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>845</v>
+        <v>358</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>700</v>
+        <v>316</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>10.1</v>
+        <v>11.19</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.52</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>10300</v>
+        <v>420</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>10900</v>
+        <v>454</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>9600</v>
+        <v>398</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>10.65</v>
+        <v>15.31</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.55</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>458</v>
+        <v>169</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>478</v>
+        <v>226</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>418</v>
+        <v>191</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>18.05</v>
+        <v>17.36</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.78</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2700</v>
+        <v>720</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>3140</v>
+        <v>845</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>2550</v>
+        <v>700</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>19.31</v>
+        <v>10.1</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-4.14</v>
+        <v>-3.03</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>149</v>
+        <v>10300</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>173</v>
+        <v>10900</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>139</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>13.82</v>
+        <v>10.65</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-4.88</v>
+        <v>-3.24</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>675</v>
+        <v>458</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>700</v>
+        <v>478</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>585</v>
+        <v>418</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>11.11</v>
+        <v>18.05</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-4.94</v>
+        <v>-4.14</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>83</v>
+        <v>2700</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>90</v>
+        <v>3140</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>77</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5485,295 +5485,295 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>10.19</v>
+        <v>19.31</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-5.1</v>
+        <v>-4.14</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>346</v>
+        <v>149</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>298</v>
+        <v>139</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>23.53</v>
+        <v>21.99</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.26</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>700</v>
+        <v>172</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>840</v>
+        <v>172</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>645</v>
+        <v>135</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>13.58</v>
+        <v>13.82</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.88</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>162</v>
+        <v>675</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>184</v>
+        <v>700</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>153</v>
+        <v>585</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>10.5</v>
+        <v>11.11</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.94</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1175</v>
+        <v>83</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>1210</v>
+        <v>90</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>1025</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>16.8</v>
+        <v>10.19</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-6.8</v>
+        <v>-5.1</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>2500</v>
+        <v>346</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>2920</v>
+        <v>346</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>2330</v>
+        <v>298</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>10.67</v>
+        <v>23.53</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.15</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>152</v>
+        <v>700</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>166</v>
+        <v>840</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>139</v>
+        <v>645</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>15.79</v>
+        <v>13.58</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.56</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>835</v>
+        <v>162</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>880</v>
+        <v>184</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>700</v>
+        <v>153</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>20.41</v>
+        <v>10.5</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-8.16</v>
+        <v>-6.39</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>100</v>
+        <v>1175</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>118</v>
+        <v>1210</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>90</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>12.73</v>
+        <v>16.8</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-8.18</v>
+        <v>-6.8</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>240</v>
+        <v>2500</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>248</v>
+        <v>2920</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>202</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>24.62</v>
+        <v>10.67</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-7.33</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1600</v>
+        <v>152</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1620</v>
+        <v>166</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>1190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>21.43</v>
+        <v>15.79</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-8.57</v>
+        <v>-7.89</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>83</v>
+        <v>835</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>85</v>
+        <v>880</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>64</v>
+        <v>700</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5782,558 +5782,693 @@
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>18.95</v>
+        <v>20.41</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-8.77</v>
+        <v>-8.16</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>8475</v>
+        <v>100</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>8475</v>
+        <v>118</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>6500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>24.44</v>
+        <v>12.73</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.18</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>91</v>
+        <v>240</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>82</v>
+        <v>202</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>20.81</v>
+        <v>24.62</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>432</v>
+        <v>1600</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>505</v>
+        <v>1620</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>380</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>16.35</v>
+        <v>21.43</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.57</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>30.37</v>
+        <v>18.95</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.77</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>176</v>
+        <v>8475</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>116</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>19.33</v>
+        <v>24.44</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>16.36</v>
+        <v>20.81</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-14.55</v>
+        <v>-9.09</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>175</v>
+        <v>432</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>141</v>
+        <v>380</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>15.1</v>
+        <v>18.18</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-14.58</v>
+        <v>-11.93</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>180</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>442</v>
+        <v>208</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>328</v>
+        <v>155</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>12.36</v>
+        <v>16.35</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-14.61</v>
+        <v>-12.5</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>860</v>
+        <v>91</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1000</v>
+        <v>121</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>760</v>
+        <v>91</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>18.87</v>
+        <v>30.37</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-14.62</v>
+        <v>-14.07</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>218</v>
+        <v>142</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>16.38</v>
+        <v>19.33</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.29</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>127</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>540</v>
+        <v>142</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>396</v>
+        <v>102</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>19.27</v>
+        <v>16.36</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.55</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>186</v>
+        <v>141</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>24.77</v>
+        <v>15.1</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.58</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>1810</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>2040</v>
+        <v>442</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>1395</v>
+        <v>328</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>17.21</v>
+        <v>12.36</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.61</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>132</v>
+        <v>860</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>143</v>
+        <v>1000</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>104</v>
+        <v>760</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>11.83</v>
+        <v>18.87</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.62</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>218</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>378</v>
+        <v>252</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>288</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>20.37</v>
+        <v>16.38</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.66</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>220</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>184</v>
+        <v>396</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>15.94</v>
+        <v>19.27</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.68</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>2760</v>
+        <v>222</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>3200</v>
+        <v>260</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>2350</v>
+        <v>186</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>14.05</v>
+        <v>24.77</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>115</v>
+        <v>1810</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>138</v>
+        <v>2040</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>103</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>25</v>
+        <v>17.21</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.75</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>18.44</v>
+        <v>11.83</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.79</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>120</v>
+        <v>316.9231611887614</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>167</v>
+        <v>378</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>120</v>
+        <v>288</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="C223" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D218" s="2" t="n">
+      <c r="D223" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E218" s="3" t="n">
+      <c r="E223" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F218" s="3" t="n">
+      <c r="F223" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G218" s="3" t="n">
+      <c r="G223" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>860</v>
+        <v>165</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>975</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>975</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -643,109 +643,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1170</v>
+        <v>460</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1255</v>
+        <v>545</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1255</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>24.85</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>24.85</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4120</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4120</v>
+        <v>975</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4120</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>24.8</v>
+        <v>24.88</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24.8</v>
+        <v>24.88</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3070</v>
+        <v>1170</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3070</v>
+        <v>1255</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3070</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24.76</v>
+        <v>24.85</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>24.76</v>
+        <v>24.85</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>525</v>
+        <v>4120</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>655</v>
+        <v>4120</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>655</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="12">
@@ -756,83 +756,83 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24.69</v>
+        <v>24.8</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.69</v>
+        <v>24.8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1625</v>
+        <v>3070</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2020</v>
+        <v>3070</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2020</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>24.6</v>
+        <v>24.76</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24.6</v>
+        <v>24.76</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>750</v>
+        <v>525</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>785</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>24.55</v>
+        <v>24.69</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24.55</v>
+        <v>24.69</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>550</v>
+        <v>1625</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>685</v>
+        <v>2020</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>685</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -841,127 +841,127 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24.41</v>
+        <v>24.6</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24.41</v>
+        <v>24.6</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>525</v>
+        <v>785</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>525</v>
+        <v>785</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>26.02</v>
+        <v>24.55</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.39</v>
+        <v>24.55</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>125</v>
+        <v>550</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>155</v>
+        <v>685</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>153</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>25</v>
+        <v>24.41</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24.09</v>
+        <v>24.41</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1185</v>
+        <v>440</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1375</v>
+        <v>525</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1365</v>
+        <v>525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.76</v>
+        <v>26.02</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22.8</v>
+        <v>24.39</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3830</v>
+        <v>125</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3830</v>
+        <v>155</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3770</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>21.95</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>21.95</v>
+        <v>24.09</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2870</v>
+        <v>1185</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3500</v>
+        <v>1375</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3500</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="20">
@@ -972,83 +972,83 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>24.75</v>
+        <v>24.76</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.78</v>
+        <v>22.8</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2490</v>
+        <v>3830</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2520</v>
+        <v>3830</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2460</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>24.68</v>
+        <v>21.95</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>21.04</v>
+        <v>21.95</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1930</v>
+        <v>2870</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2330</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>24.86</v>
+        <v>24.75</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>20.23</v>
+        <v>21.78</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1685</v>
+        <v>2490</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2160</v>
+        <v>2520</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2080</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1057,73 +1057,73 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>20.2</v>
+        <v>24.68</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>20.2</v>
+        <v>21.04</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1535</v>
+        <v>1930</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1845</v>
+        <v>2400</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1845</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>20</v>
+        <v>24.86</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20</v>
+        <v>20.23</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>6550</v>
+        <v>1685</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7800</v>
+        <v>2160</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>7800</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>19.87</v>
+        <v>20.2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>19.87</v>
+        <v>20.2</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>12125</v>
+        <v>1535</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>14025</v>
+        <v>1845</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14025</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="26">
@@ -1134,1001 +1134,1001 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5950</v>
+        <v>6550</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7125</v>
+        <v>7800</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7125</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>19.68</v>
+        <v>19.87</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>19.68</v>
+        <v>19.87</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6300</v>
+        <v>12125</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7450</v>
+        <v>14025</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7450</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24.7</v>
+        <v>19.75</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>19.52</v>
+        <v>19.75</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1565</v>
+        <v>5950</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1565</v>
+        <v>7125</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1500</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>24.57</v>
+        <v>19.68</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>19.43</v>
+        <v>19.68</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>430</v>
+        <v>6300</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>436</v>
+        <v>7450</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>418</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>33.79</v>
+        <v>24.7</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>18.62</v>
+        <v>19.52</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>149</v>
+        <v>1565</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>194</v>
+        <v>1565</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>172</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>24.89</v>
+        <v>24.57</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>18.45</v>
+        <v>19.43</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2320</v>
+        <v>430</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2910</v>
+        <v>436</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2760</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>20</v>
+        <v>33.79</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.26</v>
+        <v>18.62</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>575</v>
+        <v>149</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>690</v>
+        <v>194</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>680</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>21</v>
+        <v>24.89</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>18</v>
+        <v>18.45</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>505</v>
+        <v>2320</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>605</v>
+        <v>2910</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>590</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>34.19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17.95</v>
+        <v>18.26</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>126</v>
+        <v>575</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>157</v>
+        <v>690</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>138</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>21.31</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>17.21</v>
+        <v>18</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>635</v>
+        <v>505</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>740</v>
+        <v>605</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>715</v>
+        <v>590</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>24.88</v>
+        <v>34.19</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.07</v>
+        <v>17.95</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1020</v>
+        <v>126</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1280</v>
+        <v>157</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>24.86</v>
+        <v>21.31</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16.76</v>
+        <v>17.21</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>176</v>
+        <v>635</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>216</v>
+        <v>740</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>202</v>
+        <v>715</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>25</v>
+        <v>24.88</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15.91</v>
+        <v>17.07</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1320</v>
+        <v>1020</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1650</v>
+        <v>1280</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1530</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>22.85</v>
+        <v>24.86</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15.89</v>
+        <v>16.76</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3080</v>
+        <v>176</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3710</v>
+        <v>216</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3500</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>18.72</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>15.69</v>
+        <v>15.91</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>14700</v>
+        <v>1320</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>16650</v>
+        <v>1650</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16225</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>16.79</v>
+        <v>22.85</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15.27</v>
+        <v>15.89</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>130</v>
+        <v>3080</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>153</v>
+        <v>3710</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>151</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>22.5</v>
+        <v>18.72</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15</v>
+        <v>15.69</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>78</v>
+        <v>14700</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>98</v>
+        <v>16650</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>92</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>20.78</v>
+        <v>16.79</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>14.9</v>
+        <v>15.27</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2550</v>
+        <v>130</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3080</v>
+        <v>153</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2930</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>19.85</v>
+        <v>20.78</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>700</v>
+        <v>2550</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>785</v>
+        <v>3080</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>750</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>19.82</v>
+        <v>31.46</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>14.41</v>
+        <v>14.61</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>17.65</v>
+        <v>19.85</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>700</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>520</v>
+        <v>785</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>505</v>
+        <v>750</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>27.78</v>
+        <v>19.82</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>13.89</v>
+        <v>14.41</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>24.86</v>
+        <v>17.65</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>13.81</v>
+        <v>14.25</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>920</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1130</v>
+        <v>520</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1030</v>
+        <v>505</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>14.88</v>
+        <v>27.78</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.69</v>
+        <v>13.89</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>108</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>386</v>
+        <v>138</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>382</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17.27</v>
+        <v>24.86</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>13.64</v>
+        <v>13.81</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>550</v>
+        <v>920</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>645</v>
+        <v>1130</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>625</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>20.92</v>
+        <v>14.88</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1525</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1850</v>
+        <v>386</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1730</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>12.78</v>
+        <v>17.27</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>12.78</v>
+        <v>13.64</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>358</v>
+        <v>550</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>406</v>
+        <v>645</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>406</v>
+        <v>625</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>14.46</v>
+        <v>20.92</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12.45</v>
+        <v>13.07</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>496</v>
+        <v>1525</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>570</v>
+        <v>1850</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>560</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>14.49</v>
+        <v>12.78</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>12.32</v>
+        <v>12.78</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>158</v>
+        <v>406</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>155</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>16.42</v>
+        <v>14.49</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11.94</v>
+        <v>12.32</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>19.05</v>
+        <v>12.73</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11.9</v>
+        <v>12.12</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>86</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>94</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>23.08</v>
+        <v>16.42</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>390</v>
+        <v>135</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>436</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>131</v>
+        <v>390</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2137,1105 +2137,1105 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>16.44</v>
+        <v>14.73</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>74</v>
+        <v>1955</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>85</v>
+        <v>2220</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>81</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>10.38</v>
+        <v>16.44</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>74</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>585</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>22.64</v>
+        <v>22.48</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>770</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>815</v>
+        <v>585</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>810</v>
+        <v>585</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>19.77</v>
+        <v>10.88</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>179</v>
+        <v>770</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>212</v>
+        <v>815</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>13.04</v>
+        <v>14.68</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>17.09</v>
+        <v>19.77</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>346</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>11.72</v>
+        <v>13.04</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>128</v>
+        <v>580</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>143</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>140</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>25.18</v>
+        <v>17.09</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9.35</v>
+        <v>9.49</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>11.4</v>
+        <v>11.72</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>388</v>
+        <v>128</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>422</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>13.95</v>
+        <v>25.18</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>20500</v>
+        <v>141</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>24500</v>
+        <v>174</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>23500</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>16.67</v>
+        <v>11.4</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2820</v>
+        <v>388</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>3290</v>
+        <v>430</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>3080</v>
+        <v>422</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>22.73</v>
+        <v>13.95</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>176</v>
+        <v>20500</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>216</v>
+        <v>24500</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>192</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>104</v>
+        <v>2820</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>111</v>
+        <v>3290</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>109</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>28.09</v>
+        <v>22.73</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>22.69</v>
+        <v>11</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1085</v>
+        <v>104</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1325</v>
+        <v>111</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>15.2</v>
+        <v>28.09</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>8.77</v>
+        <v>8.99</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>364</v>
+        <v>177</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>372</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>16.1</v>
+        <v>22.69</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>120</v>
+        <v>1085</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>137</v>
+        <v>1325</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>128</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>18.46</v>
+        <v>15.2</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>141</v>
+        <v>372</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>10.19</v>
+        <v>16.1</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>8.33</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>24.57</v>
+        <v>18.46</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2600</v>
+        <v>135</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>3600</v>
+        <v>154</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>3130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>14.29</v>
+        <v>10.19</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>10.11</v>
+        <v>24.57</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>7.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>945</v>
+        <v>2600</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1035</v>
+        <v>3600</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1015</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F93" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G93" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>10.05</v>
+        <v>12.17</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>7.41</v>
+        <v>7.83</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>372</v>
+        <v>230</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>416</v>
+        <v>258</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>406</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>23.46</v>
+        <v>16.35</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>14</v>
+        <v>10.05</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>17.44</v>
+        <v>11.76</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>6.98</v>
+        <v>7.35</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>68</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>19.4</v>
+        <v>22.86</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>6.97</v>
+        <v>7.14</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>24.86</v>
+        <v>15.62</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>6.91</v>
+        <v>7.03</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2260</v>
+        <v>130</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>2260</v>
+        <v>148</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>1935</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>22.32</v>
+        <v>14</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>6.87</v>
+        <v>7</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>490</v>
+        <v>101</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>570</v>
+        <v>114</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>498</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3244,322 +3244,322 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>15.53</v>
+        <v>17.44</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>6.8</v>
+        <v>6.98</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>103</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>23.33</v>
+        <v>19.4</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>6.67</v>
+        <v>6.97</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>119</v>
+        <v>408</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>148</v>
+        <v>480</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>128</v>
+        <v>430</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>16</v>
+        <v>24.86</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>74</v>
+        <v>2260</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>87</v>
+        <v>2260</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>80</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>17.46</v>
+        <v>22.32</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.35</v>
+        <v>6.87</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>128</v>
+        <v>490</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>134</v>
+        <v>498</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>10.94</v>
+        <v>15.53</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>11.47</v>
+        <v>16</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6.18</v>
+        <v>6.67</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>3460</v>
+        <v>74</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>3790</v>
+        <v>87</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>3610</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>11.92</v>
+        <v>17.46</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.96</v>
+        <v>6.35</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>5.77</v>
+        <v>6.25</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1095</v>
+        <v>66</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1300</v>
+        <v>80</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>12.64</v>
+        <v>11.47</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>5.75</v>
+        <v>6.18</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>88</v>
+        <v>3460</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>98</v>
+        <v>3790</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>92</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>19.15</v>
+        <v>11.92</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5.67</v>
+        <v>5.96</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>705</v>
+        <v>151</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>840</v>
+        <v>169</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>745</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3568,52 +3568,52 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>5.49</v>
+        <v>5.83</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>358</v>
+        <v>605</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>346</v>
+        <v>635</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>19.15</v>
+        <v>25</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5.32</v>
+        <v>5.77</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>103</v>
+        <v>1095</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>112</v>
+        <v>1300</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3622,106 +3622,106 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>11.58</v>
+        <v>12.64</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>5.26</v>
+        <v>5.75</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>88</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>10.31</v>
+        <v>19.15</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>5.15</v>
+        <v>5.67</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>98</v>
+        <v>705</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>107</v>
+        <v>840</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>102</v>
+        <v>745</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>14.36</v>
+        <v>25</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>5.13</v>
+        <v>5.49</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>410</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11.5</v>
+        <v>19.15</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>4.87</v>
+        <v>5.32</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>2330</v>
+        <v>103</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>2520</v>
+        <v>112</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>2370</v>
+        <v>99</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3730,646 +3730,646 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>13.33</v>
+        <v>11.58</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>4.71</v>
+        <v>5.26</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>2750</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>2890</v>
+        <v>106</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>2670</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>11.63</v>
+        <v>10.31</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>10.6</v>
+        <v>14.36</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4.64</v>
+        <v>5.13</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>390</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>167</v>
+        <v>446</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>158</v>
+        <v>410</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>24.91</v>
+        <v>11.5</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>1425</v>
+        <v>2330</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>1780</v>
+        <v>2520</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>1490</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>19.77</v>
+        <v>13.33</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>177</v>
+        <v>2750</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>212</v>
+        <v>2890</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>185</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>13.04</v>
+        <v>11.63</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>87</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>260</v>
+        <v>96</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>20.56</v>
+        <v>10.6</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>4.23</v>
+        <v>4.64</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>1980</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>2140</v>
+        <v>167</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>1850</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>15</v>
+        <v>24.91</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>4</v>
+        <v>4.56</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>101</v>
+        <v>1425</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>115</v>
+        <v>1780</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>104</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>15.09</v>
+        <v>19.77</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>3.77</v>
+        <v>4.52</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>12.69</v>
+        <v>11.61</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>3.73</v>
+        <v>4.52</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>11.97</v>
+        <v>13.04</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>3.42</v>
+        <v>4.35</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>118</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>121</v>
+        <v>240</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>12.45</v>
+        <v>20.56</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>3.41</v>
+        <v>4.23</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>545</v>
+        <v>1980</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>560</v>
+        <v>2140</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>515</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>17.21</v>
+        <v>15</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>615</v>
+        <v>101</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>715</v>
+        <v>115</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>630</v>
+        <v>104</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>23.66</v>
+        <v>15.09</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>3.23</v>
+        <v>3.77</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>159</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>460</v>
+        <v>183</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>384</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>11.83</v>
+        <v>12.69</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>30.95</v>
+        <v>11.97</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>3.17</v>
+        <v>3.42</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>34.34</v>
+        <v>12.45</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>133</v>
+        <v>545</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>133</v>
+        <v>560</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>102</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>14.71</v>
+        <v>17.21</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>70</v>
+        <v>615</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>78</v>
+        <v>715</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>70</v>
+        <v>630</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>11.41</v>
+        <v>23.66</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>2080</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>2100</v>
+        <v>460</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>1940</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>11.63</v>
+        <v>11.83</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>95</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>177</v>
+        <v>96</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>11.57</v>
+        <v>30.95</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1210</v>
+        <v>141</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>1350</v>
+        <v>165</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>1245</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>12.15</v>
+        <v>34.34</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>11.89</v>
+        <v>14.71</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>320</v>
+        <v>78</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>294</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>16.7</v>
+        <v>11.41</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>5200</v>
+        <v>2080</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>5450</v>
+        <v>2100</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>4800</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4378,133 +4378,133 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>14.62</v>
+        <v>11.63</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>2550</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>2900</v>
+        <v>192</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>2600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>10.16</v>
+        <v>11.57</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>172</v>
+        <v>1210</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>206</v>
+        <v>1350</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>192</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>17.95</v>
+        <v>11.89</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>92</v>
+        <v>320</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>80</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>17.44</v>
+        <v>12.15</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>12.36</v>
+        <v>16.7</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>89</v>
+        <v>5200</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>100</v>
+        <v>5450</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>91</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4513,25 +4513,25 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>11.75</v>
+        <v>14.62</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.01</v>
+        <v>2.77</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>2550</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>3560</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4540,79 +4540,79 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>25</v>
+        <v>10.16</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>14.29</v>
+        <v>10.39</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>78</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>2320</v>
+        <v>85</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2070</v>
+        <v>79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>11.54</v>
+        <v>17.95</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2100</v>
+        <v>79</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2320</v>
+        <v>92</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4621,133 +4621,133 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>10.34</v>
+        <v>17.44</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>384</v>
+        <v>101</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>354</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>11.41</v>
+        <v>12.36</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>1490</v>
+        <v>89</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1660</v>
+        <v>100</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>1515</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>11.83</v>
+        <v>11.75</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>187</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>208</v>
+        <v>3900</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>189</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>18.31</v>
+        <v>25</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>710</v>
+        <v>208</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>840</v>
+        <v>250</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>720</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>79</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>79</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4756,430 +4756,430 @@
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>19.87</v>
+        <v>11.54</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>8125</v>
+        <v>2100</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>9350</v>
+        <v>2320</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>7900</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>15.94</v>
+        <v>10.34</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>13800</v>
+        <v>348</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>16000</v>
+        <v>384</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>13975</v>
+        <v>354</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>10.59</v>
+        <v>11.41</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>89</v>
+        <v>1490</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>94</v>
+        <v>1660</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>86</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>21.97</v>
+        <v>11.83</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>865</v>
+        <v>187</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>1055</v>
+        <v>208</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>875</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>13.64</v>
+        <v>18.31</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>88</v>
+        <v>710</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>100</v>
+        <v>840</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>89</v>
+        <v>720</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.68</v>
+        <v>15.38</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.97</v>
+        <v>1.28</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>228</v>
+        <v>90</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>208</v>
+        <v>79</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>20</v>
+        <v>19.87</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>406</v>
+        <v>8125</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>432</v>
+        <v>9350</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>362</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>22.58</v>
+        <v>15.94</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.54</v>
+        <v>1.27</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>1910</v>
+        <v>13800</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2280</v>
+        <v>16000</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1870</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>12.87</v>
+        <v>10.59</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>10.76</v>
+        <v>21.97</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>865</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>3500</v>
+        <v>1055</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>3160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>12.78</v>
+        <v>13.64</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2640</v>
+        <v>88</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>2660</v>
+        <v>89</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>17.5</v>
+        <v>10.68</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>28.48</v>
+        <v>20</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>152</v>
+        <v>406</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>14.43</v>
+        <v>22.58</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>-0.52</v>
+        <v>0.54</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>2020</v>
+        <v>1910</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2220</v>
+        <v>2280</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1930</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>18.04</v>
+        <v>10.76</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>332.87</v>
+        <v>3500</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>280</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>29.27</v>
+        <v>12.78</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>85</v>
+        <v>2640</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>106</v>
+        <v>3000</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>81</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5188,187 +5188,187 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>10.17</v>
+        <v>28.48</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>2400</v>
+        <v>152</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>2600</v>
+        <v>194</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>2330</v>
+        <v>151</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>14.29</v>
+        <v>12.87</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>11.24</v>
+        <v>17.5</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F178" s="3" t="n">
         <v>188</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>16.02</v>
+        <v>14.43</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.52</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>181</v>
+        <v>2020</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>210</v>
+        <v>2220</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>177</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>10.49</v>
+        <v>18.04</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-2.47</v>
+        <v>-0.71</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>358</v>
+        <v>332.87</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>316</v>
+        <v>280</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>11.19</v>
+        <v>29.27</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.22</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>420</v>
+        <v>85</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>398</v>
+        <v>81</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>15.31</v>
+        <v>10.17</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.27</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>169</v>
+        <v>2400</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>226</v>
+        <v>2600</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>191</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5377,106 +5377,106 @@
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>17.36</v>
+        <v>14.29</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.43</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>720</v>
+        <v>70</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>845</v>
+        <v>80</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>700</v>
+        <v>69</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>10.1</v>
+        <v>11.24</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.78</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>10300</v>
+        <v>169</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>10900</v>
+        <v>188</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>9600</v>
+        <v>166</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>10.65</v>
+        <v>16.02</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.21</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>458</v>
+        <v>181</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>478</v>
+        <v>210</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>418</v>
+        <v>177</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>18.05</v>
+        <v>10.49</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.47</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>2700</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>3140</v>
+        <v>358</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>2550</v>
+        <v>316</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5485,52 +5485,52 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>19.31</v>
+        <v>11.19</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.52</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>149</v>
+        <v>420</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>173</v>
+        <v>454</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>139</v>
+        <v>398</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>21.99</v>
+        <v>15.31</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-4.26</v>
+        <v>-2.55</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>135</v>
+        <v>191</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5539,322 +5539,322 @@
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>13.82</v>
+        <v>17.36</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.78</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="F189" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="G189" s="3" t="n">
         <v>700</v>
-      </c>
-      <c r="G189" s="3" t="n">
-        <v>585</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>11.11</v>
+        <v>10.1</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>83</v>
+        <v>10300</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>90</v>
+        <v>10900</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>77</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>23.53</v>
+        <v>19.31</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>700</v>
+        <v>149</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>840</v>
+        <v>173</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>645</v>
+        <v>139</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>13.58</v>
+        <v>18.05</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>162</v>
+        <v>2700</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>184</v>
+        <v>3140</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>153</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>10.5</v>
+        <v>21.99</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.26</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>1175</v>
+        <v>172</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>1210</v>
+        <v>172</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>1025</v>
+        <v>135</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>16.8</v>
+        <v>13.82</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.88</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>2500</v>
+        <v>675</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>2920</v>
+        <v>700</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>2330</v>
+        <v>585</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>10.67</v>
+        <v>11.11</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-7.33</v>
+        <v>-4.94</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>15.79</v>
+        <v>10.19</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.1</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>835</v>
+        <v>346</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>880</v>
+        <v>346</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>700</v>
+        <v>298</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>20.41</v>
+        <v>23.53</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.15</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>118</v>
+        <v>840</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>90</v>
+        <v>645</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>12.73</v>
+        <v>13.58</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.56</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>24.62</v>
+        <v>10.5</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.39</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>1600</v>
+        <v>1175</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>1620</v>
+        <v>1210</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1190</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5863,79 +5863,79 @@
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>21.43</v>
+        <v>16.8</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.8</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>83</v>
+        <v>2500</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>85</v>
+        <v>2920</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>64</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>18.95</v>
+        <v>10.67</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-8.77</v>
+        <v>-7.33</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>8475</v>
+        <v>152</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>8475</v>
+        <v>166</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>6500</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>24.44</v>
+        <v>15.79</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>91</v>
+        <v>835</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>112</v>
+        <v>880</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>82</v>
+        <v>700</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5944,531 +5944,693 @@
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>20.81</v>
+        <v>20.41</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.16</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>432</v>
+        <v>100</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>505</v>
+        <v>118</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>18.18</v>
+        <v>12.73</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-11.93</v>
+        <v>-8.18</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>16.35</v>
+        <v>24.62</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>91</v>
+        <v>1600</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>91</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>30.37</v>
+        <v>21.43</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.57</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>19.33</v>
+        <v>18.95</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.77</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>127</v>
+        <v>8475</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>102</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>16.36</v>
+        <v>24.44</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>141</v>
+        <v>82</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>15.1</v>
+        <v>20.81</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-14.58</v>
+        <v>-9.09</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>432</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>12.36</v>
+        <v>18.18</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-14.61</v>
+        <v>-11.93</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>860</v>
+        <v>180</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>1000</v>
+        <v>208</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>760</v>
+        <v>155</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>18.87</v>
+        <v>16.35</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.5</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>16.38</v>
+        <v>30.37</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.07</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>142</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>24.77</v>
+        <v>16.36</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.55</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>1810</v>
+        <v>175</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>2040</v>
+        <v>192</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>1395</v>
+        <v>141</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>17.21</v>
+        <v>15.1</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.58</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>132</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>104</v>
+        <v>328</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>11.83</v>
+        <v>12.36</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.61</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>378</v>
+        <v>1000</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>288</v>
+        <v>760</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>20.37</v>
+        <v>18.87</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.62</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>15.94</v>
+        <v>16.38</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.66</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>2760</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>3200</v>
+        <v>540</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>2350</v>
+        <v>396</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>25</v>
+        <v>19.27</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>14.05</v>
+        <v>24.77</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>115</v>
+        <v>1810</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>138</v>
+        <v>2040</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>103</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>18.44</v>
+        <v>17.21</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.75</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G225" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
+      <c r="C229" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D223" s="2" t="n">
+      <c r="D229" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E223" s="3" t="n">
+      <c r="E229" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F223" s="3" t="n">
+      <c r="F229" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G223" s="3" t="n">
+      <c r="G229" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,57 +598,57 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>165</v>
+        <v>460</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>202</v>
+        <v>545</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>200</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>33.62</v>
+        <v>26.25</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -658,13 +658,13 @@
         <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>460</v>
+        <v>268</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>545</v>
+        <v>290</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>545</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -697,169 +697,169 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>24.88</v>
+        <v>33.62</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1170</v>
+        <v>119</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1255</v>
+        <v>155</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1255</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4120</v>
+        <v>1170</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3070</v>
+        <v>4114.81103515625</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>525</v>
+        <v>3070</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1625</v>
+        <v>525</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24.6</v>
+        <v>24.69</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24.6</v>
+        <v>24.69</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>750</v>
+        <v>1625</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>785</v>
+        <v>2020</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>785</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -868,25 +868,25 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>685</v>
+        <v>785</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>685</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -895,673 +895,673 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>24.41</v>
+        <v>24.55</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24.41</v>
+        <v>24.55</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>440</v>
+        <v>550</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>525</v>
+        <v>685</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>525</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>26.02</v>
+        <v>24.41</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>24.39</v>
+        <v>24.41</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>125</v>
+        <v>440</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>155</v>
+        <v>525</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>153</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>25</v>
+        <v>26.02</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>24.09</v>
+        <v>24.39</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1185</v>
+        <v>125</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1375</v>
+        <v>155</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1365</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>24.76</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>22.8</v>
+        <v>24.09</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3830</v>
+        <v>1185</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3830</v>
+        <v>1375</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3770</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>21.95</v>
+        <v>24.76</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>21.95</v>
+        <v>22.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2870</v>
+        <v>3830</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3500</v>
+        <v>3830</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3500</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>24.75</v>
+        <v>21.95</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>21.78</v>
+        <v>21.95</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2490</v>
+        <v>2870</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2520</v>
+        <v>3500</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2460</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>24.68</v>
+        <v>24.75</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>21.04</v>
+        <v>21.78</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1930</v>
+        <v>2490</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2400</v>
+        <v>2520</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2330</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>24.86</v>
+        <v>24.68</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20.23</v>
+        <v>21.04</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1685</v>
+        <v>1930</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2160</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2080</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>20.2</v>
+        <v>24.86</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1535</v>
+        <v>1685</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1845</v>
+        <v>2160</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1845</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6550</v>
+        <v>1535</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>12125</v>
+        <v>6550</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5950</v>
+        <v>12125</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6300</v>
+        <v>5950</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>24.7</v>
+        <v>19.68</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>19.52</v>
+        <v>19.68</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1565</v>
+        <v>6300</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1565</v>
+        <v>7450</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1500</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>24.57</v>
+        <v>24.7</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>19.43</v>
+        <v>19.52</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>430</v>
+        <v>1565</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>436</v>
+        <v>1565</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>418</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>33.79</v>
+        <v>24.57</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>18.62</v>
+        <v>19.43</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>149</v>
+        <v>430</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>172</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>21.31</v>
+        <v>34.19</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>17.21</v>
+        <v>17.95</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>635</v>
+        <v>126</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>740</v>
+        <v>157</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>715</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1570,619 +1570,619 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>20.78</v>
+        <v>22.5</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2550</v>
+        <v>78</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>3080</v>
+        <v>98</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2930</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>31.46</v>
+        <v>20.78</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>95</v>
+        <v>2550</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>117</v>
+        <v>3080</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>102</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>20.92</v>
+        <v>17.27</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>13.07</v>
+        <v>13.64</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1525</v>
+        <v>550</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1850</v>
+        <v>645</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1730</v>
+        <v>625</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>12.78</v>
+        <v>20.92</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>358</v>
+        <v>1525</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>406</v>
+        <v>1850</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>406</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>14.49</v>
+        <v>17.72</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>12.32</v>
+        <v>12.66</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>16.42</v>
+        <v>14.49</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11.94</v>
+        <v>12.32</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>19.05</v>
+        <v>12.73</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11.9</v>
+        <v>12.12</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>86</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>94</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>23.08</v>
+        <v>16.42</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>390</v>
+        <v>135</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>436</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>131</v>
+        <v>390</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2191,2347 +2191,2345 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>16.44</v>
+        <v>14.73</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>74</v>
+        <v>1955</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>85</v>
+        <v>2220</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>81</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>22.64</v>
+        <v>16.44</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>770</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>815</v>
+        <v>585</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>810</v>
+        <v>585</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>19.77</v>
+        <v>10.88</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>179</v>
+        <v>770</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>212</v>
+        <v>815</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>13.04</v>
+        <v>21.1</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>17.09</v>
+        <v>14.68</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>9.49</v>
+        <v>10.09</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>316</v>
+        <v>545</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>370</v>
+        <v>625</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>346</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>11.72</v>
+        <v>19.77</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>25.18</v>
+        <v>13.04</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9.35</v>
+        <v>9.57</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>141</v>
+        <v>580</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>174</v>
+        <v>650</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>152</v>
+        <v>630</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>11.4</v>
+        <v>17.09</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9.33</v>
+        <v>9.49</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>422</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>13.95</v>
+        <v>11.72</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>20500</v>
+        <v>128</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>24500</v>
+        <v>143</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>23500</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>16.67</v>
+        <v>25.18</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2820</v>
+        <v>141</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>3290</v>
+        <v>174</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>3080</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>22.73</v>
+        <v>11.4</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>216</v>
+        <v>430</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>192</v>
+        <v>422</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>11</v>
+        <v>13.95</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>104</v>
+        <v>20500</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>111</v>
+        <v>24500</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>109</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>28.09</v>
+        <v>16.67</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>8.99</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>177</v>
+        <v>2820</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>228</v>
+        <v>3290</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>194</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1085</v>
+        <v>176</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1325</v>
+        <v>216</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>372</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>16.1</v>
+        <v>28.09</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>10.19</v>
+        <v>15.2</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>117</v>
+        <v>372</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>24.57</v>
+        <v>16.1</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2600</v>
+        <v>120</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>3600</v>
+        <v>137</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>945</v>
+        <v>109</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1035</v>
+        <v>119</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1015</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>12.17</v>
+        <v>24.57</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>7.83</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>230</v>
+        <v>2600</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>258</v>
+        <v>3600</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>248</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F96" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G96" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>23.46</v>
+        <v>12.17</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>7.41</v>
+        <v>7.83</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>174</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>15.62</v>
+        <v>23.46</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>14</v>
+        <v>11.76</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>7</v>
+        <v>7.35</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>17.44</v>
+        <v>22.86</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>140</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>19.4</v>
+        <v>15.62</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>6.97</v>
+        <v>7.03</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>408</v>
+        <v>130</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>480</v>
+        <v>148</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>430</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>15.53</v>
+        <v>19.4</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>6.8</v>
+        <v>6.97</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>110</v>
+        <v>430</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>23.33</v>
+        <v>24.86</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>148</v>
+        <v>2260</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>128</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>16</v>
+        <v>22.32</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>87</v>
+        <v>570</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>10.94</v>
+        <v>16</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>11.92</v>
+        <v>25</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>16.67</v>
+        <v>10.94</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>605</v>
+        <v>69</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>700</v>
+        <v>71</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>5.13</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>11.61</v>
+        <v>10.6</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="E131" s="3" t="n">
+        <v>148.9599964769581</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G131" s="3" t="n">
         <v>158</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>162</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>13.04</v>
+        <v>24.91</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.35</v>
+        <v>4.56</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>1425</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>260</v>
+        <v>1780</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>240</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>20.56</v>
+        <v>19.77</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4.23</v>
+        <v>4.52</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1980</v>
+        <v>177</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>2140</v>
+        <v>212</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>1850</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>15</v>
+        <v>11.61</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>104</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>23.66</v>
+        <v>11.97</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>118</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>460</v>
+        <v>131</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>11.83</v>
+        <v>12.45</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>95</v>
+        <v>545</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>104</v>
+        <v>560</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>96</v>
+        <v>515</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>14.71</v>
+        <v>11.83</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.89</v>
+        <v>11.41</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>288</v>
+        <v>2080</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>320</v>
+        <v>2100</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>294</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>12.15</v>
+        <v>11.63</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>109</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>110</v>
+        <v>177</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>16.7</v>
+        <v>11.57</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>5200</v>
+        <v>1210</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>5450</v>
+        <v>1350</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>4800</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>14.62</v>
+        <v>12.15</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>2550</v>
+        <v>109</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>2900</v>
+        <v>120</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2600</v>
+        <v>110</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4540,79 +4538,79 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>10.16</v>
+        <v>11.89</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>10.39</v>
+        <v>16.7</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>78</v>
+        <v>5200</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>85</v>
+        <v>5450</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>79</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>17.95</v>
+        <v>14.62</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>79</v>
+        <v>2550</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>92</v>
+        <v>2900</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>80</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4621,79 +4619,79 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>17.44</v>
+        <v>10.16</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>87</v>
+        <v>172</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>88</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>12.36</v>
+        <v>10.39</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>11.75</v>
+        <v>17.95</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>79</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>3900</v>
+        <v>92</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>3560</v>
+        <v>80</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4702,532 +4700,532 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>89</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>10.34</v>
+        <v>14</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>348</v>
+        <v>202</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>384</v>
+        <v>228</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>11.41</v>
+        <v>25</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>1490</v>
+        <v>208</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>1660</v>
+        <v>250</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1515</v>
+        <v>204</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>11.83</v>
+        <v>14.29</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>187</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>189</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>18.31</v>
+        <v>11.54</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>710</v>
+        <v>2100</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>840</v>
+        <v>2320</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>720</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>15.38</v>
+        <v>10.34</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>90</v>
+        <v>384</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>79</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>19.87</v>
+        <v>11.41</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>8125</v>
+        <v>1490</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>9350</v>
+        <v>1660</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>7900</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>15.94</v>
+        <v>11.83</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>13800</v>
+        <v>187</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>16000</v>
+        <v>208</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>13975</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>10.59</v>
+        <v>18.31</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>89</v>
+        <v>710</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>94</v>
+        <v>840</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>86</v>
+        <v>720</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>13.64</v>
+        <v>15.38</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>10.68</v>
+        <v>15.94</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>210</v>
+        <v>13800</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>228</v>
+        <v>16000</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>208</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>20</v>
+        <v>10.59</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>406</v>
+        <v>89</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>432</v>
+        <v>94</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>362</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>10.76</v>
+        <v>13.64</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>88</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>3160</v>
+        <v>89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>12.78</v>
+        <v>10.68</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2640</v>
+        <v>210</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>3000</v>
+        <v>228</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2660</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>28.48</v>
+        <v>20</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>152</v>
+        <v>406</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>12.87</v>
+        <v>22.58</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>93</v>
+        <v>1910</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>114</v>
+        <v>2280</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>101</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="178">
@@ -5260,277 +5258,277 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>14.43</v>
+        <v>12.87</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2020</v>
+        <v>93</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>2220</v>
+        <v>114</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>1930</v>
+        <v>101</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>18.04</v>
+        <v>12.38</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>108</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>332.87</v>
+        <v>118</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>280</v>
+        <v>105</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>29.27</v>
+        <v>28.48</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>10.17</v>
+        <v>12.78</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2400</v>
+        <v>2640</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2330</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>14.29</v>
+        <v>10.76</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>70</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>80</v>
+        <v>3500</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>69</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>11.24</v>
+        <v>14.43</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.52</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>169</v>
+        <v>2020</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>188</v>
+        <v>2220</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>166</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>16.02</v>
+        <v>18.04</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>181</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>210</v>
+        <v>332.87</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>10.49</v>
+        <v>29.27</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.22</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>85</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>316</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>11.19</v>
+        <v>10.17</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.27</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>420</v>
+        <v>2400</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>454</v>
+        <v>2600</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>398</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>15.31</v>
+        <v>14.29</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5539,79 +5537,79 @@
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>17.36</v>
+        <v>11.24</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.78</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>720</v>
+        <v>169</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>845</v>
+        <v>188</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>700</v>
+        <v>166</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>10.1</v>
+        <v>16.02</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.21</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>10300</v>
+        <v>181</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>10900</v>
+        <v>210</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>9600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>10.65</v>
+        <v>10.49</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.47</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>458</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>478</v>
+        <v>358</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>418</v>
+        <v>316</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5620,403 +5618,403 @@
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>19.31</v>
+        <v>11.19</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.52</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>149</v>
+        <v>420</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>173</v>
+        <v>454</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>139</v>
+        <v>398</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>18.05</v>
+        <v>15.31</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.55</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>2700</v>
+        <v>169</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>3140</v>
+        <v>226</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>2550</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>21.99</v>
+        <v>17.36</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-4.26</v>
+        <v>-2.78</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>172</v>
+        <v>720</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>172</v>
+        <v>845</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>135</v>
+        <v>700</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>13.82</v>
+        <v>10.1</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-4.88</v>
+        <v>-3.03</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>675</v>
+        <v>10300</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>700</v>
+        <v>10900</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>585</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>11.11</v>
+        <v>10.65</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.24</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>90</v>
+        <v>478</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>77</v>
+        <v>418</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>10.19</v>
+        <v>14.84</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.53</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>346</v>
+        <v>2980</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>346</v>
+        <v>3250</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>298</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>23.53</v>
+        <v>19.31</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>700</v>
+        <v>149</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>840</v>
+        <v>173</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>645</v>
+        <v>139</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>13.58</v>
+        <v>18.05</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>162</v>
+        <v>2700</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>184</v>
+        <v>3140</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>153</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>10.5</v>
+        <v>21.99</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.26</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>1175</v>
+        <v>172</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>1210</v>
+        <v>172</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1025</v>
+        <v>135</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>16.8</v>
+        <v>13.82</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.88</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>2500</v>
+        <v>675</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>2920</v>
+        <v>700</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>2330</v>
+        <v>585</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>10.67</v>
+        <v>11.11</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-7.33</v>
+        <v>-4.94</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>15.79</v>
+        <v>10.19</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.1</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>835</v>
+        <v>346</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>880</v>
+        <v>346</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>700</v>
+        <v>298</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>20.41</v>
+        <v>23.53</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.15</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>118</v>
+        <v>840</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>90</v>
+        <v>645</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>12.73</v>
+        <v>13.58</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.56</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>24.62</v>
+        <v>10.5</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.39</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>1600</v>
+        <v>1175</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1620</v>
+        <v>1210</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>1190</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6025,79 +6023,79 @@
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>21.43</v>
+        <v>16.8</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.8</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>83</v>
+        <v>2500</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>85</v>
+        <v>2920</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>64</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>18.95</v>
+        <v>10.67</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-8.77</v>
+        <v>-7.33</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>8475</v>
+        <v>152</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>8475</v>
+        <v>166</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>6500</v>
+        <v>139</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>24.44</v>
+        <v>15.79</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>91</v>
+        <v>787.2857142857142</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>112</v>
+        <v>880</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>82</v>
+        <v>700</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6106,531 +6104,693 @@
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>20.81</v>
+        <v>20.41</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.16</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>432</v>
+        <v>100</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>505</v>
+        <v>118</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>18.18</v>
+        <v>12.73</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-11.93</v>
+        <v>-8.18</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>16.35</v>
+        <v>24.62</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>91</v>
+        <v>1600</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>91</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>30.37</v>
+        <v>21.43</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.57</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>19.33</v>
+        <v>18.95</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.77</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>127</v>
+        <v>8475</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>102</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>16.36</v>
+        <v>24.44</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>141</v>
+        <v>82</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>15.1</v>
+        <v>20.81</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-14.58</v>
+        <v>-9.09</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>432</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>12.36</v>
+        <v>18.18</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-14.61</v>
+        <v>-11.93</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>847.9298015393708</v>
+        <v>180</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>1000</v>
+        <v>208</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>760</v>
+        <v>155</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>18.87</v>
+        <v>16.35</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.5</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>16.38</v>
+        <v>30.37</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.07</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>142</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>24.77</v>
+        <v>16.36</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.55</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>1810</v>
+        <v>175</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>2040</v>
+        <v>192</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>1395</v>
+        <v>141</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>17.21</v>
+        <v>15.1</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.58</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>132</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>104</v>
+        <v>328</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>11.83</v>
+        <v>12.36</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.61</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>378</v>
+        <v>1000</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>288</v>
+        <v>760</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>20.37</v>
+        <v>18.87</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.62</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>15.94</v>
+        <v>16.38</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.66</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>2760</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>3200</v>
+        <v>540</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>2350</v>
+        <v>396</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>14.05</v>
+        <v>19.27</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>103</v>
+        <v>186</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>25</v>
+        <v>24.77</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>165</v>
+        <v>1810</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>210</v>
+        <v>2040</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>143</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>18.44</v>
+        <v>17.21</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.75</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G229" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G233" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
+      <c r="C235" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D229" s="2" t="n">
+      <c r="D235" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E229" s="3" t="n">
+      <c r="E235" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F229" s="3" t="n">
+      <c r="F235" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G229" s="3" t="n">
+      <c r="G235" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -616,28 +616,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26.25</v>
+        <v>33.62</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -670,55 +670,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>165</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>975</v>
+        <v>202</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>975</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>119</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>155</v>
+        <v>975</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>145</v>
+        <v>975</v>
       </c>
     </row>
     <row r="11">
@@ -1252,7 +1252,7 @@
         <v>19.68</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6300</v>
+        <v>5906.778523489933</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>7450</v>
@@ -1453,142 +1453,142 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>21.31</v>
+        <v>24.4</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.21</v>
+        <v>17.87</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>635</v>
+        <v>416</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>740</v>
+        <v>515</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>715</v>
+        <v>488</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1597,646 +1597,646 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>20.78</v>
+        <v>22.5</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2550</v>
+        <v>78</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3080</v>
+        <v>98</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2930</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>31.46</v>
+        <v>20.78</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>95</v>
+        <v>2550</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>117</v>
+        <v>3080</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>102</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>20.92</v>
+        <v>17.27</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>13.07</v>
+        <v>13.64</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1525</v>
+        <v>550</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1850</v>
+        <v>645</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1730</v>
+        <v>625</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>12.78</v>
+        <v>17.93</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>12.78</v>
+        <v>13.1</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>406</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>17.72</v>
+        <v>20.92</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>12.66</v>
+        <v>13.07</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>80</v>
+        <v>1525</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>93</v>
+        <v>1850</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>89</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>14.49</v>
+        <v>17.72</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>12.32</v>
+        <v>12.66</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>16.42</v>
+        <v>14.49</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11.94</v>
+        <v>12.32</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>19.05</v>
+        <v>12.73</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11.9</v>
+        <v>12.12</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>86</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>94</v>
+        <v>370</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>23.08</v>
+        <v>16.42</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>390</v>
+        <v>135</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>436</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>131</v>
+        <v>390</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2245,2372 +2245,2372 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>22.5</v>
+        <v>30.41</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>89</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>30.34</v>
+        <v>16.39</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11.24</v>
+        <v>11.48</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>14.73</v>
+        <v>12.38</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>11.11</v>
+        <v>11.39</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1955</v>
+        <v>406</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2220</v>
+        <v>454</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>12.67</v>
+        <v>22.5</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1515</v>
+        <v>83</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1690</v>
+        <v>98</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1665</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>16.44</v>
+        <v>30.34</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10.96</v>
+        <v>11.24</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>22.48</v>
+        <v>14.73</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10.85</v>
+        <v>11.11</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>130</v>
+        <v>1955</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>158</v>
+        <v>2220</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>143</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>22.64</v>
+        <v>12.67</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>106</v>
+        <v>1515</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>130</v>
+        <v>1690</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>117</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>10.38</v>
+        <v>16.44</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>74</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>585</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>18.18</v>
+        <v>22.48</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10.23</v>
+        <v>10.85</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>97</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>770</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>815</v>
+        <v>585</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>810</v>
+        <v>585</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>21.1</v>
+        <v>22.64</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>10.09</v>
+        <v>10.38</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>550</v>
+        <v>106</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>660</v>
+        <v>130</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>600</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>19.77</v>
+        <v>10.88</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>179</v>
+        <v>770</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>212</v>
+        <v>815</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>194</v>
+        <v>810</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>13.04</v>
+        <v>21.1</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>17.09</v>
+        <v>14.68</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9.49</v>
+        <v>10.09</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>316</v>
+        <v>545</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>370</v>
+        <v>625</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>346</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>11.72</v>
+        <v>19.77</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>25.18</v>
+        <v>13.04</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9.35</v>
+        <v>9.57</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>141</v>
+        <v>580</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>174</v>
+        <v>650</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>152</v>
+        <v>630</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>11.4</v>
+        <v>17.09</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9.33</v>
+        <v>9.49</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>422</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>13.95</v>
+        <v>11.72</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>20500</v>
+        <v>128</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>24500</v>
+        <v>143</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>23500</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>16.67</v>
+        <v>25.18</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2820</v>
+        <v>141</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3290</v>
+        <v>174</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>3080</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>22.73</v>
+        <v>11.4</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>216</v>
+        <v>430</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>192</v>
+        <v>422</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>11</v>
+        <v>13.95</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>104</v>
+        <v>20500</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>111</v>
+        <v>24500</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>109</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>28.09</v>
+        <v>16.67</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>8.99</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>177</v>
+        <v>2820</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>228</v>
+        <v>3290</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>194</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1085</v>
+        <v>176</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1325</v>
+        <v>216</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>1175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>372</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>16.1</v>
+        <v>28.09</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>10.19</v>
+        <v>15.2</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>117</v>
+        <v>372</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>24.57</v>
+        <v>16.1</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>2600</v>
+        <v>120</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>3600</v>
+        <v>137</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>3130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>945</v>
+        <v>109</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1035</v>
+        <v>119</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1015</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>12.17</v>
+        <v>24.57</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>7.83</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>230</v>
+        <v>2600</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>258</v>
+        <v>3600</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>248</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>16.35</v>
+        <v>14.29</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F99" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G99" s="3" t="n">
         <v>121</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>112</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>13.38</v>
+        <v>10.11</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>7.48</v>
+        <v>7.98</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>4410</v>
+        <v>945</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>5000</v>
+        <v>1035</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>4740</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>10.05</v>
+        <v>12.17</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>7.41</v>
+        <v>7.83</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>372</v>
+        <v>230</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>416</v>
+        <v>258</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>406</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>23.46</v>
+        <v>16.35</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>22.86</v>
+        <v>23.46</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>15.62</v>
+        <v>10.05</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>130</v>
+        <v>372</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>148</v>
+        <v>416</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>137</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>14</v>
+        <v>11.76</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7</v>
+        <v>7.35</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>17.44</v>
+        <v>22.86</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>140</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>19.4</v>
+        <v>15.62</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>6.97</v>
+        <v>7.03</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>408</v>
+        <v>130</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>480</v>
+        <v>148</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>430</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>15.53</v>
+        <v>19.4</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>6.8</v>
+        <v>6.97</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>110</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>16</v>
+        <v>24.86</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>74</v>
+        <v>2260</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>87</v>
+        <v>2260</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>80</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>23.33</v>
+        <v>22.32</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>128</v>
+        <v>498</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>10.94</v>
+        <v>16</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>11.92</v>
+        <v>10.94</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>605</v>
+        <v>66</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>635</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>25</v>
+        <v>11.47</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>1095</v>
+        <v>3460</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1300</v>
+        <v>3790</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>1100</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="E127" s="3" t="inlineStr"/>
+        <v>5.32</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>103</v>
+      </c>
       <c r="F127" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>5.13</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>24.91</v>
+        <v>13.33</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1425</v>
+        <v>2750</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>1780</v>
+        <v>2890</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>1490</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>11.61</v>
+        <v>10.6</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="E134" s="3" t="n">
+        <v>148.9599964769581</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G134" s="3" t="n">
         <v>158</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>13.04</v>
+        <v>24.91</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.35</v>
+        <v>4.56</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>1425</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>260</v>
+        <v>1780</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>240</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>20.56</v>
+        <v>11.61</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>4.23</v>
+        <v>4.52</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>1980</v>
+        <v>158</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>2140</v>
+        <v>173</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>1850</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>15.09</v>
+        <v>13.04</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>159</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>12.69</v>
+        <v>20.56</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3.73</v>
+        <v>4.23</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>151</v>
+        <v>2140</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>139</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>23.66</v>
+        <v>11.97</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>118</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>460</v>
+        <v>131</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>11.83</v>
+        <v>12.45</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>95</v>
+        <v>545</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>104</v>
+        <v>560</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>96</v>
+        <v>515</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>30.95</v>
+        <v>17.21</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>141</v>
+        <v>615</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>165</v>
+        <v>715</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>34.34</v>
+        <v>23.66</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>133</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>14.71</v>
+        <v>11.83</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.41</v>
+        <v>30.95</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>2080</v>
+        <v>141</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>2100</v>
+        <v>165</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>1940</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>11.63</v>
+        <v>34.34</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>133</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>11.57</v>
+        <v>14.71</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1210</v>
+        <v>70</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1350</v>
+        <v>78</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1245</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>12.15</v>
+        <v>17.65</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>11.89</v>
+        <v>11.41</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>288</v>
+        <v>2080</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>320</v>
+        <v>2100</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>294</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>16.7</v>
+        <v>11.63</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>5200</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>5450</v>
+        <v>192</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>4800</v>
+        <v>177</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>14.62</v>
+        <v>11.57</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2550</v>
+        <v>1210</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>2900</v>
+        <v>1350</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2600</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4619,79 +4619,79 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>10.16</v>
+        <v>11.89</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>10.39</v>
+        <v>12.15</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>17.95</v>
+        <v>16.7</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>79</v>
+        <v>5200</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>92</v>
+        <v>5450</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>80</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4700,106 +4700,106 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>17.44</v>
+        <v>14.62</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>87</v>
+        <v>2550</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>88</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>12.36</v>
+        <v>10.16</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>11.75</v>
+        <v>10.39</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>78</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>3900</v>
+        <v>85</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>3560</v>
+        <v>79</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>14</v>
+        <v>17.95</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4808,79 +4808,79 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>25</v>
+        <v>17.44</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>204</v>
+        <v>88</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>14.29</v>
+        <v>12.36</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>89</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2070</v>
+        <v>91</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2100</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2320</v>
+        <v>3900</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>2120</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4889,592 +4889,592 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>10.34</v>
+        <v>25</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>354</v>
+        <v>204</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>11.41</v>
+        <v>14</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1490</v>
+        <v>202</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1660</v>
+        <v>228</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1515</v>
+        <v>204</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>11.83</v>
+        <v>14.29</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>187</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>208</v>
+        <v>2320</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>189</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>18.31</v>
+        <v>11.54</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>710</v>
+        <v>2100</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>840</v>
+        <v>2320</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>720</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>19.87</v>
+        <v>10.34</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>8125</v>
+        <v>348</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>9350</v>
+        <v>384</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>7900</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>15.38</v>
+        <v>11.41</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>79</v>
+        <v>1490</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>90</v>
+        <v>1660</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>79</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>15.94</v>
+        <v>11.83</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>13800</v>
+        <v>187</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>16000</v>
+        <v>208</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>13975</v>
+        <v>189</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>10.59</v>
+        <v>18.31</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>89</v>
+        <v>710</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>94</v>
+        <v>840</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>86</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>21.97</v>
+        <v>19.87</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>865</v>
+        <v>8125</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>1055</v>
+        <v>9350</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>875</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>13.64</v>
+        <v>15.38</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>10.68</v>
+        <v>15.94</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>210</v>
+        <v>13800</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>228</v>
+        <v>16000</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>208</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>20</v>
+        <v>10.59</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>406</v>
+        <v>89</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>432</v>
+        <v>94</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>362</v>
+        <v>86</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>22.58</v>
+        <v>21.97</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>1910</v>
+        <v>865</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>2280</v>
+        <v>1055</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>1870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>17.5</v>
+        <v>13.64</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>12.87</v>
+        <v>10.68</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>101</v>
+        <v>208</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>12.38</v>
+        <v>20</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>108</v>
+        <v>406</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>118</v>
+        <v>432</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>105</v>
+        <v>362</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>28.48</v>
+        <v>22.58</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>152</v>
+        <v>1910</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>194</v>
+        <v>2280</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>151</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>12.78</v>
+        <v>12.38</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>2640</v>
+        <v>108</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>3000</v>
+        <v>118</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2660</v>
+        <v>105</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>10.76</v>
+        <v>12.78</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>2640</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>3160</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>14.43</v>
+        <v>17.5</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>2020</v>
+        <v>163</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>2220</v>
+        <v>188</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>1930</v>
+        <v>160</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>18.04</v>
+        <v>12.87</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>93</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>332.87</v>
+        <v>114</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>280</v>
+        <v>101</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>29.27</v>
+        <v>10.76</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>85</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>106</v>
+        <v>3500</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>81</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5483,187 +5483,187 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>10.17</v>
+        <v>28.48</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>2400</v>
+        <v>152</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>2600</v>
+        <v>194</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>2330</v>
+        <v>151</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>14.29</v>
+        <v>11.79</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.51</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>69</v>
+        <v>388</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>11.24</v>
+        <v>14.43</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.52</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>169</v>
+        <v>2017.782805922118</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>188</v>
+        <v>2220</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>166</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>16.02</v>
+        <v>18.04</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>181</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>210</v>
+        <v>332.87</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>10.49</v>
+        <v>29.27</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.22</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>85</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>316</v>
+        <v>81</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>11.19</v>
+        <v>10.17</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.27</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>420</v>
+        <v>2400</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>454</v>
+        <v>2600</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>398</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>15.31</v>
+        <v>14.29</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5672,241 +5672,241 @@
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>17.36</v>
+        <v>11.24</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.78</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>720</v>
+        <v>169</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>845</v>
+        <v>188</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>700</v>
+        <v>166</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>10.1</v>
+        <v>16.02</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-3.03</v>
+        <v>-2.21</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>10300</v>
+        <v>181</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>10900</v>
+        <v>210</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>9600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>10.65</v>
+        <v>10.49</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.47</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>458</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>478</v>
+        <v>358</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>418</v>
+        <v>316</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>14.84</v>
+        <v>11.19</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-3.53</v>
+        <v>-2.52</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>2980</v>
+        <v>420</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>3250</v>
+        <v>454</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>2730</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>19.31</v>
+        <v>15.31</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.55</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>139</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>18.05</v>
+        <v>17.36</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.78</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>2700</v>
+        <v>720</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>3140</v>
+        <v>845</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>2550</v>
+        <v>700</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>21.99</v>
+        <v>10.1</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-4.26</v>
+        <v>-3.03</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>172</v>
+        <v>10300</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>172</v>
+        <v>10900</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>135</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>13.82</v>
+        <v>10.65</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-4.88</v>
+        <v>-3.24</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>675</v>
+        <v>458</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>700</v>
+        <v>478</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>585</v>
+        <v>418</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>11.11</v>
+        <v>14.84</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.53</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>83</v>
+        <v>2980</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>90</v>
+        <v>3250</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>77</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5915,187 +5915,187 @@
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>10.19</v>
+        <v>19.31</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-5.1</v>
+        <v>-4.14</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>346</v>
+        <v>149</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>298</v>
+        <v>139</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>23.53</v>
+        <v>18.05</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-5.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>700</v>
+        <v>2700</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>840</v>
+        <v>3140</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>645</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>13.58</v>
+        <v>21.99</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.26</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>10.5</v>
+        <v>13.82</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.88</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>1175</v>
+        <v>675</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1210</v>
+        <v>700</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>1025</v>
+        <v>585</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>16.8</v>
+        <v>11.11</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.94</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>2500</v>
+        <v>83</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>2920</v>
+        <v>90</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>2330</v>
+        <v>77</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>10.67</v>
+        <v>10.19</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.1</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>139</v>
+        <v>298</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>15.79</v>
+        <v>23.53</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.15</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>787.2857142857142</v>
+        <v>700</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>700</v>
+        <v>645</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6104,160 +6104,160 @@
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>20.41</v>
+        <v>13.58</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.56</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>90</v>
+        <v>153</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>12.73</v>
+        <v>10.5</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-8.18</v>
+        <v>-6.39</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>240</v>
+        <v>1175</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>248</v>
+        <v>1210</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>202</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>24.62</v>
+        <v>16.8</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.8</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>1620</v>
+        <v>2920</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>1190</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>21.43</v>
+        <v>11.36</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.82</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>18.95</v>
+        <v>10.67</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-8.77</v>
+        <v>-7.33</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>8475</v>
+        <v>152</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>8475</v>
+        <v>166</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>6500</v>
+        <v>139</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>24.44</v>
+        <v>15.79</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>91</v>
+        <v>787.2857142857142</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>112</v>
+        <v>880</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>82</v>
+        <v>700</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6266,531 +6266,693 @@
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>20.81</v>
+        <v>20.41</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-9.09</v>
+        <v>-8.16</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>432</v>
+        <v>100</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>505</v>
+        <v>118</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>18.18</v>
+        <v>12.73</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-11.93</v>
+        <v>-8.18</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>16.35</v>
+        <v>24.62</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>91</v>
+        <v>1600</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>91</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>30.37</v>
+        <v>21.43</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.57</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>19.33</v>
+        <v>18.95</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.77</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>127</v>
+        <v>8475</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>142</v>
+        <v>8475</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>102</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>16.36</v>
+        <v>24.44</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>141</v>
+        <v>82</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>15.1</v>
+        <v>20.81</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-14.58</v>
+        <v>-9.09</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>432</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>12.36</v>
+        <v>18.18</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>-14.61</v>
+        <v>-11.93</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>847.9298015393708</v>
+        <v>180</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>1000</v>
+        <v>208</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>760</v>
+        <v>155</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>18.87</v>
+        <v>16.35</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>-14.62</v>
+        <v>-12.5</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>16.38</v>
+        <v>30.37</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>-14.66</v>
+        <v>-14.07</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>142</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>24.77</v>
+        <v>16.36</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.55</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>1810</v>
+        <v>175</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>2040</v>
+        <v>192</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>1395</v>
+        <v>141</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>17.21</v>
+        <v>15.1</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.58</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>132</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>104</v>
+        <v>328</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>11.83</v>
+        <v>12.36</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.61</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>378</v>
+        <v>1000</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>288</v>
+        <v>760</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>20.37</v>
+        <v>18.87</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.62</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>15.94</v>
+        <v>16.38</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.66</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>2760</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>3200</v>
+        <v>540</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>2350</v>
+        <v>396</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>14.05</v>
+        <v>19.27</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>103</v>
+        <v>186</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>25</v>
+        <v>24.77</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.68</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>165</v>
+        <v>1810</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>210</v>
+        <v>2040</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>143</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>18.44</v>
+        <v>17.21</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.75</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G236" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D239" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D240" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G240" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="C241" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D235" s="2" t="n">
+      <c r="D241" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E235" s="3" t="n">
+      <c r="E241" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F235" s="3" t="n">
+      <c r="F241" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G235" s="3" t="n">
+      <c r="G241" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,109 +508,109 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34.16</v>
+        <v>34.33</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>34.16</v>
+        <v>34.33</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>216</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>216</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>32.99</v>
+        <v>34.16</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.99</v>
+        <v>34.16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>258</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>31.16</v>
+        <v>32.99</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>27.54</v>
+        <v>32.99</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>176</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25</v>
+        <v>31.16</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25</v>
+        <v>27.54</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>460</v>
+        <v>143</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>545</v>
+        <v>181</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>545</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -643,12 +643,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -658,51 +658,51 @@
         <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>268</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>290</v>
+        <v>975</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>290</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -712,208 +712,208 @@
         <v>25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>975</v>
+        <v>545</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>975</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24.88</v>
+        <v>26.25</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>24.88</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1170</v>
+        <v>165</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1255</v>
+        <v>202</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1255</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4114.81103515625</v>
+        <v>1170</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4120</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3070</v>
+        <v>4114.81103515625</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3070</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>525</v>
+        <v>3070</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>655</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24.69</v>
+        <v>24.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1625</v>
+        <v>525</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2020</v>
+        <v>655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>24.6</v>
+        <v>24.76</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.6</v>
+        <v>24.76</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>750</v>
+        <v>214</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>785</v>
+        <v>262</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>785</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>24.55</v>
+        <v>24.69</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24.55</v>
+        <v>24.69</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>550</v>
+        <v>1625</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>685</v>
+        <v>2020</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>685</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>CUAN.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -922,127 +922,127 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>24.41</v>
+        <v>24.6</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>24.41</v>
+        <v>24.6</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>440</v>
+        <v>750</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>525</v>
+        <v>785</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>525</v>
+        <v>785</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>26.02</v>
+        <v>24.55</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>24.39</v>
+        <v>24.55</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>125</v>
+        <v>550</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>155</v>
+        <v>685</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>153</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>25</v>
+        <v>24.41</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>24.09</v>
+        <v>24.41</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1185</v>
+        <v>440</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1375</v>
+        <v>525</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1365</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>24.76</v>
+        <v>26.02</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>22.8</v>
+        <v>24.39</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3830</v>
+        <v>125</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3830</v>
+        <v>155</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3770</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>21.95</v>
+        <v>25</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>21.95</v>
+        <v>24.09</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2870</v>
+        <v>1185</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3500</v>
+        <v>1375</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3500</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="23">
@@ -1053,83 +1053,83 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>24.75</v>
+        <v>24.76</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>21.78</v>
+        <v>22.8</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2490</v>
+        <v>3830</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2520</v>
+        <v>3830</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2460</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>24.68</v>
+        <v>21.95</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>21.04</v>
+        <v>21.95</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1930</v>
+        <v>2870</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2330</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>24.86</v>
+        <v>24.75</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>20.23</v>
+        <v>21.78</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1685</v>
+        <v>2490</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2160</v>
+        <v>2520</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2080</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1138,1213 +1138,1213 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>20.2</v>
+        <v>24.68</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>20.2</v>
+        <v>21.04</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1535</v>
+        <v>1930</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1845</v>
+        <v>2400</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1845</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20</v>
+        <v>24.3</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>20</v>
+        <v>20.56</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6550</v>
+        <v>615</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7800</v>
+        <v>665</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7800</v>
+        <v>645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>19.87</v>
+        <v>24.86</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>19.87</v>
+        <v>20.23</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>12125</v>
+        <v>1685</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>14025</v>
+        <v>2160</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>14025</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>19.75</v>
+        <v>20.2</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>19.75</v>
+        <v>20.2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5950</v>
+        <v>1535</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7125</v>
+        <v>1845</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7125</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>19.68</v>
+        <v>20</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>19.68</v>
+        <v>20</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5906.778523489933</v>
+        <v>6550</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>7450</v>
+        <v>7800</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7450</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>24.7</v>
+        <v>19.87</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>19.52</v>
+        <v>19.87</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1565</v>
+        <v>12125</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1565</v>
+        <v>14025</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1500</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>24.57</v>
+        <v>19.75</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.43</v>
+        <v>19.75</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>430</v>
+        <v>5950</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>436</v>
+        <v>7125</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>418</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>33.79</v>
+        <v>19.68</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>18.62</v>
+        <v>19.68</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>149</v>
+        <v>5906.778523489933</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>194</v>
+        <v>7450</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>172</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>24.89</v>
+        <v>24.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>18.45</v>
+        <v>19.52</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2320</v>
+        <v>1565</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2910</v>
+        <v>1565</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2760</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>20</v>
+        <v>24.57</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>18.26</v>
+        <v>19.43</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>575</v>
+        <v>387.3553890246524</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>690</v>
+        <v>436</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>680</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>21</v>
+        <v>33.79</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18</v>
+        <v>18.62</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>505</v>
+        <v>149</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>605</v>
+        <v>194</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>590</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>34.19</v>
+        <v>24.89</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>17.95</v>
+        <v>18.45</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>126</v>
+        <v>2320</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>157</v>
+        <v>2910</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>138</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.87</v>
+        <v>18.26</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>416</v>
+        <v>575</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>515</v>
+        <v>690</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>488</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>21.31</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>17.21</v>
+        <v>18</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>635</v>
+        <v>505</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>740</v>
+        <v>605</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>715</v>
+        <v>590</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>24.88</v>
+        <v>34.19</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>17.07</v>
+        <v>17.95</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1020</v>
+        <v>126</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1280</v>
+        <v>157</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>24.86</v>
+        <v>24.4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>16.76</v>
+        <v>17.87</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>176</v>
+        <v>416</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>216</v>
+        <v>515</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>202</v>
+        <v>488</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>25</v>
+        <v>21.31</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15.91</v>
+        <v>17.21</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1320</v>
+        <v>635</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1650</v>
+        <v>740</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1530</v>
+        <v>715</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>22.85</v>
+        <v>24.88</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15.89</v>
+        <v>17.07</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>3080</v>
+        <v>1020</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3710</v>
+        <v>1280</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>3500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>18.72</v>
+        <v>24.86</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>15.69</v>
+        <v>16.76</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>14700</v>
+        <v>176</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>16650</v>
+        <v>216</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>16225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>16.79</v>
+        <v>25</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15.27</v>
+        <v>15.91</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>130</v>
+        <v>1320</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>153</v>
+        <v>1650</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>151</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>22.5</v>
+        <v>22.85</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15</v>
+        <v>15.89</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>78</v>
+        <v>3080</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>98</v>
+        <v>3710</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>92</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>20.78</v>
+        <v>18.72</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>14.9</v>
+        <v>15.69</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2550</v>
+        <v>14700</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3080</v>
+        <v>16650</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>2930</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>31.46</v>
+        <v>16.79</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>14.61</v>
+        <v>15.27</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>19.85</v>
+        <v>22.5</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>700</v>
+        <v>78</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>785</v>
+        <v>98</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>750</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>19.82</v>
+        <v>20.78</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>14.41</v>
+        <v>14.9</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>115</v>
+        <v>2550</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>133</v>
+        <v>3080</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>127</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17.65</v>
+        <v>31.46</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>14.25</v>
+        <v>14.61</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>95</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>520</v>
+        <v>117</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>505</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>27.78</v>
+        <v>19.85</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13.89</v>
+        <v>14.5</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>108</v>
+        <v>700</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>138</v>
+        <v>785</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>123</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>24.86</v>
+        <v>19.82</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>13.81</v>
+        <v>14.41</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>920</v>
+        <v>115</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1130</v>
+        <v>133</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1030</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>14.88</v>
+        <v>17.65</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>13.69</v>
+        <v>14.25</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>386</v>
+        <v>520</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>382</v>
+        <v>505</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>17.27</v>
+        <v>27.78</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>13.64</v>
+        <v>13.89</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>550</v>
+        <v>108</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>645</v>
+        <v>138</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>625</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>17.93</v>
+        <v>24.86</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>13.1</v>
+        <v>13.81</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>312</v>
+        <v>920</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>342</v>
+        <v>1130</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>328</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>20.92</v>
+        <v>14.88</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1525</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1850</v>
+        <v>386</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1730</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>12.78</v>
+        <v>17.27</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>12.78</v>
+        <v>13.64</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>358</v>
+        <v>550</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>406</v>
+        <v>645</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>406</v>
+        <v>625</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>17.72</v>
+        <v>17.93</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>12.66</v>
+        <v>13.1</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>89</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>14.46</v>
+        <v>20.92</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>12.45</v>
+        <v>13.07</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>496</v>
+        <v>1525</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>570</v>
+        <v>1850</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>560</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>14.49</v>
+        <v>12.78</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>12.32</v>
+        <v>12.78</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>158</v>
+        <v>406</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>155</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>12.73</v>
+        <v>17.72</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>12.12</v>
+        <v>12.66</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>80</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>372</v>
+        <v>93</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>370</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>16.42</v>
+        <v>14.46</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11.94</v>
+        <v>12.45</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>135</v>
+        <v>496</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>156</v>
+        <v>570</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>150</v>
+        <v>560</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>19.05</v>
+        <v>14.49</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>11.9</v>
+        <v>12.32</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>23.08</v>
+        <v>12.73</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>11.79</v>
+        <v>12.12</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>390</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>436</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>PTMP.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>11.61</v>
+        <v>25.86</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>11.61</v>
+        <v>12.07</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>30.41</v>
+        <v>16.42</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11.49</v>
+        <v>11.94</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>16.39</v>
+        <v>19.05</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11.48</v>
+        <v>11.9</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>12.38</v>
+        <v>23.08</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>11.39</v>
+        <v>11.79</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>406</v>
+        <v>351.3223273601007</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>450</v>
+        <v>436</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>22.5</v>
+        <v>11.61</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11.25</v>
+        <v>11.61</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>98</v>
+        <v>250</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>89</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2353,295 +2353,295 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>30.34</v>
+        <v>30.41</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11.24</v>
+        <v>11.49</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>99</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>14.73</v>
+        <v>16.39</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>11.11</v>
+        <v>11.48</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1955</v>
+        <v>61</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2220</v>
+        <v>71</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2150</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>12.67</v>
+        <v>12.38</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>11</v>
+        <v>11.39</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1515</v>
+        <v>406</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1690</v>
+        <v>454</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1665</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>16.44</v>
+        <v>22.5</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10.96</v>
+        <v>11.25</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22.48</v>
+        <v>30.34</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10.85</v>
+        <v>11.24</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>143</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>10.38</v>
+        <v>14.73</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>10.38</v>
+        <v>11.11</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>1955</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>585</v>
+        <v>2220</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>585</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>22.64</v>
+        <v>12.67</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>106</v>
+        <v>1515</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>130</v>
+        <v>1690</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>117</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>18.18</v>
+        <v>16.44</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>10.23</v>
+        <v>10.96</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>10.88</v>
+        <v>22.48</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>10.2</v>
+        <v>10.85</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>770</v>
+        <v>130</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>815</v>
+        <v>158</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>810</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>21.1</v>
+        <v>10.38</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10.09</v>
+        <v>10.38</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>550</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>14.68</v>
+        <v>22.64</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10.09</v>
+        <v>10.38</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>545</v>
+        <v>106</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>625</v>
+        <v>130</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>600</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2650,862 +2650,862 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>19.77</v>
+        <v>18.18</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>9.6</v>
+        <v>10.23</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>194</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>13.04</v>
+        <v>10.88</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9.57</v>
+        <v>10.2</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>580</v>
+        <v>770</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>650</v>
+        <v>815</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>630</v>
+        <v>810</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>17.09</v>
+        <v>21.1</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>9.49</v>
+        <v>10.09</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>316</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>370</v>
+        <v>660</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>346</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>11.72</v>
+        <v>14.68</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>128</v>
+        <v>545</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>143</v>
+        <v>625</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>25.18</v>
+        <v>19.77</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>9.35</v>
+        <v>9.6</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>11.4</v>
+        <v>13.04</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>9.33</v>
+        <v>9.57</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>388</v>
+        <v>580</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>430</v>
+        <v>650</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>422</v>
+        <v>630</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>13.95</v>
+        <v>17.09</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>20500</v>
+        <v>316</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>24500</v>
+        <v>370</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>23500</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>16.67</v>
+        <v>11.72</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2820</v>
+        <v>128</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>3290</v>
+        <v>143</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>3080</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>22.73</v>
+        <v>25.18</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9.09</v>
+        <v>9.35</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>104</v>
+        <v>388</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>111</v>
+        <v>430</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>109</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>28.09</v>
+        <v>13.95</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>8.99</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>177</v>
+        <v>20500</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>228</v>
+        <v>24500</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>194</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>22.69</v>
+        <v>16.67</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1085</v>
+        <v>2820</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1325</v>
+        <v>3290</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>1175</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>15.2</v>
+        <v>22.73</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>8.77</v>
+        <v>9.09</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>364</v>
+        <v>176</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>394</v>
+        <v>216</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>372</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>16.1</v>
+        <v>11</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>9</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>18.46</v>
+        <v>28.09</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>141</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>10.19</v>
+        <v>22.69</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>8.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>109</v>
+        <v>1085</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>119</v>
+        <v>1325</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>24.57</v>
+        <v>15.2</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>2600</v>
+        <v>364</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>3600</v>
+        <v>394</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>3130</v>
+        <v>372</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>14.29</v>
+        <v>16.1</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F99" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="G99" s="3" t="n">
         <v>128</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>121</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>10.11</v>
+        <v>18.46</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>7.98</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>945</v>
+        <v>135</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1035</v>
+        <v>154</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1015</v>
+        <v>141</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>12.17</v>
+        <v>10.19</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>7.83</v>
+        <v>8.33</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>230</v>
+        <v>109</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>16.35</v>
+        <v>24.57</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.69</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>106</v>
+        <v>2600</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>121</v>
+        <v>3600</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>112</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>13.38</v>
+        <v>14.29</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>7.48</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>4410</v>
+        <v>112</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>5000</v>
+        <v>128</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>4740</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>23.46</v>
+        <v>10.11</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>7.41</v>
+        <v>7.98</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>161</v>
+        <v>945</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>200</v>
+        <v>1035</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>174</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>10.05</v>
+        <v>12.17</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.41</v>
+        <v>7.83</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>372</v>
+        <v>230</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>416</v>
+        <v>258</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>406</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>11.76</v>
+        <v>16.35</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.35</v>
+        <v>7.69</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>22.86</v>
+        <v>13.38</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.14</v>
+        <v>7.48</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>140</v>
+        <v>4410</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>172</v>
+        <v>5000</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>150</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>15.62</v>
+        <v>23.46</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>14</v>
+        <v>10.05</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7</v>
+        <v>7.41</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>17.44</v>
+        <v>11.76</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>6.98</v>
+        <v>7.35</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>68</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>19.4</v>
+        <v>22.86</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>6.97</v>
+        <v>7.14</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>408</v>
+        <v>140</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>24.86</v>
+        <v>15.62</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>6.91</v>
+        <v>7.03</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>2260</v>
+        <v>130</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>2260</v>
+        <v>148</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1935</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>22.32</v>
+        <v>14</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>6.87</v>
+        <v>7</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>490</v>
+        <v>101</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>570</v>
+        <v>114</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>498</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3514,376 +3514,376 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>15.53</v>
+        <v>17.44</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.8</v>
+        <v>6.98</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>103</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>23.33</v>
+        <v>19.4</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>6.67</v>
+        <v>6.97</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>119</v>
+        <v>408</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>148</v>
+        <v>480</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>128</v>
+        <v>430</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>16</v>
+        <v>24.86</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>74</v>
+        <v>2260</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>87</v>
+        <v>2260</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>80</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>17.46</v>
+        <v>22.32</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>6.35</v>
+        <v>6.87</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>128</v>
+        <v>490</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>134</v>
+        <v>498</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>10.94</v>
+        <v>12.75</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>6.25</v>
+        <v>6.86</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>25</v>
+        <v>15.53</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>11.47</v>
+        <v>23.33</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.18</v>
+        <v>6.67</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>3460</v>
+        <v>119</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>3610</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11.92</v>
+        <v>16</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5.96</v>
+        <v>6.67</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>169</v>
+        <v>87</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>16.67</v>
+        <v>17.46</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5.83</v>
+        <v>6.35</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>605</v>
+        <v>128</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>700</v>
+        <v>148</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>635</v>
+        <v>134</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>25</v>
+        <v>10.94</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>5.77</v>
+        <v>6.25</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>1095</v>
+        <v>69</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1300</v>
+        <v>71</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>1100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>12.64</v>
+        <v>25</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>19.15</v>
+        <v>11.47</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>5.67</v>
+        <v>6.18</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>705</v>
+        <v>3460</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>840</v>
+        <v>3790</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>745</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>25</v>
+        <v>10.53</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>5.49</v>
+        <v>6.02</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>358</v>
+        <v>133</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>410</v>
+        <v>147</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>346</v>
+        <v>141</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>19.15</v>
+        <v>11.92</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>5.32</v>
+        <v>5.96</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>99</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3892,104 +3892,106 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11.58</v>
+        <v>16.67</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>5.26</v>
+        <v>5.83</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>605</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>106</v>
+        <v>700</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>100</v>
+        <v>635</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>5.15</v>
+        <v>5.77</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>98</v>
+        <v>1095</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>107</v>
+        <v>1300</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>14.36</v>
+        <v>12.64</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="E130" s="3" t="inlineStr"/>
+        <v>5.75</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="F130" s="3" t="n">
-        <v>446</v>
+        <v>98</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>410</v>
+        <v>92</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>11.5</v>
+        <v>19.15</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.87</v>
+        <v>5.67</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>2330</v>
+        <v>705</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>2520</v>
+        <v>840</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>2370</v>
+        <v>745</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3998,808 +4000,806 @@
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>13.33</v>
+        <v>25</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.71</v>
+        <v>5.49</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>2750</v>
+        <v>358</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>2890</v>
+        <v>410</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>2670</v>
+        <v>346</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>11.63</v>
+        <v>19.15</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4.65</v>
+        <v>5.32</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>10.6</v>
+        <v>11.58</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>4.64</v>
+        <v>5.26</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>158</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>24.91</v>
+        <v>10.31</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.56</v>
+        <v>5.15</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>1425</v>
+        <v>98</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1780</v>
+        <v>107</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>1490</v>
+        <v>102</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>11.61</v>
+        <v>14.36</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>158</v>
-      </c>
+        <v>5.13</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3" t="n">
-        <v>173</v>
+        <v>446</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>162</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>19.77</v>
+        <v>11.5</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4.52</v>
+        <v>4.87</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>177</v>
+        <v>2330</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>212</v>
+        <v>2520</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>185</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>13.04</v>
+        <v>13.33</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>2750</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>260</v>
+        <v>2890</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>240</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>20.56</v>
+        <v>11.63</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4.23</v>
+        <v>4.65</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1980</v>
+        <v>87</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>2140</v>
+        <v>96</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1850</v>
+        <v>90</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>15</v>
+        <v>10.6</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>4</v>
+        <v>4.64</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>101</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>15.09</v>
+        <v>24.91</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>3.77</v>
+        <v>4.56</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>159</v>
+        <v>1425</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>183</v>
+        <v>1780</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>165</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>12.69</v>
+        <v>11.61</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>3.73</v>
+        <v>4.52</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>11.97</v>
+        <v>19.77</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3.42</v>
+        <v>4.52</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>131</v>
+        <v>212</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>12.45</v>
+        <v>13.04</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>3.41</v>
+        <v>4.35</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>545</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>560</v>
+        <v>260</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>515</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>17.21</v>
+        <v>20.56</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3.28</v>
+        <v>4.23</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>615</v>
+        <v>1980</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>715</v>
+        <v>2140</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>630</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>23.66</v>
+        <v>15</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>101</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>460</v>
+        <v>115</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>384</v>
+        <v>104</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>11.83</v>
+        <v>15.09</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3.23</v>
+        <v>3.77</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>30.95</v>
+        <v>12.69</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3.17</v>
+        <v>3.73</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>34.34</v>
+        <v>15.52</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>14.71</v>
+        <v>11.97</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>17.65</v>
+        <v>12.45</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.94</v>
+        <v>3.41</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>210</v>
+        <v>545</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>210</v>
+        <v>515</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>11.41</v>
+        <v>17.21</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>2080</v>
+        <v>615</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>2100</v>
+        <v>715</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>1940</v>
+        <v>630</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>11.63</v>
+        <v>11.83</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>95</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>177</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>11.57</v>
+        <v>23.66</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>1210</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>1350</v>
+        <v>460</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>1245</v>
+        <v>384</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>11.89</v>
+        <v>30.95</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>288</v>
+        <v>141</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>294</v>
+        <v>130</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>12.15</v>
+        <v>34.34</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>16.7</v>
+        <v>17.65</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>5200</v>
+        <v>210</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>5450</v>
+        <v>240</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>4800</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>14.62</v>
+        <v>14.71</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>2550</v>
+        <v>70</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>2900</v>
+        <v>78</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>2600</v>
+        <v>70</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>10.16</v>
+        <v>11.41</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>172</v>
+        <v>2080</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>206</v>
+        <v>2100</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>192</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>10.39</v>
+        <v>11.63</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>78</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>79</v>
+        <v>177</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>17.95</v>
+        <v>11.57</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>79</v>
+        <v>1210</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>92</v>
+        <v>1350</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>80</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4808,79 +4808,79 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>17.44</v>
+        <v>11.89</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>87</v>
+        <v>288</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>88</v>
+        <v>294</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>12.36</v>
+        <v>12.15</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>11.75</v>
+        <v>16.7</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>5200</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>3900</v>
+        <v>5450</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3560</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4889,106 +4889,106 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>25</v>
+        <v>14.62</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>208</v>
+        <v>2550</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>250</v>
+        <v>2900</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>204</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>14</v>
+        <v>10.16</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>14.29</v>
+        <v>10.39</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>78</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2320</v>
+        <v>85</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>2070</v>
+        <v>79</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>11.54</v>
+        <v>17.95</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2100</v>
+        <v>79</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2320</v>
+        <v>92</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>2120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4997,160 +4997,160 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>10.34</v>
+        <v>17.44</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>384</v>
+        <v>101</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>354</v>
+        <v>88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>11.41</v>
+        <v>12.36</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>1490</v>
+        <v>89</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>1660</v>
+        <v>100</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>1515</v>
+        <v>91</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>11.83</v>
+        <v>11.75</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>187</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>208</v>
+        <v>3900</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>189</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>18.31</v>
+        <v>25</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>710</v>
+        <v>208</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>840</v>
+        <v>250</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>720</v>
+        <v>204</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>19.87</v>
+        <v>14</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>8125</v>
+        <v>202</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>9350</v>
+        <v>228</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>7900</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>79</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>79</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5159,1018 +5159,1018 @@
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>15.94</v>
+        <v>11.54</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>13800</v>
+        <v>2100</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>16000</v>
+        <v>2320</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>13975</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>10.59</v>
+        <v>10.34</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>89</v>
+        <v>348</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>94</v>
+        <v>384</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>86</v>
+        <v>354</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>21.97</v>
+        <v>11.41</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1.16</v>
+        <v>1.68</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>865</v>
+        <v>1490</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>1055</v>
+        <v>1660</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>875</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>13.64</v>
+        <v>11.83</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.14</v>
+        <v>1.61</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>89</v>
+        <v>189</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>10.68</v>
+        <v>18.31</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>210</v>
+        <v>710</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>228</v>
+        <v>840</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>208</v>
+        <v>720</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>20</v>
+        <v>15.38</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>432</v>
+        <v>90</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>362</v>
+        <v>79</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>22.58</v>
+        <v>19.87</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>1910</v>
+        <v>8125</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>2280</v>
+        <v>9350</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1870</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>12.38</v>
+        <v>15.94</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>108</v>
+        <v>13800</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>118</v>
+        <v>16000</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>105</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>12.78</v>
+        <v>10.59</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2640</v>
+        <v>89</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>3000</v>
+        <v>94</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>2660</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>17.5</v>
+        <v>21.97</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>163</v>
+        <v>865</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>188</v>
+        <v>1055</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>12.87</v>
+        <v>13.64</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>10.76</v>
+        <v>10.68</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>210</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>3500</v>
+        <v>228</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>3160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>28.48</v>
+        <v>20</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>152</v>
+        <v>406</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>151</v>
+        <v>362</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>11.79</v>
+        <v>22.58</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.54</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>390</v>
+        <v>1910</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>436</v>
+        <v>2280</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>388</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>14.43</v>
+        <v>17.5</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>2017.782805922118</v>
+        <v>163</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>2220</v>
+        <v>188</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>1930</v>
+        <v>160</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>18.04</v>
+        <v>12.87</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>93</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>332.87</v>
+        <v>114</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>280</v>
+        <v>101</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>29.27</v>
+        <v>12.78</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>85</v>
+        <v>2640</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>106</v>
+        <v>3000</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>81</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>10.17</v>
+        <v>12.38</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>2400</v>
+        <v>108</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>2600</v>
+        <v>118</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>2330</v>
+        <v>105</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>14.29</v>
+        <v>10.76</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>70</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>80</v>
+        <v>3500</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>69</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>11.24</v>
+        <v>28.48</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>16.02</v>
+        <v>11.79</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.51</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>181</v>
+        <v>390</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>210</v>
+        <v>436</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>177</v>
+        <v>388</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>10.49</v>
+        <v>14.43</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-2.47</v>
+        <v>-0.52</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>2017.782805922118</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>358</v>
+        <v>2220</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>316</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>11.19</v>
+        <v>18.04</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-2.52</v>
+        <v>-0.71</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>420</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>454</v>
+        <v>332.87</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>398</v>
+        <v>280</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>15.31</v>
+        <v>10.75</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.08</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>191</v>
+        <v>92</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>17.36</v>
+        <v>29.27</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.22</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>720</v>
+        <v>85</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>845</v>
+        <v>106</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>700</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>10.1</v>
+        <v>10.17</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.27</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>10300</v>
+        <v>2400</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>10900</v>
+        <v>2600</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>9600</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>10.65</v>
+        <v>14.29</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-3.24</v>
+        <v>-1.43</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>458</v>
+        <v>70</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>418</v>
+        <v>69</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>14.84</v>
+        <v>11.24</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-3.53</v>
+        <v>-1.78</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>2980</v>
+        <v>169</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>3250</v>
+        <v>188</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>2730</v>
+        <v>166</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>19.31</v>
+        <v>16.02</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.21</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>139</v>
+        <v>177</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>18.05</v>
+        <v>10.49</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.47</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>2700</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>3140</v>
+        <v>358</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>2550</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>21.99</v>
+        <v>11.19</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-4.26</v>
+        <v>-2.52</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>172</v>
+        <v>420</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>172</v>
+        <v>454</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>135</v>
+        <v>398</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>13.82</v>
+        <v>15.31</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.55</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>675</v>
+        <v>169</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>700</v>
+        <v>226</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>585</v>
+        <v>191</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>11.11</v>
+        <v>17.36</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-4.94</v>
+        <v>-2.78</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>83</v>
+        <v>720</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>90</v>
+        <v>845</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>77</v>
+        <v>700</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>10.19</v>
+        <v>10.1</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.03</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>346</v>
+        <v>10300</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>346</v>
+        <v>10900</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>298</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>23.53</v>
+        <v>10.65</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.24</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>700</v>
+        <v>458</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>840</v>
+        <v>478</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>645</v>
+        <v>418</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>13.58</v>
+        <v>14.84</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-5.56</v>
+        <v>-3.53</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>162</v>
+        <v>2980</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>184</v>
+        <v>3250</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>153</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>10.5</v>
+        <v>18.05</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.14</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>1175</v>
+        <v>2700</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>1210</v>
+        <v>3140</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>1025</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>16.8</v>
+        <v>19.31</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.14</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>2500</v>
+        <v>149</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>2920</v>
+        <v>173</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>2330</v>
+        <v>139</v>
       </c>
     </row>
     <row r="213">
@@ -6181,623 +6181,623 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>11.36</v>
+        <v>21.99</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-6.82</v>
+        <v>-4.26</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>140</v>
+        <v>163.9593505859375</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>10.67</v>
+        <v>13.82</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-7.33</v>
+        <v>-4.88</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>152</v>
+        <v>675</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>166</v>
+        <v>700</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>139</v>
+        <v>585</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>15.79</v>
+        <v>11.11</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-7.89</v>
+        <v>-4.94</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>787.2857142857142</v>
+        <v>83</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>880</v>
+        <v>90</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>700</v>
+        <v>77</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>20.41</v>
+        <v>10.19</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.1</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>118</v>
+        <v>346</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>90</v>
+        <v>298</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>12.73</v>
+        <v>23.53</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.15</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>248</v>
+        <v>840</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>202</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>24.62</v>
+        <v>21.24</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-5.56</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>1600</v>
+        <v>1850</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>1620</v>
+        <v>1855</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>1190</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>21.43</v>
+        <v>13.58</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-8.57</v>
+        <v>-5.56</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>64</v>
+        <v>153</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>18.95</v>
+        <v>10.5</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-8.77</v>
+        <v>-6.39</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>8475</v>
+        <v>1175</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>8475</v>
+        <v>1210</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>6500</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>24.44</v>
+        <v>16.8</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.8</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>91</v>
+        <v>2500</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>112</v>
+        <v>2920</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>82</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>20.81</v>
+        <v>11.36</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-9.09</v>
+        <v>-6.82</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>432</v>
+        <v>133.4552764892578</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>505</v>
+        <v>147</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>380</v>
+        <v>123</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>18.18</v>
+        <v>10.67</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>-11.93</v>
+        <v>-7.33</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>16.35</v>
+        <v>15.79</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>-12.5</v>
+        <v>-7.89</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>91</v>
+        <v>787.2857142857142</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>121</v>
+        <v>880</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>30.37</v>
+        <v>20.41</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.16</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>19.33</v>
+        <v>12.73</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.18</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>102</v>
+        <v>202</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>16.36</v>
+        <v>24.62</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>175</v>
+        <v>1600</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>192</v>
+        <v>1620</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>141</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>15.1</v>
+        <v>21.43</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.57</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>83</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>328</v>
+        <v>64</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>12.36</v>
+        <v>18.95</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>-14.61</v>
+        <v>-8.77</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>847.9298015393708</v>
+        <v>8475</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>1000</v>
+        <v>8475</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>760</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>18.87</v>
+        <v>24.44</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>-14.62</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>181</v>
+        <v>82</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>16.38</v>
+        <v>20.81</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>-14.66</v>
+        <v>-9.09</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>432</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>19.27</v>
+        <v>18.18</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>-14.68</v>
+        <v>-11.93</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>24.77</v>
+        <v>16.35</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>-14.68</v>
+        <v>-12.5</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>1810</v>
+        <v>91</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>2040</v>
+        <v>121</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>1395</v>
+        <v>91</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>17.21</v>
+        <v>30.37</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.07</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>11.83</v>
+        <v>19.33</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.29</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>127</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>378</v>
+        <v>142</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>288</v>
+        <v>102</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6806,153 +6806,396 @@
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>20.37</v>
+        <v>16.36</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.55</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>15.94</v>
+        <v>15.1</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.58</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>2760</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>3200</v>
+        <v>442</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>2350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>14.05</v>
+        <v>12.36</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.61</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>115</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>138</v>
+        <v>1000</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>103</v>
+        <v>760</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>25</v>
+        <v>18.87</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.62</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>18.44</v>
+        <v>16.38</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.66</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>120</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>167</v>
+        <v>540</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>120</v>
+        <v>396</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>NZIA.JK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>YUPI.JK</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="C250" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D241" s="2" t="n">
+      <c r="D250" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E241" s="3" t="n">
+      <c r="E250" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F241" s="3" t="n">
+      <c r="F250" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G241" s="3" t="n">
+      <c r="G250" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -616,39 +616,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>119</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>155</v>
+        <v>975</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>145</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -658,94 +658,94 @@
         <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>975</v>
+        <v>545</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>975</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>119</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>545</v>
+        <v>155</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>545</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12">
@@ -1048,655 +1048,655 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>24.76</v>
+        <v>33.61</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>22.8</v>
+        <v>22.95</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3830</v>
+        <v>122</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3830</v>
+        <v>163</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3770</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>21.95</v>
+        <v>24.76</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>21.95</v>
+        <v>22.8</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2870</v>
+        <v>3830</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3500</v>
+        <v>3830</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3500</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>24.75</v>
+        <v>21.95</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>21.78</v>
+        <v>21.95</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2490</v>
+        <v>2870</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2520</v>
+        <v>3500</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2460</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>24.68</v>
+        <v>24.75</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>21.04</v>
+        <v>21.78</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1930</v>
+        <v>2490</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2400</v>
+        <v>2520</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2330</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SKBM.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>20.56</v>
+        <v>21.04</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>615</v>
+        <v>1930</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>665</v>
+        <v>2400</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>645</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24.86</v>
+        <v>24.3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20.23</v>
+        <v>20.56</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1685</v>
+        <v>615</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2160</v>
+        <v>665</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2080</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>20.2</v>
+        <v>24.86</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1535</v>
+        <v>1685</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1845</v>
+        <v>2160</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1845</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6550</v>
+        <v>1535</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12125</v>
+        <v>6550</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5950</v>
+        <v>12125</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>5906.778523489933</v>
+        <v>5950</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>24.7</v>
+        <v>19.68</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.52</v>
+        <v>19.68</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1565</v>
+        <v>5906.778523489933</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1565</v>
+        <v>7450</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1500</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>24.57</v>
+        <v>24.7</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>19.43</v>
+        <v>19.52</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>387.3553890246524</v>
+        <v>1565</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>436</v>
+        <v>1565</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>418</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>33.79</v>
+        <v>24.57</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18.62</v>
+        <v>19.43</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>149</v>
+        <v>387.3553890246524</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>172</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>24.4</v>
+        <v>34.19</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>17.87</v>
+        <v>17.95</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>416</v>
+        <v>126</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>515</v>
+        <v>157</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>488</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>21.31</v>
+        <v>24.4</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>17.21</v>
+        <v>17.87</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>635</v>
+        <v>416</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>740</v>
+        <v>515</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>715</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>24.88</v>
+        <v>21.31</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1020</v>
+        <v>635</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1280</v>
+        <v>740</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1200</v>
+        <v>715</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>24.86</v>
+        <v>24.88</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>16.76</v>
+        <v>17.07</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>176</v>
+        <v>1020</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>216</v>
+        <v>1280</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>25</v>
+        <v>24.86</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15.91</v>
+        <v>16.76</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1320</v>
+        <v>176</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1650</v>
+        <v>216</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15.89</v>
+        <v>15.91</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3710</v>
+        <v>1650</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1705,754 +1705,754 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>18.72</v>
+        <v>22.85</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>15.69</v>
+        <v>15.89</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>14700</v>
+        <v>3080</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>16650</v>
+        <v>3710</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>16225</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>20.78</v>
+        <v>22.5</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2550</v>
+        <v>78</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3080</v>
+        <v>98</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2930</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>31.46</v>
+        <v>20.78</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>95</v>
+        <v>2550</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>117</v>
+        <v>3080</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>102</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>17.93</v>
+        <v>17.27</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>13.1</v>
+        <v>13.64</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>312</v>
+        <v>550</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>342</v>
+        <v>645</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>328</v>
+        <v>625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>20.92</v>
+        <v>17.93</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>13.07</v>
+        <v>13.1</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1525</v>
+        <v>312</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1850</v>
+        <v>342</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1730</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>12.78</v>
+        <v>20.92</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>358</v>
+        <v>1525</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>406</v>
+        <v>1850</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>406</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>17.72</v>
+        <v>12.78</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>12.66</v>
+        <v>12.78</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>89</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>14.46</v>
+        <v>17.72</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>12.45</v>
+        <v>12.66</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>570</v>
+        <v>93</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>560</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>14.49</v>
+        <v>14.46</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>138</v>
+        <v>496</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>155</v>
+        <v>560</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>12.73</v>
+        <v>14.49</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>12.12</v>
+        <v>12.32</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>138</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>370</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PTMP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>25.86</v>
+        <v>12.73</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>12.07</v>
+        <v>12.12</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>58</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>73</v>
+        <v>372</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>PTMP.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>16.42</v>
+        <v>25.86</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>11.94</v>
+        <v>12.07</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>19.05</v>
+        <v>16.42</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11.9</v>
+        <v>11.94</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>23.08</v>
+        <v>19.05</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>11.79</v>
+        <v>11.9</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>351.3223273601007</v>
+        <v>86</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>480</v>
+        <v>100</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>436</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>11.61</v>
+        <v>23.08</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11.61</v>
+        <v>11.79</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>218</v>
+        <v>351.3223273601007</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>250</v>
+        <v>436</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>30.41</v>
+        <v>11.61</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11.49</v>
+        <v>11.61</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>16.39</v>
+        <v>30.41</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>12.38</v>
+        <v>16.39</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>11.39</v>
+        <v>11.48</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>406</v>
+        <v>61</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>454</v>
+        <v>71</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>450</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>22.5</v>
+        <v>12.38</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>11.25</v>
+        <v>11.39</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>98</v>
+        <v>454</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>89</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2461,262 +2461,262 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>30.34</v>
+        <v>22.5</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>14.73</v>
+        <v>30.34</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>11.11</v>
+        <v>11.24</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1955</v>
+        <v>93</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2220</v>
+        <v>116</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>12.67</v>
+        <v>14.73</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1690</v>
+        <v>2220</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1665</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>16.44</v>
+        <v>12.67</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>74</v>
+        <v>1515</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>85</v>
+        <v>1690</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>81</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>22.48</v>
+        <v>16.44</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>10.85</v>
+        <v>10.96</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>22.64</v>
+        <v>10.38</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>10.38</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>106</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>130</v>
+        <v>585</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>117</v>
+        <v>585</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>10.88</v>
+        <v>18.18</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>815</v>
+        <v>104</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>810</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>21.1</v>
+        <v>10.88</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>770</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>660</v>
+        <v>815</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="85">
@@ -2749,34 +2749,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>19.77</v>
+        <v>21.1</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>179</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>212</v>
+        <v>660</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2785,862 +2785,862 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>13.04</v>
+        <v>19.77</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>580</v>
+        <v>179</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>650</v>
+        <v>212</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>630</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>17.09</v>
+        <v>13.04</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>9.49</v>
+        <v>9.57</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>316</v>
+        <v>580</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>370</v>
+        <v>650</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>346</v>
+        <v>630</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>25.18</v>
+        <v>11.72</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>11.4</v>
+        <v>25.18</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9.33</v>
+        <v>9.35</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>422</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>13.95</v>
+        <v>11.4</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>20500</v>
+        <v>388</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>24500</v>
+        <v>430</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>23500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>16.67</v>
+        <v>13.95</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2820</v>
+        <v>20500</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>3290</v>
+        <v>24500</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>3080</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>22.73</v>
+        <v>16.67</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>9.09</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>176</v>
+        <v>2820</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>216</v>
+        <v>3290</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>192</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>11</v>
+        <v>22.73</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>28.09</v>
+        <v>11</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>194</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>22.69</v>
+        <v>28.09</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1085</v>
+        <v>177</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1325</v>
+        <v>228</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>15.2</v>
+        <v>22.69</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>8.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>364</v>
+        <v>1085</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>394</v>
+        <v>1325</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>372</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>120</v>
+        <v>364</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>137</v>
+        <v>394</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>128</v>
+        <v>372</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>18.46</v>
+        <v>16.1</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>10.19</v>
+        <v>18.46</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>24.57</v>
+        <v>10.19</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2600</v>
+        <v>109</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>3600</v>
+        <v>119</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>3130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>14.29</v>
+        <v>24.57</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>112</v>
+        <v>2600</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>128</v>
+        <v>3600</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>121</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>10.11</v>
+        <v>14.29</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>7.98</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>945</v>
+        <v>112</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>1035</v>
+        <v>128</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>1015</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>12.17</v>
+        <v>10.11</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.83</v>
+        <v>7.98</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>230</v>
+        <v>945</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>258</v>
+        <v>1035</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>248</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>16.35</v>
+        <v>12.17</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.69</v>
+        <v>7.83</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>112</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>13.38</v>
+        <v>20.31</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.48</v>
+        <v>7.81</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>4410</v>
+        <v>65</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>5000</v>
+        <v>77</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>4740</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>23.46</v>
+        <v>16.35</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>10.05</v>
+        <v>13.38</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>372</v>
+        <v>4410</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>416</v>
+        <v>5000</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>406</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>11.76</v>
+        <v>23.46</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7.35</v>
+        <v>7.41</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>73</v>
+        <v>174</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>15.62</v>
+        <v>11.76</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>7.03</v>
+        <v>7.35</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>137</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>14</v>
+        <v>22.86</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>17.44</v>
+        <v>15.62</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.98</v>
+        <v>7.03</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>130</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>SQMI.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>19.4</v>
+        <v>33.33</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>6.97</v>
+        <v>7.02</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>408</v>
+        <v>64</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>480</v>
+        <v>76</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>430</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>12.75</v>
+        <v>19.4</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>6.86</v>
+        <v>6.97</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>115</v>
+        <v>480</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>109</v>
+        <v>430</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3649,509 +3649,511 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>15.53</v>
+        <v>24.86</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>103</v>
+        <v>2260</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>110</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>23.33</v>
+        <v>22.32</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>128</v>
+        <v>498</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>16</v>
+        <v>12.75</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>10.94</v>
+        <v>23.33</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F124" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G124" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>10.53</v>
+        <v>25</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>6.02</v>
+        <v>6.25</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>11.92</v>
+        <v>10.94</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>16.67</v>
+        <v>11.47</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>5.83</v>
+        <v>6.18</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>605</v>
+        <v>3460</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>700</v>
+        <v>3790</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>635</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>25</v>
+        <v>10.53</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>5.77</v>
+        <v>6.02</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>1095</v>
+        <v>133</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>1300</v>
+        <v>147</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>1100</v>
+        <v>141</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>19.15</v>
+        <v>12.64</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>11.58</v>
+        <v>19.15</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>705</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>100</v>
+        <v>745</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>10.31</v>
+        <v>25</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>5.15</v>
+        <v>5.49</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>102</v>
+        <v>346</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>14.36</v>
+        <v>19.38</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="E136" s="3" t="inlineStr"/>
+        <v>5.43</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>650</v>
+      </c>
       <c r="F136" s="3" t="n">
-        <v>446</v>
+        <v>770</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>410</v>
+        <v>680</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>11.5</v>
+        <v>19.15</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4.87</v>
+        <v>5.32</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>2330</v>
+        <v>103</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>2520</v>
+        <v>112</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>2370</v>
+        <v>99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4160,160 +4162,158 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>13.33</v>
+        <v>11.58</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>4.71</v>
+        <v>5.26</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>2750</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>2890</v>
+        <v>106</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>2670</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>11.63</v>
+        <v>10.31</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>10.6</v>
+        <v>14.36</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>148.9599964769581</v>
-      </c>
+        <v>5.13</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3" t="n">
-        <v>167</v>
+        <v>446</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>158</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>24.91</v>
+        <v>11.5</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>1425</v>
+        <v>2330</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>1780</v>
+        <v>2520</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>1490</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>11.61</v>
+        <v>13.33</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>158</v>
+        <v>2750</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>173</v>
+        <v>2890</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>162</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>19.77</v>
+        <v>11.63</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4322,214 +4322,214 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>13.04</v>
+        <v>10.6</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>20.56</v>
+        <v>12.21</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>4.23</v>
+        <v>4.58</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>1980</v>
+        <v>260</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>2140</v>
+        <v>294</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1850</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>15</v>
+        <v>24.91</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>4</v>
+        <v>4.56</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>101</v>
+        <v>1425</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>115</v>
+        <v>1780</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>104</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>15.09</v>
+        <v>19.77</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3.77</v>
+        <v>4.52</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>12.69</v>
+        <v>11.61</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3.73</v>
+        <v>4.52</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>15.52</v>
+        <v>13.04</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>59</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>11.97</v>
+        <v>20.56</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3.42</v>
+        <v>4.23</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>118</v>
+        <v>1980</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>131</v>
+        <v>2140</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>121</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>12.45</v>
+        <v>15</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>545</v>
+        <v>101</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>560</v>
+        <v>115</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>515</v>
+        <v>104</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4538,349 +4538,349 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>17.21</v>
+        <v>15.09</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>615</v>
+        <v>159</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>715</v>
+        <v>183</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>630</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>11.83</v>
+        <v>12.69</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>23.66</v>
+        <v>15.52</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>59</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>460</v>
+        <v>67</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>384</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>30.95</v>
+        <v>11.97</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3.17</v>
+        <v>3.42</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>34.34</v>
+        <v>12.45</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>133</v>
+        <v>545</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>133</v>
+        <v>560</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>102</v>
+        <v>515</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>17.65</v>
+        <v>17.21</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>210</v>
+        <v>615</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>240</v>
+        <v>715</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>14.71</v>
+        <v>23.66</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>70</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>70</v>
+        <v>384</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>11.41</v>
+        <v>11.83</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>2080</v>
+        <v>95</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2100</v>
+        <v>104</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1940</v>
+        <v>96</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>11.63</v>
+        <v>30.95</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>141</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>11.57</v>
+        <v>34.34</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>1210</v>
+        <v>133</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1350</v>
+        <v>133</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>1245</v>
+        <v>102</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>11.89</v>
+        <v>17.65</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>288</v>
+        <v>210</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>294</v>
+        <v>210</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>12.15</v>
+        <v>14.71</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>16.7</v>
+        <v>11.41</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>5200</v>
+        <v>2080</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>5450</v>
+        <v>2100</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>4800</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4889,79 +4889,79 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>14.62</v>
+        <v>11.63</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2550</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2900</v>
+        <v>192</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2600</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>10.16</v>
+        <v>11.57</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>172</v>
+        <v>1210</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>206</v>
+        <v>1350</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>192</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>10.39</v>
+        <v>11.89</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>78</v>
+        <v>286.4117805325255</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>79</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4970,79 +4970,79 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>17.95</v>
+        <v>12.15</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>17.44</v>
+        <v>16.7</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>87</v>
+        <v>5200</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>101</v>
+        <v>5450</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>88</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>12.36</v>
+        <v>14.62</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>89</v>
+        <v>2550</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>91</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5051,133 +5051,133 @@
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>11.75</v>
+        <v>10.16</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>172</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>3900</v>
+        <v>206</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>3560</v>
+        <v>192</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>25</v>
+        <v>10.39</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>14</v>
+        <v>17.95</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>204</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>14.29</v>
+        <v>17.44</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>87</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>2320</v>
+        <v>101</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>2070</v>
+        <v>88</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>11.54</v>
+        <v>12.36</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2100</v>
+        <v>89</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>2320</v>
+        <v>100</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>2120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5186,478 +5186,478 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>10.34</v>
+        <v>11.75</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>348</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>384</v>
+        <v>3900</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>354</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>11.41</v>
+        <v>25</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>1490</v>
+        <v>208</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>1660</v>
+        <v>250</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>1515</v>
+        <v>204</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>11.83</v>
+        <v>14</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>18.31</v>
+        <v>14.29</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>710</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>840</v>
+        <v>2320</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>720</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>15.38</v>
+        <v>11.54</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>79</v>
+        <v>2100</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>79</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>19.87</v>
+        <v>10.34</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>8125</v>
+        <v>348</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>9350</v>
+        <v>384</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>7900</v>
+        <v>354</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>15.94</v>
+        <v>11.41</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>13800</v>
+        <v>1490</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>16000</v>
+        <v>1660</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>13975</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>10.59</v>
+        <v>11.83</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>89</v>
+        <v>181.15625</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>94</v>
+        <v>208</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>21.97</v>
+        <v>18.31</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>865</v>
+        <v>710</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>1055</v>
+        <v>840</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>875</v>
+        <v>720</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>13.64</v>
+        <v>19.87</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>88</v>
+        <v>8125</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>100</v>
+        <v>9350</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>89</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>10.68</v>
+        <v>15.38</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>0.97</v>
+        <v>1.28</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>228</v>
+        <v>90</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>208</v>
+        <v>79</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>20</v>
+        <v>15.94</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>406</v>
+        <v>13800</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>432</v>
+        <v>16000</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>362</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>22.58</v>
+        <v>10.59</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>0.54</v>
+        <v>1.18</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>1910</v>
+        <v>89</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>2280</v>
+        <v>94</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1870</v>
+        <v>86</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>17.5</v>
+        <v>21.97</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>163</v>
+        <v>865</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>188</v>
+        <v>1055</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>12.87</v>
+        <v>13.64</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>12.78</v>
+        <v>10.68</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>2640</v>
+        <v>210</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>3000</v>
+        <v>228</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>2660</v>
+        <v>208</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>12.38</v>
+        <v>20</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>108</v>
+        <v>406</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>118</v>
+        <v>432</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>105</v>
+        <v>362</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>10.76</v>
+        <v>22.58</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>1910</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>3500</v>
+        <v>2280</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>3160</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="194">
@@ -5690,331 +5690,331 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>11.79</v>
+        <v>17.5</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>390</v>
+        <v>163</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>436</v>
+        <v>188</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>388</v>
+        <v>160</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>14.43</v>
+        <v>10.76</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>2017.782805922118</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>2220</v>
+        <v>3500</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>1930</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>18.04</v>
+        <v>12.38</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>108</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>332.87</v>
+        <v>118</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>280</v>
+        <v>105</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>10.75</v>
+        <v>12.78</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>99</v>
+        <v>2640</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>103</v>
+        <v>3000</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>92</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>29.27</v>
+        <v>12.87</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>10.17</v>
+        <v>11.79</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-1.27</v>
+        <v>-0.51</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>2400</v>
+        <v>390</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>2600</v>
+        <v>436</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>2330</v>
+        <v>388</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.52</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>70</v>
+        <v>2017.782805922118</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>80</v>
+        <v>2220</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>69</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>11.24</v>
+        <v>18.04</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.71</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>169</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>188</v>
+        <v>332.87</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>16.02</v>
+        <v>13.68</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.85</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>177</v>
+        <v>116</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>10.49</v>
+        <v>10.75</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-2.47</v>
+        <v>-1.08</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>99</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>358</v>
+        <v>103</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>316</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>11.19</v>
+        <v>29.27</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-2.52</v>
+        <v>-1.22</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>420</v>
+        <v>85</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>398</v>
+        <v>81</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>15.31</v>
+        <v>10.17</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.27</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>169</v>
+        <v>2400</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>226</v>
+        <v>2600</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>191</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6023,187 +6023,187 @@
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>17.36</v>
+        <v>14.29</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.43</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>720</v>
+        <v>70</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>845</v>
+        <v>80</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>700</v>
+        <v>69</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>10.1</v>
+        <v>11.24</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.78</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>10300</v>
+        <v>169</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>10900</v>
+        <v>188</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>9600</v>
+        <v>166</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>10.65</v>
+        <v>16.02</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-3.24</v>
+        <v>-2.21</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>458</v>
+        <v>181</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>478</v>
+        <v>210</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>418</v>
+        <v>177</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>14.84</v>
+        <v>10.49</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-3.53</v>
+        <v>-2.47</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>2980</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>3250</v>
+        <v>358</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>2730</v>
+        <v>316</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>18.05</v>
+        <v>11.19</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.52</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>2700</v>
+        <v>420</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>3140</v>
+        <v>454</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>2550</v>
+        <v>398</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>19.31</v>
+        <v>15.19</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.53</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>21.99</v>
+        <v>15.31</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-4.26</v>
+        <v>-2.55</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>163.9593505859375</v>
+        <v>169</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>135</v>
+        <v>191</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6212,835 +6212,835 @@
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>13.82</v>
+        <v>17.36</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.78</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="F214" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="G214" s="3" t="n">
         <v>700</v>
-      </c>
-      <c r="G214" s="3" t="n">
-        <v>585</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>11.11</v>
+        <v>10.1</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-4.94</v>
+        <v>-3.03</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>83</v>
+        <v>10300</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>90</v>
+        <v>10900</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>77</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>23.53</v>
+        <v>14.84</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.53</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>700</v>
+        <v>2980</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>840</v>
+        <v>3250</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>645</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>21.24</v>
+        <v>19.31</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>1850</v>
+        <v>149</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>1855</v>
+        <v>173</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>1445</v>
+        <v>139</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>13.58</v>
+        <v>18.05</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>162</v>
+        <v>2700</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>184</v>
+        <v>3140</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>153</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>10.5</v>
+        <v>21.99</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.26</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>1175</v>
+        <v>163.9593505859375</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>1210</v>
+        <v>172</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>1025</v>
+        <v>135</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>16.8</v>
+        <v>13.82</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.88</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>2500</v>
+        <v>675</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>2920</v>
+        <v>700</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>2330</v>
+        <v>585</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>11.36</v>
+        <v>11.11</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-6.82</v>
+        <v>-4.94</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>133.4552764892578</v>
+        <v>83</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>123</v>
+        <v>77</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>10.67</v>
+        <v>13.33</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>139</v>
+        <v>57</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>15.79</v>
+        <v>10.19</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.1</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>787.2857142857142</v>
+        <v>346</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>880</v>
+        <v>346</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>700</v>
+        <v>298</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>20.41</v>
+        <v>23.53</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.15</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>118</v>
+        <v>840</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>90</v>
+        <v>645</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>12.73</v>
+        <v>13.58</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.56</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>24.62</v>
+        <v>21.24</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-5.56</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>1600</v>
+        <v>1850</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>1620</v>
+        <v>1855</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>1190</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>21.43</v>
+        <v>10.5</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.39</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>83</v>
+        <v>1175</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>85</v>
+        <v>1210</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>64</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>18.95</v>
+        <v>14.94</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>-8.77</v>
+        <v>-6.51</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>8475</v>
+        <v>2610</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>8475</v>
+        <v>3000</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>6500</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>24.44</v>
+        <v>16.8</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.8</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>91</v>
+        <v>2500</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>112</v>
+        <v>2920</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>82</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>20.81</v>
+        <v>11.36</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>-9.09</v>
+        <v>-6.82</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>432</v>
+        <v>133.4552764892578</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>505</v>
+        <v>147</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>380</v>
+        <v>123</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>18.18</v>
+        <v>10.67</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>-11.93</v>
+        <v>-7.33</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>16.35</v>
+        <v>15.79</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>-12.5</v>
+        <v>-7.89</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>91</v>
+        <v>787.2857142857142</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>121</v>
+        <v>880</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>30.37</v>
+        <v>20.41</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.16</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>19.33</v>
+        <v>12.73</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.18</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>102</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>16.36</v>
+        <v>24.62</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>175</v>
+        <v>1600</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>192</v>
+        <v>1620</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>141</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>15.1</v>
+        <v>21.43</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.57</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>83</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>328</v>
+        <v>64</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>12.36</v>
+        <v>18.95</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>-14.61</v>
+        <v>-8.77</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>847.9298015393708</v>
+        <v>8475</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1000</v>
+        <v>8475</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>760</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>18.87</v>
+        <v>24.44</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>-14.62</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>181</v>
+        <v>82</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>16.38</v>
+        <v>20.81</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>-14.66</v>
+        <v>-9.09</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>432</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>19.27</v>
+        <v>18.18</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>-14.68</v>
+        <v>-11.93</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>24.77</v>
+        <v>16.35</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>-14.68</v>
+        <v>-12.5</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>1810</v>
+        <v>91</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>2040</v>
+        <v>121</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>1395</v>
+        <v>91</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>17.21</v>
+        <v>30.37</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.07</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>11.83</v>
+        <v>19.33</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.29</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>127</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>378</v>
+        <v>142</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>288</v>
+        <v>102</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7049,153 +7049,396 @@
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>20.37</v>
+        <v>16.36</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.55</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>15.94</v>
+        <v>15.1</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.58</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>2760</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>3200</v>
+        <v>442</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>14.05</v>
+        <v>12.36</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.61</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>115</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>138</v>
+        <v>1000</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>103</v>
+        <v>760</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>25</v>
+        <v>18.87</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.62</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>18.44</v>
+        <v>16.38</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.66</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>120</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F249" s="3" t="n">
-        <v>167</v>
+        <v>540</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>120</v>
+        <v>396</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
+          <t>YUPI.JK</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>NZIA.JK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G254" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
+      <c r="C259" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D250" s="2" t="n">
+      <c r="D259" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E250" s="3" t="n">
+      <c r="E259" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F250" s="3" t="n">
+      <c r="F259" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G250" s="3" t="n">
+      <c r="G259" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -616,12 +616,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -631,19 +631,19 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>268</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>975</v>
+        <v>290</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>975</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -652,46 +652,46 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>165</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>545</v>
+        <v>202</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>545</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>165</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>202</v>
+        <v>975</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>200</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10">
@@ -724,12 +724,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -739,13 +739,13 @@
         <v>25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>268</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>290</v>
+        <v>545</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>290</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12">
@@ -832,12 +832,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -847,24 +847,24 @@
         <v>24.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>525</v>
+        <v>214</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -874,13 +874,13 @@
         <v>24.76</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>214</v>
+        <v>525</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17">
@@ -1750,1978 +1750,1978 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>16.79</v>
+        <v>30.77</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15.27</v>
+        <v>15.38</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>22.5</v>
+        <v>16.79</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>20.78</v>
+        <v>22.5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2550</v>
+        <v>78</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3080</v>
+        <v>98</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2930</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>31.46</v>
+        <v>20.78</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>95</v>
+        <v>2550</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>117</v>
+        <v>3080</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>102</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>19.85</v>
+        <v>31.46</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>14.5</v>
+        <v>14.61</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>785</v>
+        <v>117</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>750</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>115</v>
+        <v>700</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>133</v>
+        <v>785</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>127</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>17.65</v>
+        <v>19.82</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>115</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>520</v>
+        <v>133</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>505</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>13.89</v>
+        <v>14.25</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>108</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>138</v>
+        <v>520</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>24.86</v>
+        <v>27.78</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>920</v>
+        <v>108</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1130</v>
+        <v>138</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1030</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>14.88</v>
+        <v>24.86</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>920</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>386</v>
+        <v>1130</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>382</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>17.27</v>
+        <v>14.88</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>550</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>645</v>
+        <v>386</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>625</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>17.93</v>
+        <v>17.27</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>13.1</v>
+        <v>13.64</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>312</v>
+        <v>550</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>342</v>
+        <v>645</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>328</v>
+        <v>625</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>20.92</v>
+        <v>13.19</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>13.07</v>
+        <v>13.19</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1525</v>
+        <v>93</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1850</v>
+        <v>103</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1730</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>12.78</v>
+        <v>17.93</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>12.78</v>
+        <v>13.1</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>406</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>17.72</v>
+        <v>20.92</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>12.66</v>
+        <v>13.07</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>80</v>
+        <v>1525</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>93</v>
+        <v>1850</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>89</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>14.49</v>
+        <v>17.72</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>12.32</v>
+        <v>12.66</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>138</v>
+        <v>74.24242401123047</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PTMP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>25.86</v>
+        <v>14.49</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>12.07</v>
+        <v>12.32</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>PTMP.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>19.05</v>
+        <v>25.86</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>11.9</v>
+        <v>12.07</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>23.08</v>
+        <v>16.42</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>351.3223273601007</v>
+        <v>135</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>436</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>131</v>
+        <v>351.3223273601007</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>12.38</v>
+        <v>30.41</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>11.39</v>
+        <v>11.49</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>406</v>
+        <v>131</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>450</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>30.34</v>
+        <v>12.38</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>11.24</v>
+        <v>11.39</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>116</v>
+        <v>454</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>99</v>
+        <v>450</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>16.44</v>
+        <v>14.73</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>74</v>
+        <v>1955</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>85</v>
+        <v>2220</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>81</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>10.38</v>
+        <v>16.44</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>74</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>585</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>22.64</v>
+        <v>22.48</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>770</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>815</v>
+        <v>585</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>810</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>545</v>
+        <v>91</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>625</v>
+        <v>104</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>21.1</v>
+        <v>10.88</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>770</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>660</v>
+        <v>815</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>19.77</v>
+        <v>21.1</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>179</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>212</v>
+        <v>660</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>13.04</v>
+        <v>14.68</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>17.09</v>
+        <v>19.77</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>346</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>11.72</v>
+        <v>13.04</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>128</v>
+        <v>580</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>143</v>
+        <v>650</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>140</v>
+        <v>630</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>25.18</v>
+        <v>17.09</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9.35</v>
+        <v>9.49</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>11.4</v>
+        <v>11.46</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>388</v>
+        <v>191</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>430</v>
+        <v>214</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>422</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>13.95</v>
+        <v>11.72</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>20500</v>
+        <v>128</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>24500</v>
+        <v>143</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>23500</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>16.67</v>
+        <v>25.18</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>2820</v>
+        <v>141</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>3290</v>
+        <v>174</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>3080</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>22.73</v>
+        <v>11.4</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>216</v>
+        <v>430</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>192</v>
+        <v>422</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>11</v>
+        <v>13.95</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>104</v>
+        <v>20500</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>111</v>
+        <v>24500</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>109</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>28.09</v>
+        <v>16.67</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>8.99</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>177</v>
+        <v>2820</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>228</v>
+        <v>3290</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>194</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RONY.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1085</v>
+        <v>176</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1325</v>
+        <v>216</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>15.2</v>
+        <v>11</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>8.77</v>
+        <v>9</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>372</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>16.1</v>
+        <v>28.09</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>128</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>RONY.JK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>18.46</v>
+        <v>22.69</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>135</v>
+        <v>1085</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>154</v>
+        <v>1325</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>141</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>10.19</v>
+        <v>15.2</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>117</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>24.57</v>
+        <v>16.1</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2600</v>
+        <v>120</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>3600</v>
+        <v>137</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>3130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>14.29</v>
+        <v>18.46</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>7.98</v>
+        <v>8.33</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>945</v>
+        <v>109</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1035</v>
+        <v>119</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1015</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FAST.JK</t>
+          <t>KONI.JK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>12.17</v>
+        <v>24.57</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7.83</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>230</v>
+        <v>2600</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>258</v>
+        <v>3600</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>248</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>BEER.JK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>20.31</v>
+        <v>14.29</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>69</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>16.35</v>
+        <v>10.11</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7.69</v>
+        <v>7.98</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>106</v>
+        <v>945</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>121</v>
+        <v>1035</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>112</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>FAST.JK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>13.38</v>
+        <v>12.17</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>7.48</v>
+        <v>7.83</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>4410</v>
+        <v>230</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>5000</v>
+        <v>258</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>4740</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>23.46</v>
+        <v>20.31</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7.41</v>
+        <v>7.81</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>174</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OASA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>10.05</v>
+        <v>16.35</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>7.41</v>
+        <v>7.69</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>11.76</v>
+        <v>13.38</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>68</v>
+        <v>4410</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>76</v>
+        <v>5000</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>73</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>22.86</v>
+        <v>10.05</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>172</v>
+        <v>416</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>150</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>15.62</v>
+        <v>23.46</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SQMI.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>33.33</v>
+        <v>11.76</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>7.02</v>
+        <v>7.35</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>76</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>14</v>
+        <v>22.86</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>17.44</v>
+        <v>15.62</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>6.98</v>
+        <v>7.03</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>84.02298670229705</v>
+        <v>130</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRUK.JK</t>
+          <t>SQMI.JK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>19.4</v>
+        <v>33.33</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>6.97</v>
+        <v>7.02</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>408</v>
+        <v>64</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>480</v>
+        <v>76</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>430</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>24.86</v>
+        <v>14</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2260</v>
+        <v>101</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>2260</v>
+        <v>114</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1935</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>22.32</v>
+        <v>17.44</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>490</v>
+        <v>84.02298670229705</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>570</v>
+        <v>101</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>498</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>TRUK.JK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>12.75</v>
+        <v>19.4</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>6.86</v>
+        <v>6.97</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>115</v>
+        <v>480</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>109</v>
+        <v>430</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OKAS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3730,430 +3730,430 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>15.53</v>
+        <v>24.86</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>103</v>
+        <v>2260</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>119</v>
+        <v>2260</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>110</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>23.33</v>
+        <v>22.32</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6.67</v>
+        <v>6.87</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>148</v>
+        <v>570</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>128</v>
+        <v>498</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>16</v>
+        <v>12.75</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>OKAS.JK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>17.46</v>
+        <v>15.53</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>6.35</v>
+        <v>6.8</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>10.94</v>
+        <v>16</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BLUE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11.47</v>
+        <v>17.46</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>6.18</v>
+        <v>6.35</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>3460</v>
+        <v>128</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>3790</v>
+        <v>148</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>3610</v>
+        <v>134</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>10.53</v>
+        <v>25</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>6.02</v>
+        <v>6.25</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AWAN.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>11.92</v>
+        <v>10.94</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KAEF.JK</t>
+          <t>BLUE.JK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>16.67</v>
+        <v>11.47</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>5.83</v>
+        <v>6.18</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>605</v>
+        <v>3460</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>700</v>
+        <v>3790</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>635</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>25</v>
+        <v>10.53</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>5.77</v>
+        <v>6.02</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1095</v>
+        <v>133</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>1300</v>
+        <v>147</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>1100</v>
+        <v>141</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CBUT.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>19.15</v>
+        <v>16.67</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>705</v>
+        <v>605</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>745</v>
+        <v>635</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KSIX.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>25</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>5.49</v>
+        <v>5.77</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>358</v>
+        <v>1095</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>410</v>
+        <v>1300</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>346</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SKBM.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>19.38</v>
+        <v>12.64</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>650</v>
+        <v>88</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>770</v>
+        <v>98</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>680</v>
+        <v>92</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SDMU.JK</t>
+          <t>CBUT.JK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>19.15</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5.32</v>
+        <v>5.67</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>103</v>
+        <v>705</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>99</v>
+        <v>745</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>KSIX.JK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4162,887 +4162,887 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>11.58</v>
+        <v>25</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5.26</v>
+        <v>5.49</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>95.93712158203124</v>
+        <v>358</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>106</v>
+        <v>410</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>100</v>
+        <v>346</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>10.31</v>
+        <v>19.38</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>5.15</v>
+        <v>5.43</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>98</v>
+        <v>650</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>107</v>
+        <v>770</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>102</v>
+        <v>680</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>SDMU.JK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>14.36</v>
+        <v>19.15</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="E140" s="3" t="inlineStr"/>
+        <v>5.32</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>103</v>
+      </c>
       <c r="F140" s="3" t="n">
-        <v>446</v>
+        <v>112</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>4.87</v>
+        <v>5.26</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>2330</v>
+        <v>95.93712158203124</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>2520</v>
+        <v>106</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>2370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>13.33</v>
+        <v>10.31</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>2750</v>
+        <v>98</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>2890</v>
+        <v>107</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>2670</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>11.63</v>
+        <v>14.36</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>5.13</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="n">
-        <v>96</v>
+        <v>446</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>148.9599964769581</v>
+        <v>2330</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>167</v>
+        <v>2520</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>158</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>12.21</v>
+        <v>13.33</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>4.58</v>
+        <v>4.71</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>260</v>
+        <v>2750</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>294</v>
+        <v>2890</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>274</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>24.91</v>
+        <v>11.63</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>1425</v>
+        <v>87</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1780</v>
+        <v>96</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1490</v>
+        <v>90</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>HYGN.JK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>19.77</v>
+        <v>10.6</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>177</v>
+        <v>148.9599964769581</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>11.61</v>
+        <v>12.21</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>162</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MDLA.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>13.04</v>
+        <v>24.91</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>4.35</v>
+        <v>4.56</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>236.5864082336426</v>
+        <v>1425</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>260</v>
+        <v>1780</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>240</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>20.56</v>
+        <v>11.61</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4.23</v>
+        <v>4.52</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>1980</v>
+        <v>158</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>2140</v>
+        <v>173</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1850</v>
+        <v>162</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>15</v>
+        <v>19.77</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BAJA.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>15.09</v>
+        <v>20.49</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.77</v>
+        <v>4.51</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>159</v>
+        <v>2470</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>183</v>
+        <v>2940</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>165</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>MDLA.JK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>12.69</v>
+        <v>13.04</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3.73</v>
+        <v>4.35</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>136</v>
+        <v>236.5864082336426</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>139</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BRRC.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>15.52</v>
+        <v>20.56</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>3.45</v>
+        <v>4.23</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>59</v>
+        <v>1980</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>67</v>
+        <v>2140</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>60</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>11.97</v>
+        <v>15</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>BAJA.JK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>12.45</v>
+        <v>15.09</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>545</v>
+        <v>159</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>515</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>KOTA.JK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>17.21</v>
+        <v>12.69</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>715</v>
+        <v>151</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>630</v>
+        <v>139</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>BRRC.JK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>23.66</v>
+        <v>15.52</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>372.8428554534912</v>
+        <v>59</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>460</v>
+        <v>67</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>384</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>30.95</v>
+        <v>12.45</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>141</v>
+        <v>545</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>165</v>
+        <v>560</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>130</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>LAND.JK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>34.34</v>
+        <v>16.67</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>3.03</v>
+        <v>3.33</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>17.65</v>
+        <v>17.21</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>210</v>
+        <v>615</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>240</v>
+        <v>715</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>14.71</v>
+        <v>23.66</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>70</v>
+        <v>372.8428554534912</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>70</v>
+        <v>384</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>11.41</v>
+        <v>11.83</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2080</v>
+        <v>95</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2100</v>
+        <v>104</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>1940</v>
+        <v>96</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>11.63</v>
+        <v>30.95</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>169.1666616666115</v>
+        <v>141</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>11.57</v>
+        <v>15.46</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>1210</v>
+        <v>194</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1350</v>
+        <v>224</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1245</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DEPO.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>11.89</v>
+        <v>34.34</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>286.4117805325255</v>
+        <v>133</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>294</v>
+        <v>102</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>12.15</v>
+        <v>17.65</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>16.7</v>
+        <v>14.71</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>5200</v>
+        <v>70</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>5450</v>
+        <v>78</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>4800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>14.62</v>
+        <v>11.41</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2550</v>
+        <v>2080</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>2900</v>
+        <v>2100</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>2600</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>CGAS.JK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5051,52 +5051,52 @@
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>10.16</v>
+        <v>11.63</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>172</v>
+        <v>169.1666616666115</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>10.39</v>
+        <v>11.57</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>78</v>
+        <v>1210</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>85</v>
+        <v>1350</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>79</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TOOL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5105,25 +5105,25 @@
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>17.95</v>
+        <v>12.15</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>DEPO.JK</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5132,52 +5132,52 @@
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>17.44</v>
+        <v>11.89</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>87</v>
+        <v>286.4117805325255</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>88</v>
+        <v>294</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>12.36</v>
+        <v>16.7</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>89</v>
+        <v>5200</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>100</v>
+        <v>5450</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>91</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5186,25 +5186,25 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>11.75</v>
+        <v>14.62</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>2.01</v>
+        <v>2.77</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>3299.655182913448</v>
+        <v>2550</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>3560</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NIRO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5213,214 +5213,214 @@
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>25</v>
+        <v>10.16</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>14</v>
+        <v>10.39</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>202</v>
+        <v>72.38636016845703</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>TOOL.JK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>14.29</v>
+        <v>17.95</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>2132.992554873512</v>
+        <v>79</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>2320</v>
+        <v>92</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2070</v>
+        <v>80</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>11.54</v>
+        <v>17.44</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>2100</v>
+        <v>87</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>2320</v>
+        <v>101</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>2120</v>
+        <v>88</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>10.34</v>
+        <v>12.36</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>348</v>
+        <v>89</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>384</v>
+        <v>100</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>354</v>
+        <v>91</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BOGA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>11.41</v>
+        <v>11.75</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>1490</v>
+        <v>3299.655182913448</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>1660</v>
+        <v>3900</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1515</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>NIRO.JK</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>11.83</v>
+        <v>25</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>181.15625</v>
+        <v>208</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>18.31</v>
+        <v>14</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>710</v>
+        <v>202</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>840</v>
+        <v>228</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>720</v>
+        <v>204</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>JARR.JK</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5429,565 +5429,565 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>19.87</v>
+        <v>14.29</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>8125</v>
+        <v>2132.992554873512</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>9350</v>
+        <v>2320</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>7900</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>15.38</v>
+        <v>11.54</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>79</v>
+        <v>2100</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>90</v>
+        <v>2320</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>79</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>15.94</v>
+        <v>10.34</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>13800</v>
+        <v>348</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>16000</v>
+        <v>384</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>13975</v>
+        <v>354</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>BOGA.JK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>10.59</v>
+        <v>11.41</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>89</v>
+        <v>1490</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>94</v>
+        <v>1660</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>86</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>21.97</v>
+        <v>11.83</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>865</v>
+        <v>181.15625</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>1055</v>
+        <v>208</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>875</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ENZO.JK</t>
+          <t>APEX.JK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>13.64</v>
+        <v>19.26</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>89</v>
+        <v>137</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>10.68</v>
+        <v>18.31</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>210</v>
+        <v>710</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>228</v>
+        <v>840</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>208</v>
+        <v>720</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>20</v>
+        <v>15.38</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>432</v>
+        <v>90</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>362</v>
+        <v>79</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>22.58</v>
+        <v>19.87</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>1910</v>
+        <v>8125</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>2280</v>
+        <v>9350</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>1870</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CHEK.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>28.48</v>
+        <v>15.94</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>152</v>
+        <v>13800</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>194</v>
+        <v>16000</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>151</v>
+        <v>13975</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>17.5</v>
+        <v>10.59</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>10.76</v>
+        <v>21.97</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>3155.431092081191</v>
+        <v>865</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>3500</v>
+        <v>1055</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>3160</v>
+        <v>875</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>12.38</v>
+        <v>13.64</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>12.78</v>
+        <v>10.68</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>2640</v>
+        <v>210</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>3000</v>
+        <v>228</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>2660</v>
+        <v>208</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>12.87</v>
+        <v>20</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>114</v>
+        <v>432</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>101</v>
+        <v>362</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RMKO.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>11.79</v>
+        <v>22.58</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.54</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>390</v>
+        <v>1910</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>436</v>
+        <v>2280</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>388</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>14.43</v>
+        <v>12.78</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>2017.782805922118</v>
+        <v>2640</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>2220</v>
+        <v>3000</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>1930</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>CHEK.JK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>18.04</v>
+        <v>28.48</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>299.5804195804196</v>
+        <v>152</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>332.87</v>
+        <v>194</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>280</v>
+        <v>151</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>13.68</v>
+        <v>12.87</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>10.75</v>
+        <v>17.5</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>29.27</v>
+        <v>12.38</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="E205" s="3" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ROCK.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5996,1294 +5996,1294 @@
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>10.17</v>
+        <v>10.76</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>2400</v>
+        <v>3155.431092081191</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>2600</v>
+        <v>3500</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>2330</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>RMKO.JK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>14.29</v>
+        <v>11.79</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>-1.43</v>
+        <v>-0.51</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>69</v>
+        <v>388</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>11.24</v>
+        <v>14.43</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>-1.78</v>
+        <v>-0.52</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>169</v>
+        <v>2017.782805922118</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>188</v>
+        <v>2220</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>166</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DEFI.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>16.02</v>
+        <v>18.04</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>-2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>181</v>
+        <v>299.5804195804196</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>210</v>
+        <v>332.87</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>10.49</v>
+        <v>14.17</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>-2.47</v>
+        <v>-0.83</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>315.9352714441999</v>
+        <v>120</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>316</v>
+        <v>119</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ASBI.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>11.19</v>
+        <v>13.68</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>-2.52</v>
+        <v>-0.85</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>420</v>
+        <v>118</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>454</v>
+        <v>133</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>398</v>
+        <v>116</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>15.19</v>
+        <v>10.75</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>-2.53</v>
+        <v>-1.08</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>15.31</v>
+        <v>29.27</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.22</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>191</v>
+        <v>81</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>ROCK.JK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>17.36</v>
+        <v>10.17</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>-2.78</v>
+        <v>-1.27</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>720</v>
+        <v>2400</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>845</v>
+        <v>2600</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>700</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>10.1</v>
+        <v>14.29</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>-3.03</v>
+        <v>-1.43</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>10300</v>
+        <v>70</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>10900</v>
+        <v>80</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>9600</v>
+        <v>69</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>10.65</v>
+        <v>11.24</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>-3.24</v>
+        <v>-1.78</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>458</v>
+        <v>169</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>478</v>
+        <v>188</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>418</v>
+        <v>166</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>DEFI.JK</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>14.84</v>
+        <v>16.02</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>-3.53</v>
+        <v>-2.21</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>2980</v>
+        <v>181</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>3250</v>
+        <v>210</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>2730</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>19.31</v>
+        <v>10.49</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.47</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>149</v>
+        <v>315.9352714441999</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>173</v>
+        <v>358</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>139</v>
+        <v>316</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ASBI.JK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>18.05</v>
+        <v>11.19</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>-4.14</v>
+        <v>-2.52</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>2700</v>
+        <v>420</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>3140</v>
+        <v>454</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>2550</v>
+        <v>398</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>21.99</v>
+        <v>15.19</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>-4.26</v>
+        <v>-2.53</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>163.9593505859375</v>
+        <v>80</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ZONE.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>13.82</v>
+        <v>15.31</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>-4.88</v>
+        <v>-2.55</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>675</v>
+        <v>169</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>700</v>
+        <v>226</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>585</v>
+        <v>191</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>KRYA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>11.11</v>
+        <v>17.36</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>-4.94</v>
+        <v>-2.78</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>83</v>
+        <v>720</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>90</v>
+        <v>845</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>77</v>
+        <v>700</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>POLA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>13.33</v>
+        <v>10.1</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>-5</v>
+        <v>-3.03</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>61</v>
+        <v>10300</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>68</v>
+        <v>10900</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>57</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BMSR.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.24</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>346</v>
+        <v>478</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>23.53</v>
+        <v>14.84</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.53</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>700</v>
+        <v>2980</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>840</v>
+        <v>3250</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>645</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>13.58</v>
+        <v>18.05</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>162</v>
+        <v>2700</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>184</v>
+        <v>3140</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>153</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>21.24</v>
+        <v>19.31</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.14</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>1850</v>
+        <v>149</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>1855</v>
+        <v>173</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>1445</v>
+        <v>139</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>10.5</v>
+        <v>21.99</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>-6.39</v>
+        <v>-4.26</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>1175</v>
+        <v>163.9593505859375</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1210</v>
+        <v>172</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>1025</v>
+        <v>135</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>UANG.JK</t>
+          <t>ZONE.JK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>14.94</v>
+        <v>13.82</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>-6.51</v>
+        <v>-4.88</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>2610</v>
+        <v>675</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>2440</v>
+        <v>585</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>KRYA.JK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>16.8</v>
+        <v>11.11</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>-6.8</v>
+        <v>-4.94</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>2500</v>
+        <v>83</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>2920</v>
+        <v>90</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>2330</v>
+        <v>77</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PEGE.JK</t>
+          <t>POLA.JK</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>11.36</v>
+        <v>13.33</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>-6.82</v>
+        <v>-5</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>133.4552764892578</v>
+        <v>61</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>123</v>
+        <v>57</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PURI.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>10.67</v>
+        <v>10.19</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>-7.33</v>
+        <v>-5.1</v>
       </c>
       <c r="E232" s="3" t="n">
-        <v>152</v>
+        <v>346</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>139</v>
+        <v>298</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>JECC.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>15.79</v>
+        <v>23.53</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>-7.89</v>
+        <v>-5.15</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>787.2857142857142</v>
+        <v>700</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>700</v>
+        <v>645</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>20.41</v>
+        <v>21.24</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>-8.16</v>
+        <v>-5.56</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>100</v>
+        <v>1850</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>118</v>
+        <v>1855</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>90</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>LABS.JK</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>12.73</v>
+        <v>13.58</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>-8.18</v>
+        <v>-5.56</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>24.62</v>
+        <v>10.5</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>-8.460000000000001</v>
+        <v>-6.39</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>1600</v>
+        <v>1175</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>1620</v>
+        <v>1210</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>1190</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>UANG.JK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>21.43</v>
+        <v>14.94</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>-8.57</v>
+        <v>-6.51</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>83</v>
+        <v>2610</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>85</v>
+        <v>3000</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>64</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>18.95</v>
+        <v>16.8</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>-8.77</v>
+        <v>-6.8</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>8475</v>
+        <v>2500</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>8475</v>
+        <v>2920</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>6500</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>PEGE.JK</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>24.44</v>
+        <v>11.36</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>91</v>
+        <v>133.4552764892578</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>PURI.JK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>20.81</v>
+        <v>10.67</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>-9.09</v>
+        <v>-7.33</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>432</v>
+        <v>152</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>505</v>
+        <v>166</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>380</v>
+        <v>139</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>JECC.JK</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>18.18</v>
+        <v>15.79</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>-11.93</v>
+        <v>-7.89</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>180</v>
+        <v>787.2857142857142</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>208</v>
+        <v>880</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>155</v>
+        <v>700</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>16.35</v>
+        <v>20.41</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>-12.5</v>
+        <v>-8.16</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>30.37</v>
+        <v>12.73</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>-14.07</v>
+        <v>-8.18</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>116</v>
+        <v>202</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>LEAD.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>19.33</v>
+        <v>24.62</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>-14.29</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>127</v>
+        <v>1600</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>142</v>
+        <v>1620</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>102</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>16.36</v>
+        <v>21.43</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>-14.55</v>
+        <v>-8.57</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>141</v>
+        <v>64</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PEHA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>15.1</v>
+        <v>18.95</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>-14.58</v>
+        <v>-8.77</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>378.7298613757622</v>
+        <v>8475</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>442</v>
+        <v>8475</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>328</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>12.36</v>
+        <v>24.44</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>-14.61</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>847.9298015393708</v>
+        <v>91</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>1000</v>
+        <v>112</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>760</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>18.87</v>
+        <v>20.81</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>-14.62</v>
+        <v>-9.09</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>218</v>
+        <v>432</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>252</v>
+        <v>505</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>181</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>16.38</v>
+        <v>18.18</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>-14.66</v>
+        <v>-11.93</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>468.4084412545869</v>
+        <v>180</v>
       </c>
       <c r="F249" s="3" t="n">
-        <v>540</v>
+        <v>208</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>396</v>
+        <v>155</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>24.77</v>
+        <v>16.35</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>-14.68</v>
+        <v>-12.5</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>1810</v>
+        <v>91</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>2040</v>
+        <v>121</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>1395</v>
+        <v>91</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>19.27</v>
+        <v>30.37</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>-14.68</v>
+        <v>-14.07</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="F251" s="3" t="n">
-        <v>260</v>
+        <v>176</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>LEAD.JK</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>17.21</v>
+        <v>19.33</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>-14.75</v>
+        <v>-14.29</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>11.83</v>
+        <v>16.36</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>-14.79</v>
+        <v>-14.55</v>
       </c>
       <c r="E253" s="3" t="n">
-        <v>316.9231611887614</v>
+        <v>175</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>378</v>
+        <v>192</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>288</v>
+        <v>141</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>PEHA.JK</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7292,153 +7292,369 @@
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>20.37</v>
+        <v>15.1</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>-14.81</v>
+        <v>-14.58</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>220</v>
+        <v>378.7298613757622</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>260</v>
+        <v>442</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>184</v>
+        <v>328</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C255" s="2" t="n">
-        <v>15.94</v>
+        <v>12.36</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>-14.86</v>
+        <v>-14.61</v>
       </c>
       <c r="E255" s="3" t="n">
-        <v>2760</v>
+        <v>847.9298015393708</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>2350</v>
+        <v>760</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>14.05</v>
+        <v>18.87</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.62</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>103</v>
+        <v>181</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>25</v>
+        <v>16.38</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>-14.88</v>
+        <v>-14.66</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>165</v>
+        <v>468.4084412545869</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>143</v>
+        <v>396</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>18.44</v>
+        <v>19.27</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.68</v>
       </c>
       <c r="E258" s="3" t="n">
-        <v>120</v>
+        <v>222</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>167</v>
+        <v>260</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
+          <t>YUPI.JK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>316.9231611887614</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ARTA.JK</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G263" s="3" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>GRIA.JK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G264" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>LCKM.JK</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
           <t>BHAT.JK</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C267" s="2" t="n">
         <v>23.08</v>
       </c>
-      <c r="D259" s="2" t="n">
+      <c r="D267" s="2" t="n">
         <v>-14.9</v>
       </c>
-      <c r="E259" s="3" t="n">
+      <c r="E267" s="3" t="n">
         <v>2080</v>
       </c>
-      <c r="F259" s="3" t="n">
+      <c r="F267" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G259" s="3" t="n">
+      <c r="G267" s="3" t="n">
         <v>1770</v>
       </c>
     </row>

--- a/data/performance/successful_signal_list.xlsx
+++ b/data/performance/successful_signal_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G267"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -616,12 +616,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -631,13 +631,13 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>268</v>
+        <v>414.3801616703698</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>290</v>
+        <v>545</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>290</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -670,66 +670,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TALF.JK</t>
+          <t>BCIC.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25</v>
+        <v>33.62</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>847.9298302283654</v>
+        <v>119</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>975</v>
+        <v>155</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>975</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>33.62</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>25</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>119</v>
+        <v>153.7625885009766</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -739,13 +739,13 @@
         <v>25</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>414.3801616703698</v>
+        <v>847.9298302283654</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>545</v>
+        <v>975</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>545</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12">
@@ -832,12 +832,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -847,24 +847,24 @@
         <v>24.76</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>214</v>
+        <v>525</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>262</v>
+        <v>655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -874,13 +874,13 @@
         <v>24.76</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>525</v>
+        <v>214</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>655</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17">
@@ -1156,1654 +1156,1654 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>24.68</v>
+        <v>30.71</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>21.04</v>
+        <v>21.43</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1930</v>
+        <v>143</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2400</v>
+        <v>183</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2330</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SKBM.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20.56</v>
+        <v>21.04</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>615</v>
+        <v>1930</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>665</v>
+        <v>2400</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>645</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>24.86</v>
+        <v>24.3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.23</v>
+        <v>20.56</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1685</v>
+        <v>615</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2160</v>
+        <v>665</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2080</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>20.2</v>
+        <v>24.86</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1535</v>
+        <v>1685</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1845</v>
+        <v>2160</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1845</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6550</v>
+        <v>1535</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12125</v>
+        <v>6550</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14025</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>19.75</v>
+        <v>19.87</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>5950</v>
+        <v>12125</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>7125</v>
+        <v>14025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>19.68</v>
+        <v>19.75</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5906.778523489933</v>
+        <v>5950</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>7450</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>24.7</v>
+        <v>19.68</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>19.52</v>
+        <v>19.68</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1565</v>
+        <v>5906.778523489933</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1565</v>
+        <v>7450</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1500</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>24.57</v>
+        <v>24.7</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>19.43</v>
+        <v>19.52</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>387.3553890246524</v>
+        <v>1565</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>436</v>
+        <v>1565</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>418</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CITY.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>33.79</v>
+        <v>24.57</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>18.62</v>
+        <v>19.43</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>149</v>
+        <v>387.3553890246524</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>172</v>
+        <v>418</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>CITY.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>24.89</v>
+        <v>33.79</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>18.45</v>
+        <v>18.62</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2320</v>
+        <v>149</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2910</v>
+        <v>194</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2760</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>20</v>
+        <v>24.89</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>575</v>
+        <v>2320</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>690</v>
+        <v>2910</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>680</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18</v>
+        <v>18.26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>605</v>
+        <v>690</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>34.19</v>
+        <v>21</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>17.95</v>
+        <v>18</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>138</v>
+        <v>590</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>24.4</v>
+        <v>34.19</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>17.87</v>
+        <v>17.95</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>416</v>
+        <v>126</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>515</v>
+        <v>157</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>488</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>ASPI.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>21.31</v>
+        <v>24.4</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>17.21</v>
+        <v>17.87</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>635</v>
+        <v>416</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>740</v>
+        <v>515</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>715</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>24.88</v>
+        <v>22.22</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>17.07</v>
+        <v>17.78</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1020</v>
+        <v>91</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1280</v>
+        <v>110</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1200</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>24.86</v>
+        <v>21.31</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>16.76</v>
+        <v>17.21</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>176</v>
+        <v>635</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>216</v>
+        <v>740</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>202</v>
+        <v>715</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>25</v>
+        <v>24.88</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15.91</v>
+        <v>17.07</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1320</v>
+        <v>1020</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1650</v>
+        <v>1280</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1530</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>22.85</v>
+        <v>24.86</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>15.89</v>
+        <v>16.76</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>3080</v>
+        <v>176</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3710</v>
+        <v>216</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>3500</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>18.72</v>
+        <v>25</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>15.69</v>
+        <v>15.91</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14700</v>
+        <v>1320</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16650</v>
+        <v>1650</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16225</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>30.77</v>
+        <v>22.85</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15.38</v>
+        <v>15.89</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>77</v>
+        <v>3080</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>102</v>
+        <v>3710</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>90</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>16.79</v>
+        <v>18.72</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>130</v>
+        <v>14700</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>153</v>
+        <v>16650</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>151</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>22.5</v>
+        <v>30.77</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>20.78</v>
+        <v>16.79</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>14.9</v>
+        <v>15.27</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2550</v>
+        <v>130</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>3080</v>
+        <v>153</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2930</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>JAST.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>31.46</v>
+        <v>22.5</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>19.85</v>
+        <v>20.78</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>700</v>
+        <v>2550</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>785</v>
+        <v>3080</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>750</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>19.82</v>
+        <v>31.46</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>14.41</v>
+        <v>14.61</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>17.65</v>
+        <v>19.85</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>442.3442631787593</v>
+        <v>700</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>520</v>
+        <v>785</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>505</v>
+        <v>750</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BOAT.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>27.78</v>
+        <v>19.82</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>13.89</v>
+        <v>14.41</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>24.86</v>
+        <v>17.65</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>13.81</v>
+        <v>14.25</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>920</v>
+        <v>442.3442631787593</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1130</v>
+        <v>520</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1030</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BOAT.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>14.88</v>
+        <v>27.78</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>13.69</v>
+        <v>13.89</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>334.0000051128927</v>
+        <v>108</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>386</v>
+        <v>138</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>382</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MTLA.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>17.27</v>
+        <v>24.86</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>13.64</v>
+        <v>13.81</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>550</v>
+        <v>920</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>645</v>
+        <v>1130</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>625</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AHAP.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>13.19</v>
+        <v>14.88</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>13.19</v>
+        <v>13.69</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>93</v>
+        <v>334.0000051128927</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>103</v>
+        <v>386</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>103</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COCO.JK</t>
+          <t>MTLA.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>17.93</v>
+        <v>17.27</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>13.1</v>
+        <v>13.64</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>312</v>
+        <v>550</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>342</v>
+        <v>645</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>328</v>
+        <v>625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BHAT.JK</t>
+          <t>AHAP.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>20.92</v>
+        <v>13.19</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>13.07</v>
+        <v>13.19</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1525</v>
+        <v>93</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1850</v>
+        <v>103</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1730</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>COCO.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>12.78</v>
+        <v>17.93</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>12.78</v>
+        <v>13.1</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>358</v>
+        <v>179.0071868896484</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>406</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PADI.JK</t>
+          <t>BHAT.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>17.72</v>
+        <v>20.92</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>12.66</v>
+        <v>13.07</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>74.24242401123047</v>
+        <v>1525</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>93</v>
+        <v>1850</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>89</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>14.46</v>
+        <v>12.78</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>12.45</v>
+        <v>12.78</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>570</v>
+        <v>406</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>560</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>PADI.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>14.49</v>
+        <v>17.72</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>12.32</v>
+        <v>12.66</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>138</v>
+        <v>74.24242401123047</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>12.73</v>
+        <v>14.46</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>12.12</v>
+        <v>12.45</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>314.9299303209459</v>
+        <v>496</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PTMP.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>25.86</v>
+        <v>14.49</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>12.07</v>
+        <v>12.32</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>16.42</v>
+        <v>12.73</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>135</v>
+        <v>314.9299303209459</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>156</v>
+        <v>372</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SURI.JK</t>
+          <t>PTMP.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>19.05</v>
+        <v>25.86</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11.9</v>
+        <v>12.07</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>23.08</v>
+        <v>16.42</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>351.3223273601007</v>
+        <v>135</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>436</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>SURI.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>11.61</v>
+        <v>19.05</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>11.61</v>
+        <v>11.9</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>250</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MPOW.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>30.41</v>
+        <v>23.08</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>11.49</v>
+        <v>11.79</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>131</v>
+        <v>351.3223273601007</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>16.39</v>
+        <v>11.61</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>11.48</v>
+        <v>11.61</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>12.38</v>
+        <v>30.41</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>11.39</v>
+        <v>11.49</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>406</v>
+        <v>131</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>454</v>
+        <v>193</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>450</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DKHH.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>22.5</v>
+        <v>16.39</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>30.34</v>
+        <v>12.38</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>11.24</v>
+        <v>11.39</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>116</v>
+        <v>454</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>99</v>
+        <v>450</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>DKHH.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>14.73</v>
+        <v>22.5</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1955</v>
+        <v>83</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2220</v>
+        <v>98</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2150</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>12.67</v>
+        <v>30.34</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1515</v>
+        <v>93</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1690</v>
+        <v>116</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1665</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>16.44</v>
+        <v>14.73</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>74</v>
+        <v>1955</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>85</v>
+        <v>2220</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>81</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>22.48</v>
+        <v>12.67</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>130</v>
+        <v>1515</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>158</v>
+        <v>1690</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>143</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>22.64</v>
+        <v>16.44</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>CTTH.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>10.38</v>
+        <v>22.48</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>10.38</v>
+        <v>10.85</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>530.6147330520499</v>
+        <v>130</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>585</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>18.18</v>
+        <v>22.64</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>770</v>
+        <v>530.6147330520499</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>815</v>
+        <v>585</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>810</v>
+        <v>585</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRUS.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>21.1</v>
+        <v>18.18</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>10.09</v>
+        <v>10.23</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>495.4545288085938</v>
+        <v>91</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>660</v>
+        <v>104</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>600</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2812,997 +2812,997 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>14.68</v>
+        <v>10.88</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>10.09</v>
+        <v>10.2</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>545</v>
+        <v>770</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>625</v>
+        <v>815</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>600</v>
+        <v>810</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MPXL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>19.77</v>
+        <v>14.68</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>9.6</v>
+        <v>10.09</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>212</v>
+        <v>625</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>194</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KETR.JK</t>
+          <t>TRUS.JK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>13.04</v>
+        <v>21.1</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>9.57</v>
+        <v>10.09</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>580</v>
+        <v>495.4545288085938</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>MPXL.JK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>17.09</v>
+        <v>19.77</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>346</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>KETR.JK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>11.46</v>
+        <v>13.04</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>191</v>
+        <v>580</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>214</v>
+        <v>650</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VERN.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>11.72</v>
+        <v>17.09</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>128</v>
+        <v>316</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>140</v>
+        <v>346</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIC.JK</t>
+          <t>VERN.JK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>25.18</v>
+        <v>11.72</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>PGLI.JK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>11.4</v>
+        <v>11.46</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>388<